--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,7 +582,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Absolut Vodkarita 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,42 +592,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.3</v>
-      </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>6.44</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="L4" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -637,42 +637,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J5" t="n">
-        <v>8.119999999999999</v>
+        <v>17.33</v>
       </c>
       <c r="K5" t="n">
-        <v>195</v>
+        <v>1976</v>
       </c>
       <c r="L5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
         <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>17.33</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1976</v>
+        <v>415</v>
       </c>
       <c r="L6" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -776,28 +776,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F8" t="n">
         <v>133</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J8" t="n">
         <v>17.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1505</v>
+        <v>1609</v>
       </c>
       <c r="L8" t="n">
         <v>31</v>
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,38 +821,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>8.619999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="K9" t="n">
-        <v>414</v>
+        <v>124</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -862,42 +862,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>10.22</v>
+        <v>8.69</v>
       </c>
       <c r="K10" t="n">
-        <v>164</v>
+        <v>1303</v>
       </c>
       <c r="L10" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>Sunny D Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -907,42 +907,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>10.33</v>
+        <v>15.46</v>
       </c>
       <c r="K11" t="n">
-        <v>124</v>
+        <v>325</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sunny D Variety Pack 8pk 12oz can</t>
+          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -952,42 +952,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>15.46</v>
+        <v>10.22</v>
       </c>
       <c r="K12" t="n">
-        <v>325</v>
+        <v>164</v>
       </c>
       <c r="L12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>Absolut Vodkarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -997,42 +997,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F13" t="n">
-        <v>156</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>8.68</v>
+        <v>6.45</v>
       </c>
       <c r="K13" t="n">
-        <v>1302</v>
+        <v>77</v>
       </c>
       <c r="L13" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>16</v>
@@ -1077,7 +1077,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,42 +1087,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>38</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>62</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
       <c r="J15" t="n">
-        <v>8.119999999999999</v>
+        <v>18.59</v>
       </c>
       <c r="K15" t="n">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="L15" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1136,38 +1136,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
         <v>2.1</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>18.59</v>
+        <v>8.82</v>
       </c>
       <c r="K16" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1177,35 +1177,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>2.1</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>8.82</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>212</v>
+        <v>49</v>
       </c>
       <c r="L17" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -1244,20 +1244,20 @@
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>11.71</v>
+        <v>12.13</v>
       </c>
       <c r="K18" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L18" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1267,42 +1267,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
         <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>8.66</v>
+        <v>7.72</v>
       </c>
       <c r="K19" t="n">
-        <v>156</v>
+        <v>371</v>
       </c>
       <c r="L19" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1312,42 +1312,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>7.17</v>
+        <v>7.02</v>
       </c>
       <c r="K20" t="n">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1357,42 +1357,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>7.72</v>
+        <v>7.17</v>
       </c>
       <c r="K21" t="n">
-        <v>371</v>
+        <v>86</v>
       </c>
       <c r="L21" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1402,42 +1402,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
         <v>2.6</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>9.75</v>
+        <v>8.66</v>
       </c>
       <c r="K22" t="n">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="L22" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1447,42 +1447,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="E23" t="n">
         <v>2.8</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>7.19</v>
+        <v>8.67</v>
       </c>
       <c r="K23" t="n">
-        <v>43</v>
+        <v>468</v>
       </c>
       <c r="L23" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1492,35 +1492,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F24" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>8.67</v>
+        <v>9.75</v>
       </c>
       <c r="K24" t="n">
-        <v>468</v>
+        <v>58</v>
       </c>
       <c r="L24" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N24" t="inlineStr"/>
     </row>
@@ -1544,7 +1544,7 @@
         <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
@@ -1589,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F26" t="n">
         <v>35</v>
@@ -1617,7 +1617,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1627,42 +1627,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
         <v>3.3</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
         <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>10.48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="L27" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1672,42 +1672,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>49</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33</v>
+      </c>
+      <c r="G28" t="n">
         <v>14</v>
       </c>
-      <c r="E28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F28" t="n">
-        <v>22</v>
-      </c>
-      <c r="G28" t="n">
-        <v>9</v>
-      </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>8.800000000000001</v>
+        <v>7.67</v>
       </c>
       <c r="K28" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
@@ -1736,23 +1736,23 @@
         <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>9.720000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="K29" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1762,42 +1762,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
         <v>3.6</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>7.67</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="L30" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1807,42 +1807,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>446</v>
       </c>
       <c r="E31" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>8.039999999999999</v>
+        <v>21.95</v>
       </c>
       <c r="K31" t="n">
-        <v>48</v>
+        <v>1141</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1856,38 +1856,38 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>449</v>
+        <v>86</v>
       </c>
       <c r="E32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="G32" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="H32" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
-        <v>21.96</v>
+        <v>8.66</v>
       </c>
       <c r="K32" t="n">
-        <v>1142</v>
+        <v>415</v>
       </c>
       <c r="L32" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="E33" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>8.66</v>
+        <v>4.88</v>
       </c>
       <c r="K33" t="n">
-        <v>416</v>
+        <v>59</v>
       </c>
       <c r="L33" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="N33" t="inlineStr"/>
     </row>
@@ -1949,7 +1949,7 @@
         <v>80</v>
       </c>
       <c r="E34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F34" t="n">
         <v>70</v>
@@ -1977,102 +1977,102 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="E35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F35" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="K35" t="n">
+        <v>45</v>
+      </c>
+      <c r="L35" t="n">
         <v>40</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>36</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>162</v>
-      </c>
-      <c r="L35" t="n">
-        <v>44</v>
       </c>
       <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="E36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F36" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>12</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>5.03</v>
+        <v>1.91</v>
       </c>
       <c r="K36" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="L36" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2081,38 +2081,38 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>7.79</v>
+        <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="L37" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2122,42 +2122,42 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E38" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>7.55</v>
+        <v>4.83</v>
       </c>
       <c r="K38" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2167,42 +2167,42 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E39" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>7.15</v>
+        <v>8.17</v>
       </c>
       <c r="K39" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="L39" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2216,38 +2216,38 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F40" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>18.33</v>
+        <v>7.79</v>
       </c>
       <c r="K40" t="n">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="L40" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2257,59 +2257,59 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="E41" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F41" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G41" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H41" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
-        <v>4.79</v>
+        <v>18.33</v>
       </c>
       <c r="K41" t="n">
-        <v>86</v>
+        <v>220</v>
       </c>
       <c r="L41" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="E42" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F42" t="n">
         <v>7</v>
@@ -2318,26 +2318,26 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1.91</v>
+        <v>7.15</v>
       </c>
       <c r="K42" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2347,42 +2347,42 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14</v>
+      </c>
+      <c r="G43" t="n">
         <v>5</v>
       </c>
-      <c r="F43" t="n">
-        <v>16</v>
-      </c>
-      <c r="G43" t="n">
-        <v>4</v>
-      </c>
       <c r="H43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I43" t="n">
         <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>8.15</v>
+        <v>10.26</v>
       </c>
       <c r="K43" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="L43" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2392,92 +2392,92 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E44" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="F44" t="n">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>16.92</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>812</v>
+        <v>117</v>
       </c>
       <c r="L44" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="E45" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="F45" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>8.6</v>
+        <v>16.91</v>
       </c>
       <c r="K45" t="n">
-        <v>103</v>
+        <v>812</v>
       </c>
       <c r="L45" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2486,38 +2486,38 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F46" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>10.26</v>
+        <v>8.6</v>
       </c>
       <c r="K46" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="L46" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2527,42 +2527,42 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
         <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>6.81</v>
+        <v>7.56</v>
       </c>
       <c r="K47" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="L47" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2572,42 +2572,42 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="E48" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>7.56</v>
+        <v>6.81</v>
       </c>
       <c r="K48" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="L48" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2621,38 +2621,38 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.02</v>
+        <v>12</v>
       </c>
       <c r="E49" t="n">
         <v>6.4</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
-        <v>6.44</v>
+        <v>12.88</v>
       </c>
       <c r="K49" t="n">
-        <v>39</v>
+        <v>193</v>
       </c>
       <c r="L49" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2662,42 +2662,42 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>10.02</v>
       </c>
       <c r="E50" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>7.58</v>
+        <v>6.44</v>
       </c>
       <c r="K50" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2707,42 +2707,42 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="F51" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
         <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>12.88</v>
+        <v>7.58</v>
       </c>
       <c r="K51" t="n">
-        <v>193</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2752,42 +2752,42 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E52" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="K52" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="L52" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2797,92 +2797,92 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E53" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="F53" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>10.33</v>
+        <v>7.5</v>
       </c>
       <c r="K53" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L53" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E54" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>7.59</v>
+        <v>4.5</v>
       </c>
       <c r="K54" t="n">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="L54" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="F55" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G55" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I55" t="n">
         <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>4.5</v>
+        <v>10.33</v>
       </c>
       <c r="K55" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="L55" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="N55" t="inlineStr"/>
     </row>
@@ -3249,7 +3249,7 @@
         <v>13</v>
       </c>
       <c r="E63" t="n">
-        <v>33.4</v>
+        <v>36.3</v>
       </c>
       <c r="F63" t="n">
         <v>10</v>
@@ -3384,7 +3384,7 @@
         <v>65</v>
       </c>
       <c r="E66" t="n">
-        <v>51.6</v>
+        <v>58</v>
       </c>
       <c r="F66" t="n">
         <v>8</v>
@@ -3576,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3646,7 +3646,7 @@
         <v>-5</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Blaine (7)</t>
+          <t>Chanhassen (7)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -3757,7 +3757,7 @@
         <v>-5</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -4016,7 +4016,7 @@
         <v>-12</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.8</v>
+        <v>-17.5</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -4127,7 +4127,7 @@
         <v>-13</v>
       </c>
       <c r="E15" t="n">
-        <v>-11</v>
+        <v>-11.6</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
@@ -4194,28 +4194,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E17" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3</v>
+        <v>-4.5</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -4248,11 +4248,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4263,33 +4263,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.5</v>
+        <v>99</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4300,29 +4300,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E20" t="n">
-        <v>99</v>
+        <v>-2.4</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -4337,29 +4337,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Monaco Tropic Rush 12oz can</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ramsey (4)</t>
+          <t>Minneapolis (15)</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -4379,24 +4379,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monaco Tropic Rush 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E22" t="n">
         <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Minneapolis (15)</t>
+          <t>Minneapolis (11)</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4420,20 +4420,20 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="E23" t="n">
-        <v>99</v>
+        <v>-5.7</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Minneapolis (11)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -4448,19 +4448,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 12oz can</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7</v>
+        <v>99</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -4490,24 +4490,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E25" t="n">
-        <v>99</v>
+        <v>-2.5</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -4517,34 +4517,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STOCKOUT</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5</v>
+        <v>1.7</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>8</v>
+        <v>316</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Blaine (17)</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -4559,29 +4559,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>316</v>
+        <v>225</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Chanhassen (17)</t>
+          <t>St. Louis Park (13)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -4596,29 +4596,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>St. Louis Park (13)</t>
+          <t>Plymouth (10)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4642,20 +4642,20 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Plymouth (10)</t>
+          <t>Plymouth (9)</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -4670,29 +4670,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F30" t="n">
         <v>6</v>
       </c>
-      <c r="E30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9</v>
-      </c>
       <c r="G30" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Plymouth (9)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4716,24 +4716,24 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>St. Louis Park (5), Vadnais Heights (4)</t>
+          <t>Bloomington (7)</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4744,29 +4744,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F32" t="n">
         <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Chanhassen (6)</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -4781,29 +4781,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -4818,29 +4818,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F34" t="n">
         <v>4</v>
       </c>
-      <c r="E34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>6</v>
-      </c>
       <c r="G34" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -4855,33 +4855,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -4892,29 +4892,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Bloomington (7)</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="F37" t="n">
         <v>7</v>
@@ -4966,29 +4966,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -5008,24 +5008,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -5040,33 +5040,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Vadnais Heights (5)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5077,29 +5077,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -5119,61 +5119,61 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>38</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Stillwater (5)</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
         <v>2</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F42" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" t="n">
-        <v>31</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="F43" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>944</v>
+        <v>31</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Minneapolis (24), Rosemount (19)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5197,20 +5197,20 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="F44" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G44" t="n">
-        <v>373</v>
+        <v>944</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Blaine (13), Bloomington (4)</t>
+          <t>Minneapolis (24), Rosemount (19)</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5234,20 +5234,20 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E45" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Andover (15)</t>
+          <t>Blaine (12), Bloomington (5)</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -5262,29 +5262,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E46" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>220</v>
+        <v>329</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Andover (15)</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5308,24 +5308,24 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E47" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G47" t="n">
-        <v>220</v>
+        <v>329</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Minnetonka (6), Vadnais Heights (4)</t>
+          <t>Minnetonka (7), Bloomington (4), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -5336,29 +5336,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Blaine (8)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -5388,18 +5388,18 @@
         <v>4.5</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Stillwater (10)</t>
+          <t>Minneapolis (8), Stillwater (4)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5419,20 +5419,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Blaine (8)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -5452,24 +5452,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E51" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -5484,33 +5484,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bloomington (5)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5521,29 +5521,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E53" t="n">
-        <v>2.4</v>
+        <v>99</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6), Minnetonka (5)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -5558,33 +5558,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>99</v>
+        <v>5.1</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5595,33 +5595,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G55" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Andover (6), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -5632,33 +5632,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Andover (6), Vadnais Heights (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5669,33 +5669,33 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>10.7</v>
+        <v>2.5</v>
       </c>
       <c r="F57" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (9)</t>
+          <t>St. Louis Park (9)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5743,33 +5743,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>7.1</v>
+        <v>99</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5780,33 +5780,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="E60" t="n">
-        <v>2.5</v>
+        <v>60.1</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>St. Louis Park (9)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5817,29 +5817,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>3.8</v>
+        <v>99</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -5854,33 +5854,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>99</v>
+        <v>11.1</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G62" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -5891,29 +5891,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>60.1</v>
+        <v>3.2</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5928,33 +5928,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E64" t="n">
-        <v>99</v>
+        <v>7.1</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -5970,24 +5970,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Cottage Grove (7)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -6002,29 +6002,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E66" t="n">
-        <v>2.5</v>
+        <v>99</v>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G66" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Cottage Grove (7)</t>
+          <t>Minneapolis (27)</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -6039,29 +6039,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
-        <v>99</v>
+        <v>11.7</v>
       </c>
       <c r="F67" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Minneapolis (27)</t>
+          <t>Cottage Grove (6)</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -6076,25 +6076,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E68" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F68" t="n">
         <v>5</v>
       </c>
       <c r="G68" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
@@ -6113,29 +6113,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 4pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>11.7</v>
+        <v>3.3</v>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Cottage Grove (6)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6150,33 +6150,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Vadnais Heights (5)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -6187,29 +6187,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Vadnais Heights (5)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="F72" t="n">
         <v>4</v>
@@ -6246,11 +6246,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6261,19 +6261,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>4.5</v>
+        <v>99</v>
       </c>
       <c r="F73" t="n">
         <v>4</v>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -6298,33 +6298,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>99</v>
+        <v>4.4</v>
       </c>
       <c r="F74" t="n">
         <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -6335,33 +6335,33 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F75" t="n">
         <v>6</v>
       </c>
-      <c r="E75" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F75" t="n">
-        <v>4</v>
-      </c>
       <c r="G75" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6372,29 +6372,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>14.3</v>
+        <v>4.1</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -6409,29 +6409,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D77" t="n">
+        <v>17</v>
+      </c>
+      <c r="E77" t="n">
         <v>4</v>
       </c>
-      <c r="E77" t="n">
-        <v>4.1</v>
-      </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Cottage Grove (11)</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -6446,33 +6446,33 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" t="n">
         <v>4</v>
       </c>
-      <c r="F78" t="n">
-        <v>11</v>
-      </c>
       <c r="G78" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Cottage Grove (11)</t>
+          <t>Osseo (4)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -6483,33 +6483,33 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="F79" t="n">
         <v>4</v>
       </c>
       <c r="G79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Osseo (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6520,29 +6520,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E80" t="n">
-        <v>2.7</v>
+        <v>99</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G80" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -6557,19 +6557,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>10</v>
       </c>
       <c r="E81" t="n">
-        <v>99</v>
+        <v>6.4</v>
       </c>
       <c r="F81" t="n">
         <v>6</v>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6606,7 +6606,7 @@
         <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>6.4</v>
+        <v>99</v>
       </c>
       <c r="F82" t="n">
         <v>6</v>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -6631,29 +6631,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>99</v>
+        <v>26.8</v>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -6668,19 +6668,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Lemonade 12oz can</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E84" t="n">
-        <v>26.8</v>
+        <v>99</v>
       </c>
       <c r="F84" t="n">
         <v>5</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -6705,19 +6705,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monaco Lemonade 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F85" t="n">
         <v>5</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6751,20 +6751,20 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
+        <v>99</v>
+      </c>
+      <c r="F86" t="n">
         <v>4</v>
       </c>
-      <c r="F86" t="n">
-        <v>5</v>
-      </c>
       <c r="G86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -6779,19 +6779,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>99</v>
+        <v>32.1</v>
       </c>
       <c r="F87" t="n">
         <v>4</v>
@@ -6801,47 +6801,10 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Monaco Purple Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F88" t="n">
-        <v>4</v>
-      </c>
-      <c r="G88" t="n">
-        <v>8</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,7 +582,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>Absolut Vodkarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,42 +592,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>8.119999999999999</v>
+        <v>6.44</v>
       </c>
       <c r="K4" t="n">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="L4" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -637,42 +637,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="I5" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>17.33</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1976</v>
+        <v>195</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
         <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="J6" t="n">
-        <v>8.640000000000001</v>
+        <v>17.33</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>1976</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -776,28 +776,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F8" t="n">
         <v>133</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H8" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J8" t="n">
         <v>17.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1609</v>
+        <v>1505</v>
       </c>
       <c r="L8" t="n">
         <v>31</v>
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,38 +821,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>10.33</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>124</v>
+        <v>414</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -862,42 +862,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F10" t="n">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>8.69</v>
+        <v>10.22</v>
       </c>
       <c r="K10" t="n">
-        <v>1303</v>
+        <v>164</v>
       </c>
       <c r="L10" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunny D Variety Pack 8pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -907,42 +907,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>15.46</v>
+        <v>10.33</v>
       </c>
       <c r="K11" t="n">
-        <v>325</v>
+        <v>124</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
+          <t>Sunny D Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -952,42 +952,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>10.22</v>
+        <v>15.46</v>
       </c>
       <c r="K12" t="n">
-        <v>164</v>
+        <v>325</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Absolut Vodkarita 4pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -997,42 +997,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>98</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>156</v>
+      </c>
+      <c r="G13" t="n">
         <v>6</v>
       </c>
-      <c r="E13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F13" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
-        <v>6.45</v>
+        <v>8.68</v>
       </c>
       <c r="K13" t="n">
-        <v>77</v>
+        <v>1302</v>
       </c>
       <c r="L13" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>16</v>
@@ -1077,7 +1077,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,42 +1087,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>18.59</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>223</v>
+        <v>49</v>
       </c>
       <c r="L15" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1136,38 +1136,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
         <v>2.1</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>8.82</v>
+        <v>18.59</v>
       </c>
       <c r="K16" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1177,35 +1177,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
         <v>2.1</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>8.119999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="K17" t="n">
-        <v>49</v>
+        <v>212</v>
       </c>
       <c r="L17" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -1244,20 +1244,20 @@
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>12.13</v>
+        <v>11.71</v>
       </c>
       <c r="K18" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1267,42 +1267,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
         <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>7.72</v>
+        <v>8.66</v>
       </c>
       <c r="K19" t="n">
-        <v>371</v>
+        <v>156</v>
       </c>
       <c r="L19" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1312,42 +1312,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>7.02</v>
+        <v>7.17</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="L20" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1357,42 +1357,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>7.17</v>
+        <v>7.72</v>
       </c>
       <c r="K21" t="n">
-        <v>86</v>
+        <v>371</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1402,42 +1402,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
         <v>2.6</v>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>8.66</v>
+        <v>9.75</v>
       </c>
       <c r="K22" t="n">
-        <v>156</v>
+        <v>58</v>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1447,42 +1447,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
         <v>2.8</v>
       </c>
       <c r="F23" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>8.67</v>
+        <v>7.19</v>
       </c>
       <c r="K23" t="n">
-        <v>468</v>
+        <v>43</v>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1492,35 +1492,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>9.75</v>
+        <v>8.67</v>
       </c>
       <c r="K24" t="n">
-        <v>58</v>
+        <v>468</v>
       </c>
       <c r="L24" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N24" t="inlineStr"/>
     </row>
@@ -1544,7 +1544,7 @@
         <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
@@ -1589,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F26" t="n">
         <v>35</v>
@@ -1617,7 +1617,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1627,42 +1627,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
         <v>3.3</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>8.800000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="K27" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1672,42 +1672,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F28" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>7.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="L28" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
@@ -1736,23 +1736,23 @@
         <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>10.48</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="L29" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1762,42 +1762,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="E30" t="n">
         <v>3.6</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>8.039999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="K30" t="n">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1807,42 +1807,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>446</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="F31" t="n">
-        <v>171</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>21.95</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>1141</v>
+        <v>48</v>
       </c>
       <c r="L31" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1856,38 +1856,38 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>86</v>
+        <v>449</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
+        <v>171</v>
       </c>
       <c r="G32" t="n">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="H32" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>8.66</v>
+        <v>21.96</v>
       </c>
       <c r="K32" t="n">
-        <v>415</v>
+        <v>1142</v>
       </c>
       <c r="L32" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H33" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
-        <v>4.88</v>
+        <v>8.66</v>
       </c>
       <c r="K33" t="n">
-        <v>59</v>
+        <v>416</v>
       </c>
       <c r="L33" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="N33" t="inlineStr"/>
     </row>
@@ -1949,7 +1949,7 @@
         <v>80</v>
       </c>
       <c r="E34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F34" t="n">
         <v>70</v>
@@ -1977,102 +1977,102 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>7.55</v>
+        <v>4.5</v>
       </c>
       <c r="K35" t="n">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>116</v>
+        <v>30</v>
       </c>
       <c r="E36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H36" t="n">
         <v>12</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>1.91</v>
+        <v>5.03</v>
       </c>
       <c r="K36" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="L36" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2081,38 +2081,38 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F37" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>4.5</v>
+        <v>7.79</v>
       </c>
       <c r="K37" t="n">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2122,42 +2122,42 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="E38" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>4.83</v>
+        <v>7.55</v>
       </c>
       <c r="K38" t="n">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="L38" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2167,42 +2167,42 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>8.17</v>
+        <v>7.15</v>
       </c>
       <c r="K39" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="L39" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2216,38 +2216,38 @@
         </is>
       </c>
       <c r="D40" t="n">
+        <v>76</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>59</v>
+      </c>
+      <c r="G40" t="n">
+        <v>48</v>
+      </c>
+      <c r="H40" t="n">
+        <v>12</v>
+      </c>
+      <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="E40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>6</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
       <c r="J40" t="n">
-        <v>7.79</v>
+        <v>18.33</v>
       </c>
       <c r="K40" t="n">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="L40" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2257,59 +2257,59 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="E41" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F41" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="G41" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>18.33</v>
+        <v>4.79</v>
       </c>
       <c r="K41" t="n">
-        <v>220</v>
+        <v>86</v>
       </c>
       <c r="L41" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="E42" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F42" t="n">
         <v>7</v>
@@ -2318,26 +2318,26 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>7.15</v>
+        <v>1.91</v>
       </c>
       <c r="K42" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="L42" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2347,42 +2347,42 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E43" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I43" t="n">
         <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>10.26</v>
+        <v>8.15</v>
       </c>
       <c r="K43" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L43" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2392,92 +2392,92 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="E44" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>9.720000000000001</v>
+        <v>16.92</v>
       </c>
       <c r="K44" t="n">
-        <v>117</v>
+        <v>812</v>
       </c>
       <c r="L44" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="E45" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="F45" t="n">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="G45" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>16.91</v>
+        <v>8.6</v>
       </c>
       <c r="K45" t="n">
-        <v>812</v>
+        <v>103</v>
       </c>
       <c r="L45" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2486,38 +2486,38 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E46" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>8.6</v>
+        <v>10.26</v>
       </c>
       <c r="K46" t="n">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="L46" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2527,42 +2527,42 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E47" t="n">
         <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>7.56</v>
+        <v>6.81</v>
       </c>
       <c r="K47" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="L47" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2572,42 +2572,42 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="E48" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="F48" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>6.81</v>
+        <v>7.56</v>
       </c>
       <c r="K48" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="L48" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2621,38 +2621,38 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12</v>
+        <v>10.02</v>
       </c>
       <c r="E49" t="n">
         <v>6.4</v>
       </c>
       <c r="F49" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>12.88</v>
+        <v>6.44</v>
       </c>
       <c r="K49" t="n">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="L49" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2662,42 +2662,42 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.02</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>6.44</v>
+        <v>7.58</v>
       </c>
       <c r="K50" t="n">
+        <v>38</v>
+      </c>
+      <c r="L50" t="n">
         <v>39</v>
-      </c>
-      <c r="L50" t="n">
-        <v>48</v>
       </c>
       <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2707,42 +2707,42 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E51" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I51" t="n">
         <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>7.58</v>
+        <v>12.88</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="L51" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2752,42 +2752,42 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>7.58</v>
+        <v>7.5</v>
       </c>
       <c r="K52" t="n">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="L52" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2797,92 +2797,92 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="F53" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>7.5</v>
+        <v>10.33</v>
       </c>
       <c r="K53" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="L53" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E54" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="F54" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>4.5</v>
+        <v>7.59</v>
       </c>
       <c r="K54" t="n">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E55" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="F55" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H55" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I55" t="n">
         <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>10.33</v>
+        <v>4.5</v>
       </c>
       <c r="K55" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="L55" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="N55" t="inlineStr"/>
     </row>
@@ -3249,7 +3249,7 @@
         <v>13</v>
       </c>
       <c r="E63" t="n">
-        <v>36.3</v>
+        <v>33.4</v>
       </c>
       <c r="F63" t="n">
         <v>10</v>
@@ -3384,7 +3384,7 @@
         <v>65</v>
       </c>
       <c r="E66" t="n">
-        <v>58</v>
+        <v>51.6</v>
       </c>
       <c r="F66" t="n">
         <v>8</v>
@@ -3576,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3646,7 +3646,7 @@
         <v>-5</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Chanhassen (7)</t>
+          <t>Blaine (7)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -3757,7 +3757,7 @@
         <v>-5</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -4016,7 +4016,7 @@
         <v>-12</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.5</v>
+        <v>-16.8</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -4127,7 +4127,7 @@
         <v>-13</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.6</v>
+        <v>-11</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
@@ -4194,28 +4194,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E17" t="n">
         <v>-1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.3</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.5</v>
+        <v>-0.3</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -4248,11 +4248,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -4263,33 +4263,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="E19" t="n">
-        <v>99</v>
+        <v>-4.5</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -4300,29 +4300,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4</v>
+        <v>99</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Minneapolis (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -4337,29 +4337,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monaco Tropic Rush 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E21" t="n">
-        <v>99</v>
+        <v>-2.4</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Minneapolis (15)</t>
+          <t>Ramsey (4)</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -4379,24 +4379,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Monaco Tropic Rush 12oz can</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E22" t="n">
         <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Minneapolis (11)</t>
+          <t>Minneapolis (15)</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4420,20 +4420,20 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7</v>
+        <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Minneapolis (11)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -4448,19 +4448,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="E24" t="n">
-        <v>99</v>
+        <v>-5.7</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -4490,24 +4490,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 12oz can</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5</v>
+        <v>99</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -4517,34 +4517,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>-2</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>316</v>
+        <v>8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Blaine (17)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -4559,29 +4559,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>225</v>
+        <v>316</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>St. Louis Park (13)</t>
+          <t>Chanhassen (17)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -4596,29 +4596,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Plymouth (10)</t>
+          <t>St. Louis Park (13)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4642,20 +4642,20 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Plymouth (9)</t>
+          <t>Plymouth (10)</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -4670,29 +4670,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Plymouth (9)</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4716,24 +4716,24 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>St. Louis Park (5), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -4744,29 +4744,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="F32" t="n">
         <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Chanhassen (6)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -4781,29 +4781,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Bloomington (7)</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -4818,29 +4818,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -4855,33 +4855,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F35" t="n">
         <v>5</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4</v>
-      </c>
       <c r="G35" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4892,29 +4892,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="F37" t="n">
         <v>7</v>
@@ -4966,29 +4966,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" t="n">
         <v>1</v>
       </c>
-      <c r="E38" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Bloomington (7)</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -5008,24 +5008,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -5040,33 +5040,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Vadnais Heights (5)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -5077,29 +5077,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -5119,61 +5119,61 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>Top-up</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G43" t="n">
-        <v>31</v>
+        <v>944</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Minneapolis (24), Rosemount (19)</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5197,20 +5197,20 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E44" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="F44" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G44" t="n">
-        <v>944</v>
+        <v>373</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Minneapolis (24), Rosemount (19)</t>
+          <t>Blaine (13), Bloomington (4)</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5234,20 +5234,20 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G45" t="n">
-        <v>373</v>
+        <v>329</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Blaine (12), Bloomington (5)</t>
+          <t>Andover (15)</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -5262,29 +5262,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>329</v>
+        <v>220</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Andover (15)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5308,24 +5308,24 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="E47" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
-        <v>329</v>
+        <v>220</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Minnetonka (7), Bloomington (4), Vadnais Heights (4)</t>
+          <t>Minnetonka (6), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -5336,29 +5336,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E48" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>220</v>
+        <v>176</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Blaine (8)</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -5388,18 +5388,18 @@
         <v>4.5</v>
       </c>
       <c r="F49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Minneapolis (8), Stillwater (4)</t>
+          <t>Stillwater (10)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5419,20 +5419,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Blaine (8)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -5452,24 +5452,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -5484,33 +5484,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E52" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Bloomington (5)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -5521,29 +5521,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>99</v>
+        <v>2.4</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G53" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Vadnais Heights (6), Minnetonka (5)</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -5558,33 +5558,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E54" t="n">
-        <v>5.1</v>
+        <v>99</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -5595,33 +5595,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Andover (6), Vadnais Heights (4)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5632,33 +5632,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G56" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Andover (6), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -5669,33 +5669,33 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>2.5</v>
+        <v>10.7</v>
       </c>
       <c r="F57" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>St. Louis Park (9)</t>
+          <t>Blaine (10), Minnetonka (9)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D58" t="n">
+        <v>6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F58" t="n">
         <v>5</v>
       </c>
-      <c r="E58" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4</v>
-      </c>
       <c r="G58" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5743,33 +5743,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D59" t="n">
+        <v>18</v>
+      </c>
+      <c r="E59" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F59" t="n">
         <v>5</v>
       </c>
-      <c r="E59" t="n">
-        <v>99</v>
-      </c>
-      <c r="F59" t="n">
-        <v>4</v>
-      </c>
       <c r="G59" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -5780,33 +5780,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="E60" t="n">
-        <v>60.1</v>
+        <v>2.5</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G60" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>St. Louis Park (9)</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -5817,29 +5817,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>99</v>
+        <v>3.8</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -5854,33 +5854,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>11.1</v>
+        <v>99</v>
       </c>
       <c r="F62" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G62" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (6)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5891,29 +5891,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="E63" t="n">
-        <v>3.2</v>
+        <v>60.1</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5928,33 +5928,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>7.1</v>
+        <v>99</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5970,24 +5970,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Cottage Grove (7)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -6002,29 +6002,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>99</v>
+        <v>2.5</v>
       </c>
       <c r="F66" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Minneapolis (27)</t>
+          <t>Cottage Grove (7)</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -6039,29 +6039,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 4pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E67" t="n">
-        <v>11.7</v>
+        <v>99</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G67" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Cottage Grove (6)</t>
+          <t>Minneapolis (27)</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -6076,25 +6076,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F68" t="n">
         <v>5</v>
       </c>
       <c r="G68" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6113,29 +6113,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>3.3</v>
+        <v>11.7</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G69" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Cottage Grove (6)</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6150,33 +6150,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Vadnais Heights (5)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6187,29 +6187,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Vadnais Heights (5)</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E72" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="F72" t="n">
         <v>4</v>
@@ -6246,11 +6246,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -6261,19 +6261,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>99</v>
+        <v>4.5</v>
       </c>
       <c r="F73" t="n">
         <v>4</v>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -6298,33 +6298,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>4.4</v>
+        <v>99</v>
       </c>
       <c r="F74" t="n">
         <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6335,33 +6335,33 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>14.3</v>
+        <v>4.4</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -6372,29 +6372,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>4.1</v>
+        <v>14.3</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -6409,29 +6409,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F77" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Cottage Grove (11)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -6446,33 +6446,33 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G78" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Osseo (4)</t>
+          <t>Cottage Grove (11)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6483,33 +6483,33 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E79" t="n">
-        <v>2.7</v>
+        <v>6.9</v>
       </c>
       <c r="F79" t="n">
         <v>4</v>
       </c>
       <c r="G79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Osseo (4)</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -6520,29 +6520,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>99</v>
+        <v>2.7</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -6557,19 +6557,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>10</v>
       </c>
       <c r="E81" t="n">
-        <v>6.4</v>
+        <v>99</v>
       </c>
       <c r="F81" t="n">
         <v>6</v>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6606,7 +6606,7 @@
         <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>99</v>
+        <v>6.4</v>
       </c>
       <c r="F82" t="n">
         <v>6</v>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -6631,29 +6631,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E83" t="n">
-        <v>26.8</v>
+        <v>99</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -6668,19 +6668,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monaco Lemonade 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
-        <v>99</v>
+        <v>26.8</v>
       </c>
       <c r="F84" t="n">
         <v>5</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -6705,19 +6705,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Lemonade 12oz can</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F85" t="n">
         <v>5</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6751,20 +6751,20 @@
         </is>
       </c>
       <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
         <v>4</v>
       </c>
-      <c r="E86" t="n">
-        <v>99</v>
-      </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -6779,19 +6779,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monaco Purple Crush 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>32.1</v>
+        <v>99</v>
       </c>
       <c r="F87" t="n">
         <v>4</v>
@@ -6801,10 +6801,47 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
+          <t>Vadnais Heights (4)</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ramsey</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Monaco Purple Crush 12oz can</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>4</v>
+      </c>
+      <c r="G88" t="n">
+        <v>8</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>Minneapolis (4)</t>
         </is>
       </c>
-      <c r="I87" t="n">
+      <c r="I88" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -582,7 +582,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Absolut Vodkarita 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -592,42 +592,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.3</v>
-      </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>6.44</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="L4" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -637,42 +637,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J5" t="n">
-        <v>8.119999999999999</v>
+        <v>17.33</v>
       </c>
       <c r="K5" t="n">
-        <v>195</v>
+        <v>1976</v>
       </c>
       <c r="L5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
         <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>17.33</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1976</v>
+        <v>415</v>
       </c>
       <c r="L6" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N6" t="inlineStr"/>
     </row>
@@ -776,28 +776,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F8" t="n">
         <v>133</v>
       </c>
       <c r="G8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J8" t="n">
         <v>17.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1505</v>
+        <v>1609</v>
       </c>
       <c r="L8" t="n">
         <v>31</v>
@@ -807,7 +807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,38 +821,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>8.619999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="K9" t="n">
-        <v>414</v>
+        <v>124</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -862,42 +862,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>10.22</v>
+        <v>8.69</v>
       </c>
       <c r="K10" t="n">
-        <v>164</v>
+        <v>1303</v>
       </c>
       <c r="L10" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>Sunny D Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -907,42 +907,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>10.33</v>
+        <v>15.46</v>
       </c>
       <c r="K11" t="n">
-        <v>124</v>
+        <v>325</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sunny D Variety Pack 8pk 12oz can</t>
+          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -952,42 +952,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>15.46</v>
+        <v>10.22</v>
       </c>
       <c r="K12" t="n">
-        <v>325</v>
+        <v>164</v>
       </c>
       <c r="L12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>Absolut Vodkarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -997,42 +997,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F13" t="n">
-        <v>156</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>8.68</v>
+        <v>6.45</v>
       </c>
       <c r="K13" t="n">
-        <v>1302</v>
+        <v>77</v>
       </c>
       <c r="L13" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>16</v>
@@ -1077,7 +1077,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,42 +1087,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>38</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>62</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
       <c r="J15" t="n">
-        <v>8.119999999999999</v>
+        <v>18.59</v>
       </c>
       <c r="K15" t="n">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="L15" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1136,38 +1136,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
         <v>2.1</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>18.59</v>
+        <v>8.82</v>
       </c>
       <c r="K16" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1177,35 +1177,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>2.1</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>8.82</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>212</v>
+        <v>49</v>
       </c>
       <c r="L17" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -1244,20 +1244,20 @@
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>11.71</v>
+        <v>12.13</v>
       </c>
       <c r="K18" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L18" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1267,42 +1267,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G19" t="n">
         <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>8.66</v>
+        <v>7.72</v>
       </c>
       <c r="K19" t="n">
-        <v>156</v>
+        <v>371</v>
       </c>
       <c r="L19" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1312,42 +1312,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>7.17</v>
+        <v>7.02</v>
       </c>
       <c r="K20" t="n">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1357,42 +1357,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>7.72</v>
+        <v>7.17</v>
       </c>
       <c r="K21" t="n">
-        <v>371</v>
+        <v>86</v>
       </c>
       <c r="L21" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1402,42 +1402,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E22" t="n">
         <v>2.6</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>9.75</v>
+        <v>8.66</v>
       </c>
       <c r="K22" t="n">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="L22" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1447,42 +1447,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="E23" t="n">
         <v>2.8</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>7.19</v>
+        <v>8.67</v>
       </c>
       <c r="K23" t="n">
-        <v>43</v>
+        <v>468</v>
       </c>
       <c r="L23" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1492,35 +1492,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F24" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>8.67</v>
+        <v>9.75</v>
       </c>
       <c r="K24" t="n">
-        <v>468</v>
+        <v>58</v>
       </c>
       <c r="L24" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N24" t="inlineStr"/>
     </row>
@@ -1544,7 +1544,7 @@
         <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
@@ -1589,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F26" t="n">
         <v>35</v>
@@ -1617,7 +1617,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1627,42 +1627,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
         <v>3.3</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
         <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>10.48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="L27" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1672,42 +1672,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>49</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33</v>
+      </c>
+      <c r="G28" t="n">
         <v>14</v>
       </c>
-      <c r="E28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F28" t="n">
-        <v>22</v>
-      </c>
-      <c r="G28" t="n">
-        <v>9</v>
-      </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>8.800000000000001</v>
+        <v>7.67</v>
       </c>
       <c r="K28" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F29" t="n">
         <v>11</v>
@@ -1736,23 +1736,23 @@
         <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>9.720000000000001</v>
+        <v>10.48</v>
       </c>
       <c r="K29" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="L29" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1762,42 +1762,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
         <v>3.6</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>7.67</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="L30" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1807,42 +1807,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>446</v>
       </c>
       <c r="E31" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>8.039999999999999</v>
+        <v>21.95</v>
       </c>
       <c r="K31" t="n">
-        <v>48</v>
+        <v>1141</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1856,38 +1856,38 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>449</v>
+        <v>86</v>
       </c>
       <c r="E32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="G32" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="H32" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
-        <v>21.96</v>
+        <v>8.66</v>
       </c>
       <c r="K32" t="n">
-        <v>1142</v>
+        <v>415</v>
       </c>
       <c r="L32" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="E33" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H33" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>8.66</v>
+        <v>4.88</v>
       </c>
       <c r="K33" t="n">
-        <v>416</v>
+        <v>59</v>
       </c>
       <c r="L33" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="N33" t="inlineStr"/>
     </row>
@@ -1949,7 +1949,7 @@
         <v>80</v>
       </c>
       <c r="E34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F34" t="n">
         <v>70</v>
@@ -1977,102 +1977,102 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="E35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="F35" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="K35" t="n">
+        <v>45</v>
+      </c>
+      <c r="L35" t="n">
         <v>40</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>36</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>162</v>
-      </c>
-      <c r="L35" t="n">
-        <v>44</v>
       </c>
       <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="E36" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F36" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>12</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>5.03</v>
+        <v>1.91</v>
       </c>
       <c r="K36" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="L36" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2081,38 +2081,38 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>7.79</v>
+        <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="L37" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2122,42 +2122,42 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="E38" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>7.55</v>
+        <v>4.83</v>
       </c>
       <c r="K38" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="L38" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2167,42 +2167,42 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E39" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>7.15</v>
+        <v>8.17</v>
       </c>
       <c r="K39" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="L39" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2216,38 +2216,38 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F40" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>18.33</v>
+        <v>7.79</v>
       </c>
       <c r="K40" t="n">
-        <v>220</v>
+        <v>47</v>
       </c>
       <c r="L40" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2257,59 +2257,59 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="E41" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F41" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G41" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H41" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
-        <v>4.79</v>
+        <v>18.33</v>
       </c>
       <c r="K41" t="n">
-        <v>86</v>
+        <v>220</v>
       </c>
       <c r="L41" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="E42" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F42" t="n">
         <v>7</v>
@@ -2318,26 +2318,26 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1.91</v>
+        <v>7.15</v>
       </c>
       <c r="K42" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2347,42 +2347,42 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>14</v>
+      </c>
+      <c r="G43" t="n">
         <v>5</v>
       </c>
-      <c r="F43" t="n">
-        <v>16</v>
-      </c>
-      <c r="G43" t="n">
-        <v>4</v>
-      </c>
       <c r="H43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I43" t="n">
         <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>8.15</v>
+        <v>10.26</v>
       </c>
       <c r="K43" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="L43" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2392,92 +2392,92 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E44" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="F44" t="n">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>16.92</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>812</v>
+        <v>117</v>
       </c>
       <c r="L44" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="E45" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="F45" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H45" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>8.6</v>
+        <v>16.91</v>
       </c>
       <c r="K45" t="n">
-        <v>103</v>
+        <v>812</v>
       </c>
       <c r="L45" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2486,38 +2486,38 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="F46" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>10.26</v>
+        <v>8.6</v>
       </c>
       <c r="K46" t="n">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="L46" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2527,42 +2527,42 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
         <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>6.81</v>
+        <v>7.56</v>
       </c>
       <c r="K47" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="L47" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2572,42 +2572,42 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="E48" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
-        <v>7.56</v>
+        <v>6.81</v>
       </c>
       <c r="K48" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="L48" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2621,38 +2621,38 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.02</v>
+        <v>12</v>
       </c>
       <c r="E49" t="n">
         <v>6.4</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
-        <v>6.44</v>
+        <v>12.88</v>
       </c>
       <c r="K49" t="n">
-        <v>39</v>
+        <v>193</v>
       </c>
       <c r="L49" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2662,42 +2662,42 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>10.02</v>
       </c>
       <c r="E50" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>7.58</v>
+        <v>6.44</v>
       </c>
       <c r="K50" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2707,42 +2707,42 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="F51" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
         <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>12.88</v>
+        <v>7.58</v>
       </c>
       <c r="K51" t="n">
-        <v>193</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2752,42 +2752,42 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E52" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F52" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="K52" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="L52" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2797,92 +2797,92 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E53" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="F53" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>10.33</v>
+        <v>7.5</v>
       </c>
       <c r="K53" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="L53" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E54" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>7.59</v>
+        <v>4.5</v>
       </c>
       <c r="K54" t="n">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="L54" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="F55" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G55" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I55" t="n">
         <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>4.5</v>
+        <v>10.33</v>
       </c>
       <c r="K55" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="L55" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="N55" t="inlineStr"/>
     </row>
@@ -3249,7 +3249,7 @@
         <v>13</v>
       </c>
       <c r="E63" t="n">
-        <v>33.4</v>
+        <v>36.3</v>
       </c>
       <c r="F63" t="n">
         <v>10</v>
@@ -3384,7 +3384,7 @@
         <v>65</v>
       </c>
       <c r="E66" t="n">
-        <v>51.6</v>
+        <v>58</v>
       </c>
       <c r="F66" t="n">
         <v>8</v>
@@ -3576,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3646,7 +3646,7 @@
         <v>-5</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Blaine (7)</t>
+          <t>Chanhassen (7)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -3757,7 +3757,7 @@
         <v>-5</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -4016,7 +4016,7 @@
         <v>-12</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.8</v>
+        <v>-17.5</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
@@ -4127,7 +4127,7 @@
         <v>-13</v>
       </c>
       <c r="E15" t="n">
-        <v>-11</v>
+        <v>-11.6</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
@@ -4194,28 +4194,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E17" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3</v>
+        <v>-4.5</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -4248,11 +4248,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4263,33 +4263,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.5</v>
+        <v>99</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4300,29 +4300,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E20" t="n">
-        <v>99</v>
+        <v>-2.4</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -4337,29 +4337,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Monaco Tropic Rush 12oz can</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Ramsey (4)</t>
+          <t>Minneapolis (15)</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -4379,24 +4379,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monaco Tropic Rush 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E22" t="n">
         <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Minneapolis (15)</t>
+          <t>Minneapolis (11)</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4420,20 +4420,20 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="E23" t="n">
-        <v>99</v>
+        <v>-5.7</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Minneapolis (11)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -4448,19 +4448,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 12oz can</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7</v>
+        <v>99</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -4490,24 +4490,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E25" t="n">
-        <v>99</v>
+        <v>-2.5</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -4517,34 +4517,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STOCKOUT</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5</v>
+        <v>1.7</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>8</v>
+        <v>316</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Blaine (17)</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -4559,29 +4559,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>316</v>
+        <v>225</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Chanhassen (17)</t>
+          <t>St. Louis Park (13)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -4596,29 +4596,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>St. Louis Park (13)</t>
+          <t>Plymouth (10)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4642,20 +4642,20 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Plymouth (10)</t>
+          <t>Plymouth (9)</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -4670,29 +4670,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F30" t="n">
         <v>6</v>
       </c>
-      <c r="E30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9</v>
-      </c>
       <c r="G30" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Plymouth (9)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4716,24 +4716,24 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>St. Louis Park (5), Vadnais Heights (4)</t>
+          <t>Bloomington (7)</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4744,29 +4744,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F32" t="n">
         <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Chanhassen (6)</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -4781,29 +4781,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -4818,29 +4818,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F34" t="n">
         <v>4</v>
       </c>
-      <c r="E34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>6</v>
-      </c>
       <c r="G34" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -4855,33 +4855,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -4892,29 +4892,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Bloomington (7)</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="F37" t="n">
         <v>7</v>
@@ -4966,29 +4966,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -5008,24 +5008,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -5040,33 +5040,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Vadnais Heights (5)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5077,29 +5077,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="F41" t="n">
         <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -5119,61 +5119,61 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>38</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Stillwater (5)</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
         <v>2</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F42" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" t="n">
-        <v>31</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="F43" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>944</v>
+        <v>31</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Minneapolis (24), Rosemount (19)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5197,20 +5197,20 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="F44" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G44" t="n">
-        <v>373</v>
+        <v>944</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Blaine (13), Bloomington (4)</t>
+          <t>Minneapolis (24), Rosemount (19)</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5234,20 +5234,20 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E45" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Andover (15)</t>
+          <t>Blaine (12), Bloomington (5)</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -5262,29 +5262,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E46" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>220</v>
+        <v>329</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Andover (15)</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5308,24 +5308,24 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="E47" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G47" t="n">
-        <v>220</v>
+        <v>329</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Minnetonka (6), Vadnais Heights (4)</t>
+          <t>Minnetonka (7), Bloomington (4), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -5336,29 +5336,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Blaine (8)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -5388,18 +5388,18 @@
         <v>4.5</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Stillwater (10)</t>
+          <t>Minneapolis (8), Stillwater (4)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5419,20 +5419,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Blaine (8)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -5452,24 +5452,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E51" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -5484,33 +5484,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bloomington (5)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5521,29 +5521,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E53" t="n">
-        <v>2.4</v>
+        <v>99</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6), Minnetonka (5)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -5558,33 +5558,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>99</v>
+        <v>5.1</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5595,33 +5595,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G55" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Andover (6), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -5632,33 +5632,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Andover (6), Vadnais Heights (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5669,33 +5669,33 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>10.7</v>
+        <v>2.5</v>
       </c>
       <c r="F57" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (9)</t>
+          <t>St. Louis Park (9)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -5743,33 +5743,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>7.1</v>
+        <v>99</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5780,33 +5780,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="E60" t="n">
-        <v>2.5</v>
+        <v>60.1</v>
       </c>
       <c r="F60" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>St. Louis Park (9)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5817,29 +5817,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>3.8</v>
+        <v>99</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -5854,33 +5854,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>99</v>
+        <v>11.1</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G62" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -5891,29 +5891,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>60.1</v>
+        <v>3.2</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -5928,33 +5928,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E64" t="n">
-        <v>99</v>
+        <v>7.1</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -5970,24 +5970,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Cottage Grove (7)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -6002,29 +6002,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E66" t="n">
-        <v>2.5</v>
+        <v>99</v>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G66" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Cottage Grove (7)</t>
+          <t>Minneapolis (27)</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -6039,29 +6039,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
-        <v>99</v>
+        <v>11.7</v>
       </c>
       <c r="F67" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Minneapolis (27)</t>
+          <t>Cottage Grove (6)</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -6076,25 +6076,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E68" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F68" t="n">
         <v>5</v>
       </c>
       <c r="G68" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
@@ -6113,29 +6113,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 4pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>11.7</v>
+        <v>3.3</v>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Cottage Grove (6)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -6150,33 +6150,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Vadnais Heights (5)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -6187,29 +6187,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Vadnais Heights (5)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="F72" t="n">
         <v>4</v>
@@ -6246,11 +6246,11 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6261,19 +6261,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>4.5</v>
+        <v>99</v>
       </c>
       <c r="F73" t="n">
         <v>4</v>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -6298,33 +6298,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>99</v>
+        <v>4.4</v>
       </c>
       <c r="F74" t="n">
         <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -6335,33 +6335,33 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F75" t="n">
         <v>6</v>
       </c>
-      <c r="E75" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F75" t="n">
-        <v>4</v>
-      </c>
       <c r="G75" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6372,29 +6372,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>14.3</v>
+        <v>4.1</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -6409,29 +6409,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D77" t="n">
+        <v>17</v>
+      </c>
+      <c r="E77" t="n">
         <v>4</v>
       </c>
-      <c r="E77" t="n">
-        <v>4.1</v>
-      </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G77" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Cottage Grove (11)</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -6446,33 +6446,33 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" t="n">
         <v>4</v>
       </c>
-      <c r="F78" t="n">
-        <v>11</v>
-      </c>
       <c r="G78" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Cottage Grove (11)</t>
+          <t>Osseo (4)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -6483,33 +6483,33 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="F79" t="n">
         <v>4</v>
       </c>
       <c r="G79" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Osseo (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6520,29 +6520,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E80" t="n">
-        <v>2.7</v>
+        <v>99</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G80" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -6557,19 +6557,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>10</v>
       </c>
       <c r="E81" t="n">
-        <v>99</v>
+        <v>6.4</v>
       </c>
       <c r="F81" t="n">
         <v>6</v>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6606,7 +6606,7 @@
         <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>6.4</v>
+        <v>99</v>
       </c>
       <c r="F82" t="n">
         <v>6</v>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -6631,29 +6631,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>99</v>
+        <v>26.8</v>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -6668,19 +6668,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Lemonade 12oz can</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E84" t="n">
-        <v>26.8</v>
+        <v>99</v>
       </c>
       <c r="F84" t="n">
         <v>5</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -6705,19 +6705,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monaco Lemonade 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F85" t="n">
         <v>5</v>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6751,20 +6751,20 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
+        <v>99</v>
+      </c>
+      <c r="F86" t="n">
         <v>4</v>
       </c>
-      <c r="F86" t="n">
-        <v>5</v>
-      </c>
       <c r="G86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -6779,19 +6779,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>99</v>
+        <v>32.1</v>
       </c>
       <c r="F87" t="n">
         <v>4</v>
@@ -6801,47 +6801,10 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Monaco Purple Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F88" t="n">
-        <v>4</v>
-      </c>
-      <c r="G88" t="n">
-        <v>8</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -942,7 +943,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
+          <t>Absolut Vodkarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -956,38 +957,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>1.9</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>10.22</v>
+        <v>6.45</v>
       </c>
       <c r="K12" t="n">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Absolut Vodkarita 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -997,42 +998,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H13" t="n">
         <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>6.45</v>
+        <v>18.59</v>
       </c>
       <c r="K13" t="n">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="L13" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1042,42 +1043,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>10.22</v>
+        <v>8.82</v>
       </c>
       <c r="K14" t="n">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,42 +1088,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>2.1</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>18.59</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>223</v>
+        <v>49</v>
       </c>
       <c r="L15" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1132,42 +1133,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>8.82</v>
+        <v>12.13</v>
       </c>
       <c r="K16" t="n">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="L16" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1177,32 +1178,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>43</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>54</v>
+      </c>
+      <c r="G17" t="n">
         <v>4</v>
       </c>
-      <c r="E17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>8.119999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="K17" t="n">
-        <v>49</v>
+        <v>371</v>
       </c>
       <c r="L17" t="n">
         <v>41</v>
@@ -1212,7 +1213,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1226,38 +1227,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>12.13</v>
+        <v>7.02</v>
       </c>
       <c r="K18" t="n">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="L18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1267,42 +1268,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>86</v>
+      </c>
+      <c r="L19" t="n">
         <v>43</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>54</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I19" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="K19" t="n">
-        <v>371</v>
-      </c>
-      <c r="L19" t="n">
-        <v>41</v>
       </c>
       <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1312,42 +1313,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>7.02</v>
+        <v>8.66</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="L20" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1357,42 +1358,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>73</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>72</v>
+      </c>
+      <c r="G21" t="n">
+        <v>17</v>
+      </c>
+      <c r="H21" t="n">
+        <v>54</v>
+      </c>
+      <c r="I21" t="n">
         <v>9</v>
       </c>
-      <c r="E21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>11</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>12</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
       <c r="J21" t="n">
-        <v>7.17</v>
+        <v>8.67</v>
       </c>
       <c r="K21" t="n">
-        <v>86</v>
+        <v>468</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1402,42 +1403,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>8.66</v>
+        <v>9.75</v>
       </c>
       <c r="K22" t="n">
-        <v>156</v>
+        <v>58</v>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Two Chicks New Fashioned 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1447,42 +1448,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="F23" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>8.67</v>
+        <v>7.84</v>
       </c>
       <c r="K23" t="n">
-        <v>468</v>
+        <v>141</v>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1496,28 +1497,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>9.75</v>
       </c>
       <c r="K24" t="n">
-        <v>58</v>
+        <v>292</v>
       </c>
       <c r="L24" t="n">
         <v>35</v>
@@ -1527,7 +1528,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Two Chicks New Fashioned 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1537,42 +1538,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>7.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1586,38 +1587,38 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>9.75</v>
+        <v>7.67</v>
       </c>
       <c r="K26" t="n">
-        <v>292</v>
+        <v>138</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1627,42 +1628,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1672,42 +1673,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>446</v>
       </c>
       <c r="E28" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="F28" t="n">
+        <v>171</v>
+      </c>
+      <c r="G28" t="n">
+        <v>119</v>
+      </c>
+      <c r="H28" t="n">
+        <v>52</v>
+      </c>
+      <c r="I28" t="n">
+        <v>26</v>
+      </c>
+      <c r="J28" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1141</v>
+      </c>
+      <c r="L28" t="n">
         <v>33</v>
-      </c>
-      <c r="G28" t="n">
-        <v>14</v>
-      </c>
-      <c r="H28" t="n">
-        <v>18</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="K28" t="n">
-        <v>138</v>
-      </c>
-      <c r="L28" t="n">
-        <v>41</v>
       </c>
       <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1717,42 +1718,42 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="E29" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>10.48</v>
+        <v>8.66</v>
       </c>
       <c r="K29" t="n">
-        <v>126</v>
+        <v>415</v>
       </c>
       <c r="L29" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1762,42 +1763,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>28</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>18</v>
+      </c>
+      <c r="G30" t="n">
         <v>6</v>
       </c>
-      <c r="E30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>8.039999999999999</v>
+        <v>4.88</v>
       </c>
       <c r="K30" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1811,38 +1812,38 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>446</v>
+        <v>80</v>
       </c>
       <c r="E31" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="F31" t="n">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="G31" t="n">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="H31" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>21.95</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>1141</v>
+        <v>313</v>
       </c>
       <c r="L31" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1852,92 +1853,92 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>8.66</v>
+        <v>7.55</v>
       </c>
       <c r="K32" t="n">
-        <v>415</v>
+        <v>45</v>
       </c>
       <c r="L32" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>12</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>4.88</v>
+        <v>1.91</v>
       </c>
       <c r="K33" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="L33" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1946,38 +1947,38 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="F34" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G34" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>36</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>8.699999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="K34" t="n">
-        <v>313</v>
+        <v>162</v>
       </c>
       <c r="L34" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1987,92 +1988,92 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="E35" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>7.55</v>
+        <v>4.83</v>
       </c>
       <c r="K35" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E36" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
         <v>12</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>1.91</v>
+        <v>8.17</v>
       </c>
       <c r="K36" t="n">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="L36" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2081,38 +2082,38 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F37" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>4.5</v>
+        <v>7.79</v>
       </c>
       <c r="K37" t="n">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="L37" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2122,42 +2123,42 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E38" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H38" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>4.83</v>
+        <v>18.33</v>
       </c>
       <c r="K38" t="n">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="L38" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2167,42 +2168,42 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>8.17</v>
+        <v>7.15</v>
       </c>
       <c r="K39" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="L39" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2212,42 +2213,42 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E40" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>7.79</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="L40" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2261,43 +2262,43 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="E41" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="F41" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="G41" t="n">
+        <v>37</v>
+      </c>
+      <c r="H41" t="n">
         <v>48</v>
       </c>
-      <c r="H41" t="n">
-        <v>12</v>
-      </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>18.33</v>
+        <v>16.91</v>
       </c>
       <c r="K41" t="n">
-        <v>220</v>
+        <v>812</v>
       </c>
       <c r="L41" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2306,38 +2307,38 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E42" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>7.15</v>
+        <v>8.6</v>
       </c>
       <c r="K42" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="L42" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2347,42 +2348,42 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="E43" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>10.26</v>
+        <v>7.56</v>
       </c>
       <c r="K43" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="L43" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2392,42 +2393,42 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E44" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>9.720000000000001</v>
+        <v>6.81</v>
       </c>
       <c r="K44" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L44" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2437,47 +2438,47 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="F45" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="G45" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J45" t="n">
-        <v>16.91</v>
+        <v>12.88</v>
       </c>
       <c r="K45" t="n">
-        <v>812</v>
+        <v>193</v>
       </c>
       <c r="L45" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2486,38 +2487,38 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>10.02</v>
       </c>
       <c r="E46" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="F46" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>8.6</v>
+        <v>6.44</v>
       </c>
       <c r="K46" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="L46" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2531,28 +2532,28 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J47" t="n">
-        <v>7.56</v>
+        <v>7.58</v>
       </c>
       <c r="K47" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
         <v>39</v>
@@ -2562,7 +2563,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2576,38 +2577,38 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E48" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>6.81</v>
+        <v>7.58</v>
       </c>
       <c r="K48" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="L48" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2621,83 +2622,83 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E49" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="F49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>12.88</v>
+        <v>7.5</v>
       </c>
       <c r="K49" t="n">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="L49" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.02</v>
+        <v>33</v>
       </c>
       <c r="E50" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>6.44</v>
+        <v>4.5</v>
       </c>
       <c r="K50" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="L50" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2707,87 +2708,87 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>7.58</v>
+        <v>10.33</v>
       </c>
       <c r="K51" t="n">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="L51" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="F52" t="n">
         <v>7</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>7.58</v>
+        <v>1.87</v>
       </c>
       <c r="K52" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2797,47 +2798,47 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>8.4</v>
+        <v>15.4</v>
       </c>
       <c r="F53" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J53" t="n">
-        <v>7.5</v>
+        <v>15.55</v>
       </c>
       <c r="K53" t="n">
-        <v>135</v>
+        <v>373</v>
       </c>
       <c r="L53" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Saint Spritz Sicily 4pk 355ml</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2846,38 +2847,38 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E54" t="n">
-        <v>8.6</v>
+        <v>29.8</v>
       </c>
       <c r="F54" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I54" t="n">
         <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>4.5</v>
+        <v>10.33</v>
       </c>
       <c r="K54" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2891,128 +2892,123 @@
         </is>
       </c>
       <c r="D55" t="n">
+        <v>13</v>
+      </c>
+      <c r="E55" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>7</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
         <v>6</v>
       </c>
-      <c r="E55" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F55" t="n">
-        <v>12</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>12</v>
-      </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>10.33</v>
+        <v>7.8</v>
       </c>
       <c r="K55" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="L55" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="E56" t="n">
-        <v>10.4</v>
+        <v>32.1</v>
       </c>
       <c r="F56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
         <v>6</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1.87</v>
+        <v>7.8</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="L56" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
+          <t>Samichlaus Classic</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>15.4</v>
+        <v>32.1</v>
       </c>
       <c r="F57" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
-        <v>15.55</v>
+        <v>15.38</v>
       </c>
       <c r="K57" t="n">
-        <v>373</v>
+        <v>31</v>
       </c>
       <c r="L57" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jack &amp; Coke Zero 4pk 12oz can</t>
+          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3026,13 +3022,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E58" t="n">
-        <v>27.6</v>
+        <v>36.3</v>
       </c>
       <c r="F58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -3044,20 +3040,20 @@
         <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>7.86</v>
+        <v>7.8</v>
       </c>
       <c r="K58" t="n">
         <v>94</v>
       </c>
       <c r="L58" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Saint Spritz Sicily 4pk 355ml</t>
+          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3067,42 +3063,42 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E59" t="n">
-        <v>29.8</v>
+        <v>42.2</v>
       </c>
       <c r="F59" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>10.33</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="L59" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3112,20 +3108,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="E60" t="n">
-        <v>29.8</v>
+        <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H60" t="n">
         <v>6</v>
@@ -3134,436 +3130,131 @@
         <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>7.8</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="L60" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
+          <t>Estrella Daura IPA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17</v>
-      </c>
-      <c r="E61" t="n">
-        <v>32.1</v>
+        <v>-1</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="K61" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="L61" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Samichlaus Classic</t>
+          <t>Insight Control Alt Beer 4pk 16oz can</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Craft</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Insight Brewing Company (D)</t>
         </is>
       </c>
       <c r="D62" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6</v>
+      </c>
+      <c r="I62" t="n">
         <v>1</v>
       </c>
-      <c r="E62" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F62" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" t="n">
-        <v>2</v>
-      </c>
       <c r="J62" t="n">
-        <v>15.38</v>
+        <v>11.53</v>
       </c>
       <c r="K62" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="L62" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
+          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13</v>
-      </c>
-      <c r="E63" t="n">
-        <v>36.3</v>
+        <v>-4</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K63" t="n">
         <v>2</v>
       </c>
-      <c r="J63" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K63" t="n">
-        <v>94</v>
-      </c>
       <c r="L63" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="N63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>21</v>
-      </c>
-      <c r="E64" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="F64" t="n">
-        <v>26</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>24</v>
-      </c>
-      <c r="I64" t="n">
-        <v>4</v>
-      </c>
-      <c r="J64" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="K64" t="n">
-        <v>195</v>
-      </c>
-      <c r="L64" t="n">
-        <v>35</v>
-      </c>
-      <c r="N64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Jack &amp; Coke 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>33</v>
-      </c>
-      <c r="E65" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="F65" t="n">
-        <v>7</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>6</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="K65" t="n">
-        <v>51</v>
-      </c>
-      <c r="L65" t="n">
-        <v>39</v>
-      </c>
-      <c r="N65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>65</v>
-      </c>
-      <c r="E66" t="n">
-        <v>58</v>
-      </c>
-      <c r="F66" t="n">
-        <v>8</v>
-      </c>
-      <c r="G66" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" t="n">
-        <v>6</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="K66" t="n">
-        <v>59</v>
-      </c>
-      <c r="L66" t="n">
-        <v>48</v>
-      </c>
-      <c r="N66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Ketel One Spritz Cucumber &amp; Mint 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>8</v>
-      </c>
-      <c r="E67" t="n">
-        <v>128.6</v>
-      </c>
-      <c r="F67" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>5</v>
-      </c>
-      <c r="I67" t="n">
-        <v>5</v>
-      </c>
-      <c r="J67" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="K67" t="n">
-        <v>36</v>
-      </c>
-      <c r="L67" t="n">
-        <v>52</v>
-      </c>
-      <c r="N67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Estrella Daura IPA</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Import</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K68" t="n">
-        <v>8</v>
-      </c>
-      <c r="L68" t="n">
-        <v>29</v>
-      </c>
-      <c r="N68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Insight Control Alt Beer 4pk 16oz can</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Craft</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Insight Brewing Company (D)</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F69" t="n">
-        <v>6</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>6</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" t="n">
-        <v>11.53</v>
-      </c>
-      <c r="K69" t="n">
-        <v>69</v>
-      </c>
-      <c r="L69" t="n">
-        <v>32</v>
-      </c>
-      <c r="N69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Single Serve</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L70" t="n">
-        <v>34</v>
-      </c>
-      <c r="N70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3576,6 +3267,402 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Chain OH (TOH)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>WOS</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Gross Need</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Buy Units</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Buy Cases</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Net Buy $</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GM %</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Discount %</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Deal Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jack &amp; Coke 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="K2" t="n">
+        <v>51</v>
+      </c>
+      <c r="L2" t="n">
+        <v>39</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jack &amp; Coke Zero 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="K3" t="n">
+        <v>94</v>
+      </c>
+      <c r="L3" t="n">
+        <v>44</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ketel One Spritz Cucumber &amp; Mint 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="K4" t="n">
+        <v>36</v>
+      </c>
+      <c r="L4" t="n">
+        <v>52</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="K5" t="n">
+        <v>164</v>
+      </c>
+      <c r="L5" t="n">
+        <v>49</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="K6" t="n">
+        <v>126</v>
+      </c>
+      <c r="L6" t="n">
+        <v>56</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="K7" t="n">
+        <v>164</v>
+      </c>
+      <c r="L7" t="n">
+        <v>49</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="K8" t="n">
+        <v>82</v>
+      </c>
+      <c r="L8" t="n">
+        <v>49</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +490,11 @@
           <t>Deal Terms</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Buy Month</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,6 +540,11 @@
         <v>37</v>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,6 +590,7 @@
         <v>41</v>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -624,6 +636,7 @@
         <v>29</v>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -669,6 +682,11 @@
         <v>31</v>
       </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -714,6 +732,11 @@
         <v>37</v>
       </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -759,6 +782,7 @@
         <v>42</v>
       </c>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -804,6 +828,11 @@
         <v>31</v>
       </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -849,6 +878,7 @@
         <v>31</v>
       </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -894,6 +924,11 @@
         <v>37</v>
       </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -939,6 +974,7 @@
         <v>36</v>
       </c>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -984,6 +1020,7 @@
         <v>48</v>
       </c>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1029,11 +1066,16 @@
         <v>38</v>
       </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1043,42 +1085,43 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>2.1</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>8.82</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>212</v>
+        <v>49</v>
       </c>
       <c r="L14" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1088,42 +1131,43 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>8.119999999999999</v>
+        <v>12.13</v>
       </c>
       <c r="K15" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="L15" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1137,38 +1181,39 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="F16" t="n">
+        <v>54</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
         <v>8</v>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
       <c r="J16" t="n">
-        <v>12.13</v>
+        <v>7.72</v>
       </c>
       <c r="K16" t="n">
-        <v>109</v>
+        <v>371</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1182,38 +1227,39 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>2.4</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>7.72</v>
+        <v>7.02</v>
       </c>
       <c r="K17" t="n">
-        <v>371</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1223,42 +1269,43 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>7.02</v>
+        <v>7.17</v>
       </c>
       <c r="K18" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="L18" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1268,42 +1315,43 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>7.17</v>
+        <v>9.75</v>
       </c>
       <c r="K19" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="L19" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Two Chicks New Fashioned 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1313,20 +1361,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>18</v>
@@ -1335,20 +1383,21 @@
         <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>8.66</v>
+        <v>7.84</v>
       </c>
       <c r="K20" t="n">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1358,42 +1407,43 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F21" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>8.67</v>
+        <v>9.75</v>
       </c>
       <c r="K21" t="n">
-        <v>468</v>
+        <v>292</v>
       </c>
       <c r="L21" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1407,38 +1457,39 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="E22" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>9.75</v>
+        <v>7.67</v>
       </c>
       <c r="K22" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="L22" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Two Chicks New Fashioned 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1448,42 +1499,43 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>7.84</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1497,38 +1549,39 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
         <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>9.75</v>
+        <v>4.88</v>
       </c>
       <c r="K24" t="n">
-        <v>292</v>
+        <v>59</v>
       </c>
       <c r="L24" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1538,132 +1591,135 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>8.800000000000001</v>
+        <v>7.55</v>
       </c>
       <c r="K25" t="n">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="E26" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>7.67</v>
+        <v>1.91</v>
       </c>
       <c r="K26" t="n">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>8.039999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="L27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1673,42 +1729,43 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>446</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="F28" t="n">
-        <v>171</v>
+        <v>25</v>
       </c>
       <c r="G28" t="n">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>21.95</v>
+        <v>4.83</v>
       </c>
       <c r="K28" t="n">
-        <v>1141</v>
+        <v>87</v>
       </c>
       <c r="L28" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1718,42 +1775,43 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="n">
-        <v>63</v>
-      </c>
-      <c r="G29" t="n">
-        <v>17</v>
-      </c>
       <c r="H29" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>8.66</v>
+        <v>8.17</v>
       </c>
       <c r="K29" t="n">
-        <v>415</v>
+        <v>98</v>
       </c>
       <c r="L29" t="n">
         <v>37</v>
       </c>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1763,42 +1821,43 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>6</v>
       </c>
-      <c r="H30" t="n">
-        <v>12</v>
-      </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>4.88</v>
+        <v>7.79</v>
       </c>
       <c r="K30" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L30" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1812,38 +1871,43 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E31" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="F31" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G31" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H31" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>8.699999999999999</v>
+        <v>18.33</v>
       </c>
       <c r="K31" t="n">
-        <v>313</v>
+        <v>220</v>
       </c>
       <c r="L31" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1853,20 +1917,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>6</v>
@@ -1875,40 +1939,41 @@
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>7.55</v>
+        <v>7.15</v>
       </c>
       <c r="K32" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1917,28 +1982,29 @@
         <v>12</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>1.91</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="L33" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1947,83 +2013,89 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="E34" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H34" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>4.5</v>
+        <v>16.91</v>
       </c>
       <c r="K34" t="n">
-        <v>162</v>
+        <v>812</v>
       </c>
       <c r="L34" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="F35" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>4.83</v>
+        <v>8.6</v>
       </c>
       <c r="K35" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L35" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2033,42 +2105,43 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>8.17</v>
+        <v>7.56</v>
       </c>
       <c r="K36" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="L36" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2078,42 +2151,43 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E37" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>7.79</v>
+        <v>6.81</v>
       </c>
       <c r="K37" t="n">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="L37" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2123,42 +2197,43 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="F38" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>18.33</v>
+        <v>12.88</v>
       </c>
       <c r="K38" t="n">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="L38" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2172,13 +2247,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>10.02</v>
       </c>
       <c r="E39" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2190,20 +2265,21 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>7.15</v>
+        <v>6.44</v>
       </c>
       <c r="K39" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L39" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2213,42 +2289,43 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>9.720000000000001</v>
+        <v>7.58</v>
       </c>
       <c r="K40" t="n">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="L40" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2258,47 +2335,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="E41" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="F41" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>16.91</v>
+        <v>7.58</v>
       </c>
       <c r="K41" t="n">
-        <v>812</v>
+        <v>45</v>
       </c>
       <c r="L41" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2307,83 +2385,85 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E42" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="F42" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="K42" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L42" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E43" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>7.56</v>
+        <v>4.5</v>
       </c>
       <c r="K43" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="L43" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2393,87 +2473,89 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D44" t="n">
+        <v>6</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="K44" t="n">
+        <v>124</v>
+      </c>
+      <c r="L44" t="n">
         <v>31</v>
       </c>
-      <c r="E44" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F44" t="n">
-        <v>16</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>18</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="K44" t="n">
-        <v>123</v>
-      </c>
-      <c r="L44" t="n">
-        <v>48</v>
-      </c>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>6.4</v>
+        <v>10.4</v>
       </c>
       <c r="F45" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H45" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>12.88</v>
+        <v>1.87</v>
       </c>
       <c r="K45" t="n">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
         <v>46</v>
       </c>
       <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2483,42 +2565,43 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.02</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>6.4</v>
+        <v>15.4</v>
       </c>
       <c r="F46" t="n">
+        <v>24</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>24</v>
+      </c>
+      <c r="I46" t="n">
         <v>8</v>
       </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>6</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1</v>
-      </c>
       <c r="J46" t="n">
-        <v>6.44</v>
+        <v>15.55</v>
       </c>
       <c r="K46" t="n">
-        <v>39</v>
+        <v>373</v>
       </c>
       <c r="L46" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Saint Spritz Sicily 4pk 355ml</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2528,42 +2611,43 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
-        <v>6.9</v>
+        <v>29.8</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>7.58</v>
+        <v>10.33</v>
       </c>
       <c r="K47" t="n">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="L47" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2573,14 +2657,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E48" t="n">
-        <v>8</v>
+        <v>29.8</v>
       </c>
       <c r="F48" t="n">
         <v>7</v>
@@ -2595,20 +2679,21 @@
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>7.58</v>
+        <v>7.8</v>
       </c>
       <c r="K48" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L48" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2618,87 +2703,84 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E49" t="n">
-        <v>8.4</v>
+        <v>32.1</v>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="K49" t="n">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Samichlaus Classic</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Single Serve</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>8.6</v>
+        <v>32.1</v>
       </c>
       <c r="F50" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>4.5</v>
+        <v>15.38</v>
       </c>
       <c r="K50" t="n">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2712,13 +2794,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E51" t="n">
-        <v>8.6</v>
+        <v>36.3</v>
       </c>
       <c r="F51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2730,65 +2812,67 @@
         <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>10.33</v>
+        <v>7.8</v>
       </c>
       <c r="K51" t="n">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="L51" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="E52" t="n">
-        <v>10.4</v>
+        <v>42.2</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
-        <v>1.87</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="L52" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2802,103 +2886,94 @@
         </is>
       </c>
       <c r="D53" t="n">
+        <v>65</v>
+      </c>
+      <c r="E53" t="n">
+        <v>58</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" t="n">
         <v>6</v>
       </c>
-      <c r="E53" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F53" t="n">
-        <v>24</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>24</v>
-      </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>15.55</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>373</v>
+        <v>59</v>
       </c>
       <c r="L53" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Saint Spritz Sicily 4pk 355ml</t>
+          <t>Estrella Daura IPA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>19</v>
-      </c>
-      <c r="E54" t="n">
-        <v>29.8</v>
+        <v>-1</v>
       </c>
       <c r="F54" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>10.33</v>
+        <v>8.5</v>
       </c>
       <c r="K54" t="n">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="L54" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
+          <t>Insight Control Alt Beer 4pk 16oz can</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Craft</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Insight Brewing Company (D)</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
-      </c>
-      <c r="E55" t="n">
-        <v>29.8</v>
+        <v>-5</v>
       </c>
       <c r="F55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2910,351 +2985,54 @@
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>7.8</v>
+        <v>11.53</v>
       </c>
       <c r="K55" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="L55" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
+          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
-      </c>
-      <c r="E56" t="n">
-        <v>32.1</v>
+        <v>-4</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="K56" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="N56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Samichlaus Classic</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Import</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="K57" t="n">
-        <v>31</v>
-      </c>
-      <c r="L57" t="n">
-        <v>27</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>13</v>
-      </c>
-      <c r="E58" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="F58" t="n">
-        <v>10</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>12</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="K58" t="n">
-        <v>94</v>
-      </c>
-      <c r="L58" t="n">
-        <v>43</v>
-      </c>
-      <c r="N58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>21</v>
-      </c>
-      <c r="E59" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="F59" t="n">
-        <v>26</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>24</v>
-      </c>
-      <c r="I59" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" t="n">
-        <v>8.130000000000001</v>
-      </c>
-      <c r="K59" t="n">
-        <v>195</v>
-      </c>
-      <c r="L59" t="n">
-        <v>35</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>65</v>
-      </c>
-      <c r="E60" t="n">
-        <v>58</v>
-      </c>
-      <c r="F60" t="n">
-        <v>8</v>
-      </c>
-      <c r="G60" t="n">
-        <v>4</v>
-      </c>
-      <c r="H60" t="n">
-        <v>6</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="K60" t="n">
-        <v>59</v>
-      </c>
-      <c r="L60" t="n">
-        <v>48</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Estrella Daura IPA</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Import</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K61" t="n">
-        <v>8</v>
-      </c>
-      <c r="L61" t="n">
-        <v>29</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Insight Control Alt Beer 4pk 16oz can</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Craft</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Insight Brewing Company (D)</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>-5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>6</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>6</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>11.53</v>
-      </c>
-      <c r="K62" t="n">
-        <v>69</v>
-      </c>
-      <c r="L62" t="n">
-        <v>32</v>
-      </c>
-      <c r="N62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Single Serve</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" t="n">
-        <v>34</v>
-      </c>
-      <c r="N63" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3663,6 +3441,447 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Chain OH (TOH)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>WOS</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Gross Need</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Buy Units</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Buy Cases</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Net Buy $</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GM %</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Discount %</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Deal Terms</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Buy Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>86</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>63</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="K2" t="n">
+        <v>415</v>
+      </c>
+      <c r="L2" t="n">
+        <v>37</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>High Noon Lemon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="K3" t="n">
+        <v>156</v>
+      </c>
+      <c r="L3" t="n">
+        <v>37</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>High Noon Lime 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70</v>
+      </c>
+      <c r="G4" t="n">
+        <v>37</v>
+      </c>
+      <c r="H4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>313</v>
+      </c>
+      <c r="L4" t="n">
+        <v>37</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>High Noon Mango 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>106</v>
+      </c>
+      <c r="L5" t="n">
+        <v>36</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>High Noon Peach 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>73</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>72</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="K6" t="n">
+        <v>468</v>
+      </c>
+      <c r="L6" t="n">
+        <v>37</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>446</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>171</v>
+      </c>
+      <c r="G7" t="n">
+        <v>119</v>
+      </c>
+      <c r="H7" t="n">
+        <v>52</v>
+      </c>
+      <c r="I7" t="n">
+        <v>26</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1141</v>
+      </c>
+      <c r="L7" t="n">
+        <v>33</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>High Noon Watermelon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="K8" t="n">
+        <v>212</v>
+      </c>
+      <c r="L8" t="n">
+        <v>36</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Being Removed" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Buy-Month Wait" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
@@ -531,10 +531,10 @@
         <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>8.69</v>
+        <v>8.73</v>
       </c>
       <c r="K2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L2" t="n">
         <v>37</v>
@@ -595,7 +595,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -605,43 +605,47 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J4" t="n">
-        <v>8.119999999999999</v>
+        <v>17.17</v>
       </c>
       <c r="K4" t="n">
-        <v>195</v>
+        <v>1957</v>
       </c>
       <c r="L4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>Absolut Vodkarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -651,47 +655,43 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>17.33</v>
+        <v>6.45</v>
       </c>
       <c r="K5" t="n">
-        <v>1976</v>
+        <v>77</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -705,43 +705,39 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>8.640000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>124</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -751,43 +747,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
-        <v>13.45</v>
+        <v>8.69</v>
       </c>
       <c r="K7" t="n">
-        <v>161</v>
+        <v>1303</v>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -797,47 +797,43 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="F8" t="n">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="I8" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>17.3</v>
+        <v>15.46</v>
       </c>
       <c r="K8" t="n">
-        <v>1609</v>
+        <v>325</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -851,39 +847,43 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J9" t="n">
-        <v>10.33</v>
+        <v>17.13</v>
       </c>
       <c r="K9" t="n">
-        <v>124</v>
+        <v>1593</v>
       </c>
       <c r="L9" t="n">
         <v>31</v>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>Two Chicks Vodka Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -893,47 +893,43 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F10" t="n">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>8.69</v>
+        <v>13.53</v>
       </c>
       <c r="K10" t="n">
-        <v>1303</v>
+        <v>162</v>
       </c>
       <c r="L10" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunny D Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -947,31 +943,31 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>29</v>
+      </c>
+      <c r="G11" t="n">
         <v>6</v>
       </c>
-      <c r="E11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F11" t="n">
-        <v>21</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>15.46</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>325</v>
+        <v>195</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -979,7 +975,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Absolut Vodkarita 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -989,35 +985,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9</v>
-      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>6.45</v>
+        <v>6.98</v>
       </c>
       <c r="K12" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1025,7 +1021,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1035,47 +1031,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>2.1</v>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>18.59</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>223</v>
+        <v>49</v>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1085,35 +1077,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>8.119999999999999</v>
+        <v>12.13</v>
       </c>
       <c r="K14" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="L14" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1121,7 +1113,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1135,31 +1127,31 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F15" t="n">
+        <v>54</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
         <v>8</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>9</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
       <c r="J15" t="n">
-        <v>12.13</v>
+        <v>7.72</v>
       </c>
       <c r="K15" t="n">
-        <v>109</v>
+        <v>371</v>
       </c>
       <c r="L15" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1167,7 +1159,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1177,43 +1169,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
+        <v>62</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8</v>
-      </c>
       <c r="J16" t="n">
-        <v>7.72</v>
+        <v>18.53</v>
       </c>
       <c r="K16" t="n">
-        <v>371</v>
+        <v>222</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1227,13 +1223,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1245,13 +1241,13 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>7.02</v>
+        <v>9.75</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="L17" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1259,7 +1255,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Two Chicks New Fashioned 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1269,35 +1265,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>7.17</v>
+        <v>7.84</v>
       </c>
       <c r="K18" t="n">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="L18" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1305,7 +1301,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1319,31 +1315,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>9.75</v>
+        <v>7.67</v>
       </c>
       <c r="K19" t="n">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="L19" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1351,7 +1347,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Two Chicks New Fashioned 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1368,28 +1364,28 @@
         <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>7.84</v>
+        <v>9.75</v>
       </c>
       <c r="K20" t="n">
-        <v>141</v>
+        <v>292</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1397,7 +1393,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1411,31 +1407,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>9.75</v>
+        <v>4.88</v>
       </c>
       <c r="K21" t="n">
-        <v>292</v>
+        <v>59</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1443,7 +1439,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1453,35 +1449,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>7.67</v>
+        <v>7.17</v>
       </c>
       <c r="K22" t="n">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="L22" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1489,7 +1485,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1499,20 +1495,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="E23" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
         <v>6</v>
@@ -1521,13 +1517,13 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>8.039999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="K23" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L23" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1535,45 +1531,45 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>12</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>4.88</v>
+        <v>1.91</v>
       </c>
       <c r="K24" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="L24" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1581,45 +1577,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
         <v>4.4</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>7.55</v>
+        <v>4.5</v>
       </c>
       <c r="K25" t="n">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1627,45 +1623,45 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>1.91</v>
+        <v>8.17</v>
       </c>
       <c r="K26" t="n">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="L26" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1673,45 +1669,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>7.15</v>
       </c>
       <c r="K27" t="n">
-        <v>162</v>
+        <v>43</v>
       </c>
       <c r="L27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1719,7 +1715,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1729,43 +1725,47 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="E28" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H28" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>4.83</v>
+        <v>18.33</v>
       </c>
       <c r="K28" t="n">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="L28" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1775,43 +1775,47 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="E29" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
+        <v>84</v>
+      </c>
+      <c r="G29" t="n">
+        <v>37</v>
+      </c>
+      <c r="H29" t="n">
+        <v>48</v>
+      </c>
+      <c r="I29" t="n">
         <v>16</v>
       </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>12</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
       <c r="J29" t="n">
-        <v>8.17</v>
+        <v>16.9</v>
       </c>
       <c r="K29" t="n">
-        <v>98</v>
+        <v>811</v>
       </c>
       <c r="L29" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1821,17 +1825,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="n">
         <v>4</v>
-      </c>
-      <c r="E30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1843,13 +1847,13 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>7.79</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L30" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1857,7 +1861,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1867,47 +1871,43 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="F31" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>18.33</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="L31" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>9.02</v>
       </c>
       <c r="E32" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>7.15</v>
+        <v>6.44</v>
       </c>
       <c r="K32" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L32" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -1953,7 +1953,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1967,31 +1967,31 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>9.720000000000001</v>
+        <v>12.88</v>
       </c>
       <c r="K33" t="n">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="L33" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2013,38 +2013,34 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F34" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>16.91</v>
+        <v>7.79</v>
       </c>
       <c r="K34" t="n">
-        <v>812</v>
+        <v>47</v>
       </c>
       <c r="L34" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2063,10 +2059,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="F35" t="n">
         <v>19</v>
@@ -2095,7 +2091,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2105,35 +2101,35 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>7.56</v>
+        <v>6.81</v>
       </c>
       <c r="K36" t="n">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="L36" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2141,7 +2137,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2155,31 +2151,31 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E37" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>6.81</v>
+        <v>5.41</v>
       </c>
       <c r="K37" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="L37" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -2187,7 +2183,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2197,35 +2193,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E38" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>12.88</v>
+        <v>7.56</v>
       </c>
       <c r="K38" t="n">
-        <v>193</v>
+        <v>45</v>
       </c>
       <c r="L38" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -2233,7 +2229,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2243,17 +2239,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.02</v>
+        <v>30</v>
       </c>
       <c r="E39" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2265,13 +2261,13 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>6.44</v>
+        <v>7.58</v>
       </c>
       <c r="K39" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L39" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2279,7 +2275,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2289,35 +2285,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E40" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>7.58</v>
+        <v>7.5</v>
       </c>
       <c r="K40" t="n">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="L40" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -2325,45 +2321,45 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>7.58</v>
+        <v>4.5</v>
       </c>
       <c r="K41" t="n">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="L41" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -2371,7 +2367,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2381,35 +2377,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="F42" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>7.5</v>
+        <v>10.33</v>
       </c>
       <c r="K42" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="L42" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -2417,45 +2413,45 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5</v>
+        <v>7.58</v>
       </c>
       <c r="K43" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="L43" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -2463,45 +2459,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D44" t="n">
+        <v>68</v>
+      </c>
+      <c r="E44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7</v>
+      </c>
+      <c r="G44" t="n">
         <v>6</v>
       </c>
-      <c r="E44" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F44" t="n">
-        <v>12</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K44" t="n">
         <v>2</v>
       </c>
-      <c r="J44" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="K44" t="n">
-        <v>124</v>
-      </c>
       <c r="L44" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -2509,45 +2505,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>10.4</v>
+        <v>16.8</v>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
-        <v>1.87</v>
+        <v>15.55</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>373</v>
       </c>
       <c r="L45" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -2555,7 +2551,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
+          <t>Saint Spritz Sicily 4pk 355ml</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2565,35 +2561,35 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E46" t="n">
-        <v>15.4</v>
+        <v>29.8</v>
       </c>
       <c r="F46" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>15.55</v>
+        <v>10.33</v>
       </c>
       <c r="K46" t="n">
-        <v>373</v>
+        <v>124</v>
       </c>
       <c r="L46" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -2601,7 +2597,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Saint Spritz Sicily 4pk 355ml</t>
+          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2615,31 +2611,31 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E47" t="n">
         <v>29.8</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>10.33</v>
+        <v>7.8</v>
       </c>
       <c r="K47" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="L47" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -2647,7 +2643,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
+          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2661,13 +2657,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E48" t="n">
-        <v>29.8</v>
+        <v>32.1</v>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2693,45 +2689,40 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
+          <t>Samichlaus Classic</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>32.1</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>7.8</v>
+        <v>15.38</v>
       </c>
       <c r="K49" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="L49" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -2739,40 +2730,45 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Samichlaus Classic</t>
+          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E50" t="n">
-        <v>32.1</v>
+        <v>39.8</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>15.38</v>
+        <v>7.8</v>
       </c>
       <c r="K50" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="L50" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -2780,7 +2776,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2790,35 +2786,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E51" t="n">
-        <v>36.3</v>
+        <v>42.2</v>
       </c>
       <c r="F51" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>7.8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="L51" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -2826,7 +2822,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2840,31 +2836,31 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E52" t="n">
-        <v>42.2</v>
+        <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H52" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>8.130000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>195</v>
+        <v>59</v>
       </c>
       <c r="L52" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -2872,45 +2868,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Estrella Daura IPA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>65</v>
-      </c>
-      <c r="E53" t="n">
-        <v>58</v>
+        <v>-1</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>9.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="K53" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="L53" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -2918,37 +2906,42 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Estrella Daura IPA</t>
+          <t>Insight Control Alt Beer 4pk 16oz can</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>Craft</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Insight Brewing Company (D)</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>8.5</v>
+        <v>11.53</v>
       </c>
       <c r="K54" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="L54" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -2956,83 +2949,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Insight Control Alt Beer 4pk 16oz can</t>
+          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Craft</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Insight Brewing Company (D)</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>11.53</v>
+        <v>2.3</v>
       </c>
       <c r="K55" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Single Serve</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" t="n">
-        <v>34</v>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3182,10 +3132,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>27.6</v>
+        <v>18.4</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
@@ -3200,7 +3150,7 @@
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>7.86</v>
+        <v>7.82</v>
       </c>
       <c r="K3" t="n">
         <v>94</v>
@@ -3267,10 +3217,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -3312,10 +3262,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="F6" t="n">
         <v>11</v>
@@ -3330,7 +3280,7 @@
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>10.48</v>
+        <v>10.52</v>
       </c>
       <c r="K6" t="n">
         <v>126</v>
@@ -3357,10 +3307,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F7" t="n">
         <v>19</v>
@@ -3402,10 +3352,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="F8" t="n">
         <v>14</v>
@@ -3441,7 +3391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3538,28 +3488,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F2" t="n">
         <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>8.66</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>415</v>
+        <v>362</v>
       </c>
       <c r="L2" t="n">
         <v>37</v>
@@ -3574,7 +3524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3588,31 +3538,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>8.66</v>
+        <v>8.49</v>
       </c>
       <c r="K3" t="n">
-        <v>156</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -3624,7 +3574,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3638,28 +3588,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K4" t="n">
-        <v>313</v>
+        <v>156</v>
       </c>
       <c r="L4" t="n">
         <v>37</v>
@@ -3674,7 +3624,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3688,31 +3638,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>106</v>
+        <v>314</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -3724,7 +3674,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3738,31 +3688,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>8.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>468</v>
+        <v>106</v>
       </c>
       <c r="L6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -3774,7 +3724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3788,31 +3738,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>446</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="G7" t="n">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I7" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>21.95</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>1141</v>
+        <v>465</v>
       </c>
       <c r="L7" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -3824,7 +3774,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3838,34 +3788,84 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>438</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="H8" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
-        <v>8.82</v>
+        <v>21.89</v>
       </c>
       <c r="K8" t="n">
-        <v>212</v>
+        <v>1314</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>High Noon Watermelon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="K9" t="n">
+        <v>156</v>
+      </c>
+      <c r="L9" t="n">
+        <v>37</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -3882,7 +3882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3958,7 +3958,7 @@
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Chanhassen (7)</t>
+          <t>Blaine (7)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -4093,24 +4093,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Chanhassen (6)</t>
+          <t>Blaine (5)</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -4125,29 +4125,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Blaine (5)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -4162,29 +4162,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4</v>
+        <v>-21.4</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Chanhassen (5)</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -4199,29 +4199,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E9" t="n">
-        <v>-21.4</v>
+        <v>-0.4</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Chanhassen (5)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -4236,33 +4236,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Bloomington (10)</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4273,33 +4273,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3</v>
+        <v>-19.3</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bloomington (10)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4310,29 +4310,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -4347,19 +4347,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-192.9</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
@@ -4369,11 +4369,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4384,33 +4384,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="E14" t="n">
-        <v>-192.9</v>
+        <v>-11.9</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Andover (6)</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -4421,33 +4421,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="E15" t="n">
-        <v>-11.6</v>
+        <v>-2.1</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Andover (6)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4458,29 +4458,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -4574,24 +4574,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Rosemount (4)</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -4606,29 +4606,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4</v>
+        <v>99</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Minneapolis (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -4643,29 +4643,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monaco Tropic Rush 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E21" t="n">
-        <v>99</v>
+        <v>-2.4</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Minneapolis (15)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -4685,24 +4685,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Monaco Tropic Rush 12oz can</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E22" t="n">
         <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Minneapolis (11)</t>
+          <t>Minneapolis (15)</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4726,20 +4726,20 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7</v>
+        <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Minneapolis (11)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -4754,19 +4754,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="E24" t="n">
-        <v>99</v>
+        <v>-6.6</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -4796,24 +4796,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 12oz can</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5</v>
+        <v>99</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -4823,34 +4823,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>-2</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7</v>
+        <v>-2.5</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>316</v>
+        <v>8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Blaine (17)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
         <v>0.5</v>
@@ -4883,11 +4883,11 @@
         <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>St. Louis Park (13)</t>
+          <t>St. Louis Park (8), Bloomington (5)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -4994,7 +4994,7 @@
         <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -5031,11 +5031,11 @@
         <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>St. Louis Park (7)</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -5050,33 +5050,33 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Chanhassen (6)</t>
+          <t>Vadnais Heights (6), Minnetonka (5)</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F35" t="n">
         <v>4</v>
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -5198,29 +5198,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -5240,20 +5240,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F37" t="n">
         <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Vadnais Heights (5)</t>
+          <t>Bloomington (5)</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -5383,33 +5383,33 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
@@ -5457,66 +5457,66 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F43" t="n">
         <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="F44" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>944</v>
+        <v>31</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Minneapolis (24), Rosemount (19)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5540,20 +5540,20 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E45" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>373</v>
+        <v>941</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Blaine (12), Bloomington (5)</t>
+          <t>Rosemount (22), Minneapolis (21)</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5577,20 +5577,20 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E46" t="n">
-        <v>3.9</v>
+        <v>6.1</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G46" t="n">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Andover (15)</t>
+          <t>Blaine (11), Bloomington (6)</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5614,24 +5614,24 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E47" t="n">
-        <v>6.7</v>
+        <v>3.9</v>
       </c>
       <c r="F47" t="n">
         <v>15</v>
       </c>
       <c r="G47" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Minnetonka (7), Bloomington (4), Vadnais Heights (4)</t>
+          <t>Andover (15)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G48" t="n">
-        <v>220</v>
+        <v>315</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Chanhassen (17)</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -5679,29 +5679,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="F49" t="n">
         <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Minneapolis (8), Stillwater (4)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -5716,29 +5716,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Blaine (8)</t>
+          <t>Minneapolis (8), Stillwater (4)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5762,20 +5762,20 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E51" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Blaine (8)</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -5790,33 +5790,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E52" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="F52" t="n">
         <v>7</v>
       </c>
       <c r="G52" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Minnetonka (7)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -5827,33 +5827,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E53" t="n">
-        <v>99</v>
+        <v>4.4</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -5864,29 +5864,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -5901,33 +5901,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Andover (6), Vadnais Heights (4)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5938,29 +5938,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Chanhassen (6)</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -5975,33 +5975,33 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E57" t="n">
-        <v>2.5</v>
+        <v>99</v>
       </c>
       <c r="F57" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>St. Louis Park (9)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -6017,24 +6017,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D58" t="n">
+        <v>6</v>
+      </c>
+      <c r="E58" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F58" t="n">
         <v>5</v>
       </c>
-      <c r="E58" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4</v>
-      </c>
       <c r="G58" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -6049,33 +6049,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E59" t="n">
-        <v>99</v>
+        <v>2.5</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G59" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Andover (6), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -6086,29 +6086,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>60.1</v>
+        <v>6.1</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -6128,28 +6128,28 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>99</v>
+        <v>2.5</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G61" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>St. Louis Park (9)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -6160,33 +6160,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>11.1</v>
+        <v>3.8</v>
       </c>
       <c r="F62" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G62" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (6)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6197,29 +6197,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>3.2</v>
+        <v>99</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -6234,33 +6234,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="E64" t="n">
-        <v>7.1</v>
+        <v>60.1</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
       </c>
       <c r="G64" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -6271,29 +6271,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>2.6</v>
+        <v>99</v>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Cottage Grove (7)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -6308,33 +6308,33 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F66" t="n">
         <v>16</v>
       </c>
-      <c r="E66" t="n">
-        <v>99</v>
-      </c>
-      <c r="F66" t="n">
-        <v>27</v>
-      </c>
       <c r="G66" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Minneapolis (27)</t>
+          <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
@@ -6345,33 +6345,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E67" t="n">
-        <v>11.7</v>
+        <v>7.1</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Cottage Grove (6)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68">
@@ -6382,33 +6382,33 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G68" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Cottage Grove (7)</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6419,33 +6419,33 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
-        <v>3.3</v>
+        <v>99</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="G69" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Vadnais Heights (26)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -6456,33 +6456,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F70" t="n">
         <v>6</v>
       </c>
-      <c r="E70" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F70" t="n">
-        <v>5</v>
-      </c>
       <c r="G70" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Vadnais Heights (5)</t>
+          <t>Cottage Grove (6)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6493,33 +6493,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="F71" t="n">
         <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6530,33 +6530,33 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E72" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G72" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -6567,19 +6567,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E73" t="n">
-        <v>99</v>
+        <v>3.5</v>
       </c>
       <c r="F73" t="n">
         <v>4</v>
@@ -6589,11 +6589,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>St. Louis Park (4)</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -6604,29 +6604,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="F74" t="n">
         <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -6641,29 +6641,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>14.3</v>
+        <v>3.4</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -6678,29 +6678,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
+        <v>6</v>
+      </c>
+      <c r="E76" t="n">
+        <v>99</v>
+      </c>
+      <c r="F76" t="n">
         <v>4</v>
       </c>
-      <c r="E76" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F76" t="n">
-        <v>5</v>
-      </c>
       <c r="G76" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -6715,33 +6715,33 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E77" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F77" t="n">
         <v>4</v>
       </c>
-      <c r="F77" t="n">
-        <v>11</v>
-      </c>
       <c r="G77" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Cottage Grove (11)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -6757,28 +6757,28 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="F78" t="n">
         <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Osseo (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6789,33 +6789,33 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E79" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G79" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>St. Louis Park (6)</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -6826,29 +6826,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>99</v>
+        <v>3.4</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -6863,29 +6863,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>10</v>
       </c>
       <c r="E81" t="n">
-        <v>6.4</v>
+        <v>14.3</v>
       </c>
       <c r="F81" t="n">
         <v>6</v>
       </c>
       <c r="G81" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -6900,29 +6900,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>99</v>
+        <v>10.2</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Blaine (5)</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -6937,29 +6937,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E83" t="n">
-        <v>26.8</v>
+        <v>4</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Cottage Grove (11)</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -6974,29 +6974,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monaco Lemonade 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>99</v>
+        <v>2.7</v>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G84" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -7011,29 +7011,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G85" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -7048,29 +7048,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E86" t="n">
-        <v>99</v>
+        <v>6.4</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G86" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -7085,32 +7085,217 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>Blaine</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Monaco Watermelon Crush 12oz can</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="n">
+        <v>99</v>
+      </c>
+      <c r="F87" t="n">
+        <v>6</v>
+      </c>
+      <c r="G87" t="n">
+        <v>11</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Minneapolis (6)</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>Ramsey</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Monaco Citrus Rush 12oz can</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>9</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Cottage Grove (5)</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Osseo</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Monaco Lemonade 12oz can</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>13</v>
+      </c>
+      <c r="E89" t="n">
+        <v>99</v>
+      </c>
+      <c r="F89" t="n">
+        <v>5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>9</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Minneapolis (5)</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ramsey</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Monaco Mai Tai 12oz can</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" t="n">
+        <v>5</v>
+      </c>
+      <c r="G90" t="n">
+        <v>9</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Cottage Grove (5)</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Blaine</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Monaco Mai Tai 12oz can</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" t="n">
+        <v>99</v>
+      </c>
+      <c r="F91" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Minneapolis (4)</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ramsey</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D92" t="n">
         <v>3</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E92" t="n">
         <v>32.1</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F92" t="n">
         <v>4</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G92" t="n">
         <v>8</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Minneapolis (4)</t>
         </is>
       </c>
-      <c r="I87" t="n">
+      <c r="I92" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Being Removed" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Buy-Month Wait" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +496,11 @@
           <t>Buy Month</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -545,6 +551,11 @@
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -591,6 +602,7 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -641,6 +653,11 @@
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -687,6 +704,7 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -733,6 +751,7 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -783,6 +802,11 @@
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -829,6 +853,7 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -879,6 +904,11 @@
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -925,6 +955,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -971,6 +1002,7 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1017,6 +1049,7 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1063,6 +1096,7 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1109,6 +1143,7 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1155,6 +1190,7 @@
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1205,6 +1241,7 @@
           <t>In buy-month (Jun)</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1251,6 +1288,7 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1297,6 +1335,7 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1343,6 +1382,7 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1389,6 +1429,7 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1435,6 +1476,7 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1481,6 +1523,7 @@
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1527,6 +1570,7 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1573,6 +1617,7 @@
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1619,6 +1664,7 @@
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1665,6 +1711,7 @@
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1711,6 +1758,7 @@
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1761,6 +1809,7 @@
           <t>In buy-month (Jun)</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1811,6 +1860,7 @@
           <t>In buy-month (Jun)</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1857,6 +1907,7 @@
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1903,6 +1954,7 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1949,6 +2001,7 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1995,6 +2048,7 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2041,6 +2095,7 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2087,6 +2142,7 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2133,6 +2189,7 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2179,6 +2236,7 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2225,6 +2283,7 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2271,6 +2330,7 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2317,6 +2377,7 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2363,6 +2424,7 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2409,6 +2471,7 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2455,6 +2518,7 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2501,6 +2565,7 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2547,6 +2612,7 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2593,6 +2659,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2639,6 +2706,7 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2685,6 +2753,7 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2726,6 +2795,7 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2772,6 +2842,7 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2818,6 +2889,7 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2864,6 +2936,7 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2902,6 +2975,7 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2945,6 +3019,7 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2983,6 +3058,7 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2995,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3069,11 +3145,21 @@
           <t>Deal Terms</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Buy Month</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jack &amp; Coke 4pk 12oz can</t>
+          <t>High Noon Passionfruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3087,38 +3173,48 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>-5</v>
       </c>
       <c r="E2" t="n">
-        <v>49.3</v>
+        <v>-1.5</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>8.56</v>
+        <v>8.73</v>
       </c>
       <c r="K2" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="L2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jack &amp; Coke Zero 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3132,38 +3228,48 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>18.4</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="J3" t="n">
-        <v>7.82</v>
+        <v>17.17</v>
       </c>
       <c r="K3" t="n">
-        <v>94</v>
+        <v>1957</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ketel One Spritz Cucumber &amp; Mint 4pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3171,39 +3277,54 @@
           <t>RTD</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>128.6</v>
+        <v>1.7</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>7.22</v>
+        <v>8.69</v>
       </c>
       <c r="K4" t="n">
-        <v>36</v>
+        <v>1303</v>
       </c>
       <c r="L4" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3213,172 +3334,47 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="J5" t="n">
-        <v>10.22</v>
+        <v>17.13</v>
       </c>
       <c r="K5" t="n">
-        <v>164</v>
+        <v>1593</v>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>12</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="K6" t="n">
-        <v>126</v>
-      </c>
-      <c r="L6" t="n">
-        <v>56</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>23</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>19</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>16</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="K7" t="n">
-        <v>164</v>
-      </c>
-      <c r="L7" t="n">
-        <v>49</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>29</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>14</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="K8" t="n">
-        <v>82</v>
-      </c>
-      <c r="L8" t="n">
-        <v>49</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3391,7 +3387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3465,16 +3461,11 @@
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Buy Month</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>Jack &amp; Coke 4pk 12oz can</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3488,43 +3479,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4</v>
+        <v>49.3</v>
       </c>
       <c r="F2" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>8.630000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="K2" t="n">
-        <v>362</v>
+        <v>51</v>
       </c>
       <c r="L2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>Jack &amp; Coke Zero 4pk 12oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3538,43 +3524,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4</v>
+        <v>18.4</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>8.49</v>
+        <v>7.82</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>94</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Ketel One Spritz Cucumber &amp; Mint 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3582,49 +3563,39 @@
           <t>RTD</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4</v>
+        <v>128.6</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>8.65</v>
+        <v>7.22</v>
       </c>
       <c r="K4" t="n">
-        <v>156</v>
+        <v>36</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>The Finnish Long Drink Cranberry 6pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3634,47 +3605,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>8.720000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>164</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>The Finnish Long Drink Strong 6pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3684,47 +3650,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>8.800000000000001</v>
+        <v>10.52</v>
       </c>
       <c r="K6" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3734,47 +3695,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
         <v>16</v>
       </c>
-      <c r="H7" t="n">
-        <v>54</v>
-      </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8.619999999999999</v>
+        <v>10.22</v>
       </c>
       <c r="K7" t="n">
-        <v>465</v>
+        <v>164</v>
       </c>
       <c r="L7" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3784,92 +3740,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="F8" t="n">
-        <v>171</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>21.89</v>
+        <v>10.26</v>
       </c>
       <c r="K8" t="n">
-        <v>1314</v>
+        <v>82</v>
       </c>
       <c r="L8" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>31</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>31</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>18</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="K9" t="n">
-        <v>156</v>
-      </c>
-      <c r="L9" t="n">
-        <v>37</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3882,6 +3783,497 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Chain OH (TOH)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>WOS</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Gross Need</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Buy Units</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Buy Cases</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Unit Cost</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Net Buy $</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GM %</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Discount %</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Deal Terms</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Buy Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>92</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>63</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="K2" t="n">
+        <v>362</v>
+      </c>
+      <c r="L2" t="n">
+        <v>37</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>42</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="K3" t="n">
+        <v>356</v>
+      </c>
+      <c r="L3" t="n">
+        <v>38</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>High Noon Lemon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="K4" t="n">
+        <v>156</v>
+      </c>
+      <c r="L4" t="n">
+        <v>37</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>High Noon Lime 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>76</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" t="n">
+        <v>37</v>
+      </c>
+      <c r="H5" t="n">
+        <v>36</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>314</v>
+      </c>
+      <c r="L5" t="n">
+        <v>37</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>High Noon Mango 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>106</v>
+      </c>
+      <c r="L6" t="n">
+        <v>36</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>High Noon Peach 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>80</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>72</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>54</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>465</v>
+      </c>
+      <c r="L7" t="n">
+        <v>37</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>438</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>171</v>
+      </c>
+      <c r="G8" t="n">
+        <v>111</v>
+      </c>
+      <c r="H8" t="n">
+        <v>60</v>
+      </c>
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1314</v>
+      </c>
+      <c r="L8" t="n">
+        <v>34</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>High Noon Watermelon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="K9" t="n">
+        <v>156</v>
+      </c>
+      <c r="L9" t="n">
+        <v>37</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Wait for buy-month (May, Aug)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +560,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bacardi Mojito 4pk 12oz can</t>
+          <t>Absolut Vodkarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -574,31 +574,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>8.119999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="K3" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -617,52 +617,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F4" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="n">
-        <v>114</v>
-      </c>
       <c r="I4" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>17.17</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1957</v>
+        <v>49</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Off buy-month - confirm timing</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Absolut Vodkarita 4pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -672,17 +664,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -694,13 +686,13 @@
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>6.45</v>
+        <v>10.33</v>
       </c>
       <c r="K5" t="n">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="L5" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -709,7 +701,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -723,40 +715,48 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J6" t="n">
-        <v>10.33</v>
+        <v>17.04</v>
       </c>
       <c r="K6" t="n">
-        <v>124</v>
+        <v>1534</v>
       </c>
       <c r="L6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -770,31 +770,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F7" t="n">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J7" t="n">
-        <v>8.69</v>
+        <v>17.07</v>
       </c>
       <c r="K7" t="n">
-        <v>1303</v>
+        <v>1946</v>
       </c>
       <c r="L7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sunny D Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -825,31 +825,31 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>29</v>
+      </c>
+      <c r="G8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>21</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>15.46</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>325</v>
+        <v>195</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -858,7 +858,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -872,31 +872,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F9" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="G9" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="I9" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>17.13</v>
+        <v>8.65</v>
       </c>
       <c r="K9" t="n">
-        <v>1593</v>
+        <v>1297</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F10" t="n">
         <v>11</v>
@@ -945,10 +945,10 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>13.53</v>
+        <v>13.59</v>
       </c>
       <c r="K10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L10" t="n">
         <v>41</v>
@@ -960,7 +960,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>Sunny D Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -974,31 +974,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>8.119999999999999</v>
+        <v>15.47</v>
       </c>
       <c r="K11" t="n">
-        <v>195</v>
+        <v>325</v>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1017,44 +1017,48 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>6.98</v>
+        <v>18.53</v>
       </c>
       <c r="K12" t="n">
-        <v>42</v>
+        <v>222</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1064,35 +1068,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>8.119999999999999</v>
+        <v>12.31</v>
       </c>
       <c r="K13" t="n">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="L13" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1101,7 +1105,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks New Fashioned 4pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1115,31 +1119,31 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>12.13</v>
+        <v>7.84</v>
       </c>
       <c r="K14" t="n">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="L14" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1148,7 +1152,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1162,31 +1166,31 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>7.72</v>
+        <v>9.75</v>
       </c>
       <c r="K15" t="n">
-        <v>371</v>
+        <v>58</v>
       </c>
       <c r="L15" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1195,7 +1199,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1205,48 +1209,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>18.53</v>
+        <v>7.72</v>
       </c>
       <c r="K16" t="n">
-        <v>222</v>
+        <v>371</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1260,28 +1260,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>9.75</v>
       </c>
       <c r="K17" t="n">
-        <v>58</v>
+        <v>292</v>
       </c>
       <c r="L17" t="n">
         <v>35</v>
@@ -1293,7 +1293,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Two Chicks New Fashioned 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>7.84</v>
+        <v>7.17</v>
       </c>
       <c r="K18" t="n">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1340,7 +1340,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Bacardi Mojito 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1350,32 +1350,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>7.67</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="L19" t="n">
         <v>41</v>
@@ -1387,7 +1387,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1401,31 +1401,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>9.75</v>
+        <v>7.68</v>
       </c>
       <c r="K20" t="n">
-        <v>292</v>
+        <v>138</v>
       </c>
       <c r="L20" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1444,20 +1444,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>12</v>
@@ -1466,13 +1466,13 @@
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>4.88</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="L21" t="n">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1481,7 +1481,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1491,11 +1491,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
         <v>4.2</v>
@@ -1504,7 +1504,7 @@
         <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
@@ -1513,13 +1513,13 @@
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>7.17</v>
+        <v>7.56</v>
       </c>
       <c r="K22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L22" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1538,35 +1538,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>7.56</v>
+        <v>8.19</v>
       </c>
       <c r="K23" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="L23" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1575,24 +1575,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1.91</v>
+        <v>7.15</v>
       </c>
       <c r="K24" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="L24" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1622,45 +1622,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>4.4</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>4.5</v>
+        <v>7.17</v>
       </c>
       <c r="K25" t="n">
-        <v>162</v>
+        <v>43</v>
       </c>
       <c r="L25" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1669,7 +1669,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1679,44 +1679,48 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E26" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H26" t="n">
         <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>8.17</v>
+        <v>18.32</v>
       </c>
       <c r="K26" t="n">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="L26" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1726,35 +1730,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E27" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>7.15</v>
+        <v>5.27</v>
       </c>
       <c r="K27" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="L27" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1763,7 +1767,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1773,42 +1777,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="K28" t="n">
         <v>48</v>
       </c>
-      <c r="H28" t="n">
-        <v>12</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="K28" t="n">
-        <v>220</v>
-      </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1828,28 +1828,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F29" t="n">
         <v>84</v>
       </c>
       <c r="G29" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H29" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>16.9</v>
+        <v>16.88</v>
       </c>
       <c r="K29" t="n">
-        <v>811</v>
+        <v>861</v>
       </c>
       <c r="L29" t="n">
         <v>32</v>
@@ -1865,7 +1865,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9.02</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1897,13 +1897,13 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>8.039999999999999</v>
+        <v>6.44</v>
       </c>
       <c r="K30" t="n">
+        <v>39</v>
+      </c>
+      <c r="L30" t="n">
         <v>48</v>
-      </c>
-      <c r="L30" t="n">
-        <v>46</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1912,45 +1912,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
         <v>5.2</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>9.720000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="K31" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="L31" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -1959,45 +1959,45 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.02</v>
+        <v>139</v>
       </c>
       <c r="E32" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>6.44</v>
+        <v>1.92</v>
       </c>
       <c r="K32" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="L32" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2016,35 +2016,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>12.88</v>
+        <v>7.79</v>
       </c>
       <c r="K33" t="n">
-        <v>193</v>
+        <v>47</v>
       </c>
       <c r="L33" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2053,45 +2053,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>24</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>19</v>
+      </c>
+      <c r="G34" t="n">
         <v>4</v>
       </c>
-      <c r="E34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>7.79</v>
+        <v>8.6</v>
       </c>
       <c r="K34" t="n">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2100,12 +2100,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2114,31 +2114,31 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
         <v>5.7</v>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
-        <v>8.6</v>
+        <v>12.88</v>
       </c>
       <c r="K35" t="n">
-        <v>103</v>
+        <v>193</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2161,31 +2161,31 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E36" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>6.81</v>
+        <v>5.41</v>
       </c>
       <c r="K36" t="n">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="L36" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2194,7 +2194,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2204,35 +2204,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E37" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>5.41</v>
+        <v>7.57</v>
       </c>
       <c r="K37" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="L37" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2251,35 +2251,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="E38" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>7.56</v>
+        <v>6.94</v>
       </c>
       <c r="K38" t="n">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="L38" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -2382,12 +2382,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2396,31 +2396,31 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
         <v>8.6</v>
       </c>
       <c r="F41" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I41" t="n">
         <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>4.5</v>
+        <v>10.33</v>
       </c>
       <c r="K41" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -2429,12 +2429,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2443,31 +2443,31 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E42" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>10.33</v>
+        <v>4.5</v>
       </c>
       <c r="K42" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="L42" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -2476,12 +2476,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2490,31 +2490,31 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="E43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>7.58</v>
+        <v>1.87</v>
       </c>
       <c r="K43" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -2523,12 +2523,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2537,31 +2537,31 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>1.87</v>
+        <v>7.58</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="L44" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -2617,7 +2617,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Saint Spritz Sicily 4pk 355ml</t>
+          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2631,31 +2631,31 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E46" t="n">
-        <v>29.8</v>
+        <v>19.8</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>10.33</v>
+        <v>7.8</v>
       </c>
       <c r="K46" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="L46" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
+          <t>Saint Spritz Sicily 4pk 355ml</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2678,31 +2678,31 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
-        <v>29.8</v>
+        <v>31.3</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>7.8</v>
+        <v>10.33</v>
       </c>
       <c r="K47" t="n">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="L47" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3228,31 +3228,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I3" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>17.17</v>
+        <v>17.04</v>
       </c>
       <c r="K3" t="n">
-        <v>1957</v>
+        <v>1534</v>
       </c>
       <c r="L3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -3269,7 +3269,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3283,31 +3283,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F4" t="n">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="J4" t="n">
-        <v>8.69</v>
+        <v>17.07</v>
       </c>
       <c r="K4" t="n">
-        <v>1303</v>
+        <v>1946</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
@@ -3324,7 +3324,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3338,31 +3338,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="I5" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
-        <v>17.13</v>
+        <v>8.65</v>
       </c>
       <c r="K5" t="n">
-        <v>1593</v>
+        <v>1297</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -3627,7 +3627,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>10.22</v>
+        <v>10.23</v>
       </c>
       <c r="K5" t="n">
         <v>164</v>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="F7" t="n">
         <v>19</v>
@@ -3717,7 +3717,7 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>10.22</v>
+        <v>10.23</v>
       </c>
       <c r="K7" t="n">
         <v>164</v>
@@ -3747,7 +3747,7 @@
         <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="F8" t="n">
         <v>14</v>
@@ -3880,16 +3880,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="F2" t="n">
         <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
         <v>42</v>
@@ -3898,13 +3898,13 @@
         <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>8.630000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="K2" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="F3" t="n">
         <v>60</v>
@@ -3948,13 +3948,13 @@
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>8.49</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -3980,28 +3980,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>24</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I4" t="n">
         <v>4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>8.65</v>
       </c>
       <c r="K4" t="n">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="L4" t="n">
         <v>37</v>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="F5" t="n">
         <v>70</v>
@@ -4083,7 +4083,7 @@
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="F6" t="n">
         <v>22</v>
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F7" t="n">
         <v>72</v>
@@ -4148,13 +4148,13 @@
         <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>8.619999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="K7" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="L7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E8" t="n">
         <v>3.8</v>
@@ -4189,22 +4189,22 @@
         <v>171</v>
       </c>
       <c r="G8" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J8" t="n">
-        <v>21.89</v>
+        <v>22.06</v>
       </c>
       <c r="K8" t="n">
-        <v>1314</v>
+        <v>1235</v>
       </c>
       <c r="L8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="F9" t="n">
         <v>31</v>
@@ -4248,13 +4248,13 @@
         <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>8.640000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="K9" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
@@ -4274,7 +4274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4350,7 +4350,7 @@
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4591,33 +4591,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Minneapolis (4)</t>
+          <t>Bloomington (10)</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4628,33 +4628,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3</v>
+        <v>-20.3</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bloomington (10)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4665,29 +4665,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-19.3</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -4702,19 +4702,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-192.9</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
@@ -4724,11 +4724,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4739,33 +4739,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="E13" t="n">
-        <v>-192.9</v>
+        <v>-13.9</v>
       </c>
       <c r="F13" t="n">
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Andover (6)</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -4776,33 +4776,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.9</v>
+        <v>-2.3</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Andover (6)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4813,29 +4813,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -4855,28 +4855,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-4.5</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4887,33 +4887,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Rosemount (4)</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4924,33 +4924,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.5</v>
+        <v>99</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4961,29 +4961,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Rosemount (4)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -4998,29 +4998,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Monaco Tropic Rush 12oz can</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E20" t="n">
         <v>99</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Minneapolis (15)</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -5035,29 +5035,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-3</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Minneapolis (4)</t>
+          <t>Minneapolis (11)</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -5072,29 +5072,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monaco Tropic Rush 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1</v>
+        <v>-11</v>
       </c>
       <c r="E22" t="n">
-        <v>99</v>
+        <v>-6.6</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Minneapolis (15)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -5109,29 +5109,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 12oz can</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Minneapolis (11)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -5146,29 +5146,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6</v>
+        <v>-2.5</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -5178,34 +5178,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STOCKOUT</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E25" t="n">
-        <v>99</v>
+        <v>1.8</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>949</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Blaine (25), Minneapolis (18)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -5215,38 +5215,38 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STOCKOUT</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5</v>
+        <v>1.3</v>
       </c>
       <c r="F26" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" t="n">
+        <v>290</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Bloomington (8), St. Louis Park (5), Vadnais Heights (4)</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>8</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Cottage Grove (4)</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -5262,24 +5262,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>St. Louis Park (8), Bloomington (5)</t>
+          <t>Plymouth (10)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -5294,29 +5294,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Plymouth (10)</t>
+          <t>St. Louis Park (10)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -5343,7 +5343,7 @@
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F29" t="n">
         <v>9</v>
@@ -5377,20 +5377,20 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -5405,29 +5405,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>St. Louis Park (7)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -5442,33 +5442,33 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6), Minnetonka (5)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5488,20 +5488,20 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -5516,29 +5516,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Bloomington (7)</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -5553,33 +5553,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F35" t="n">
         <v>6</v>
       </c>
-      <c r="E35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4</v>
-      </c>
       <c r="G35" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -5590,33 +5590,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" t="n">
+        <v>51</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (6)</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" t="n">
-        <v>68</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Stillwater (4)</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -5627,29 +5627,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -5664,29 +5664,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Bloomington (5)</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -5701,25 +5701,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="F39" t="n">
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -5738,33 +5738,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D40" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F40" t="n">
         <v>4</v>
       </c>
-      <c r="E40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F40" t="n">
-        <v>5</v>
-      </c>
       <c r="G40" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bloomington (5)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -5780,108 +5780,108 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>Top-up</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G42" t="n">
-        <v>38</v>
+        <v>375</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Rosemount (10), Bloomington (7)</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>Top-up</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>34</v>
+        <v>331</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Andover (15)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>Top-up</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5891,28 +5891,28 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G44" t="n">
-        <v>31</v>
+        <v>331</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Osseo (8), Minnetonka (7)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -5928,24 +5928,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
         <v>2.1</v>
       </c>
       <c r="F45" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
-        <v>941</v>
+        <v>315</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Rosemount (22), Minneapolis (21)</t>
+          <t>Chanhassen (17)</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -5965,24 +5965,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>372</v>
+        <v>220</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Blaine (11), Bloomington (6)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -5997,29 +5997,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>328</v>
+        <v>203</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Andover (15)</t>
+          <t>Stillwater (8), Minneapolis (4)</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -6034,29 +6034,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E48" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="F48" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>315</v>
+        <v>176</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Chanhassen (17)</t>
+          <t>Rosemount (8)</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -6071,29 +6071,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E49" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="F49" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G49" t="n">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6117,20 +6117,20 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="F50" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Minneapolis (8), Stillwater (4)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -6145,29 +6145,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Blaine (8)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -6182,33 +6182,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Minnetonka (7)</t>
+          <t>Chanhassen (6)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -6219,33 +6219,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E53" t="n">
-        <v>4.4</v>
+        <v>99</v>
       </c>
       <c r="F53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -6256,29 +6256,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="F54" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -6293,33 +6293,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E55" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -6330,33 +6330,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E56" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G56" t="n">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Chanhassen (6)</t>
+          <t>Osseo (5), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6376,24 +6376,24 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>99</v>
+        <v>3.8</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -6404,29 +6404,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>5.1</v>
+        <v>99</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -6441,33 +6441,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="E59" t="n">
-        <v>2.5</v>
+        <v>51.7</v>
       </c>
       <c r="F59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Andover (6), Vadnais Heights (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6478,29 +6478,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>6.1</v>
+        <v>99</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -6515,33 +6515,33 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>2.5</v>
+        <v>11.9</v>
       </c>
       <c r="F61" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G61" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>St. Louis Park (9)</t>
+          <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -6552,33 +6552,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Bloomington (4), Woodbury (4)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -6589,29 +6589,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>99</v>
+        <v>2.2</v>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G63" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Cottage Grove (7)</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -6626,33 +6626,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="E64" t="n">
-        <v>60.1</v>
+        <v>3.1</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Andover (6)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -6663,29 +6663,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E65" t="n">
         <v>99</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G65" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Vadnais Heights (27)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -6700,33 +6700,33 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E66" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="F66" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (6)</t>
+          <t>Cottage Grove (6)</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -6737,33 +6737,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G67" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -6779,28 +6779,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E68" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="F68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G68" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Cottage Grove (7)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -6811,33 +6811,33 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>99</v>
+        <v>3.3</v>
       </c>
       <c r="F69" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Vadnais Heights (26)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6848,33 +6848,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>8</v>
       </c>
       <c r="E70" t="n">
-        <v>11.7</v>
+        <v>3.5</v>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Cottage Grove (6)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -6885,33 +6885,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -6922,33 +6922,33 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>6</v>
       </c>
       <c r="E72" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="F72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G72" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>St. Louis Park (4)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6959,19 +6959,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>3.5</v>
+        <v>99</v>
       </c>
       <c r="F73" t="n">
         <v>4</v>
@@ -6981,11 +6981,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>St. Louis Park (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6996,33 +6996,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="F74" t="n">
         <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -7038,28 +7038,28 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="F75" t="n">
         <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -7075,24 +7075,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F76" t="n">
         <v>6</v>
       </c>
-      <c r="E76" t="n">
-        <v>99</v>
-      </c>
-      <c r="F76" t="n">
-        <v>4</v>
-      </c>
       <c r="G76" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -7112,28 +7112,28 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E77" t="n">
+        <v>7</v>
+      </c>
+      <c r="F77" t="n">
         <v>6</v>
       </c>
-      <c r="E77" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
-      </c>
       <c r="G77" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>St. Louis Park (6)</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -7149,28 +7149,28 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="F78" t="n">
         <v>4</v>
       </c>
       <c r="G78" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7190,24 +7190,24 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>10.2</v>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>St. Louis Park (6)</t>
+          <t>Blaine (5)</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -7218,29 +7218,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E80" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Cottage Grove (11)</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -7255,29 +7255,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>14.3</v>
+        <v>2.7</v>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G81" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -7292,29 +7292,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>10.2</v>
+        <v>99</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G82" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Blaine (5)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -7329,29 +7329,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="F83" t="n">
+        <v>6</v>
+      </c>
+      <c r="G83" t="n">
         <v>11</v>
       </c>
-      <c r="G83" t="n">
-        <v>21</v>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Cottage Grove (11)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -7366,29 +7366,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E84" t="n">
-        <v>2.7</v>
+        <v>99</v>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -7403,29 +7403,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D85" t="n">
+        <v>5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="n">
         <v>10</v>
       </c>
-      <c r="E85" t="n">
-        <v>99</v>
-      </c>
-      <c r="F85" t="n">
-        <v>6</v>
-      </c>
-      <c r="G85" t="n">
-        <v>11</v>
-      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -7440,29 +7440,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" t="n">
         <v>10</v>
       </c>
-      <c r="E86" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F86" t="n">
-        <v>6</v>
-      </c>
-      <c r="G86" t="n">
-        <v>11</v>
-      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -7477,29 +7477,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Lemonade 12oz can</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E87" t="n">
         <v>99</v>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G87" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -7514,29 +7514,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>26.8</v>
+        <v>99</v>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -7551,143 +7551,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Monaco Lemonade 12oz can</t>
+          <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>99</v>
+        <v>32.1</v>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Monaco Mai Tai 12oz can</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>4</v>
-      </c>
-      <c r="F90" t="n">
-        <v>5</v>
-      </c>
-      <c r="G90" t="n">
-        <v>9</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Cottage Grove (5)</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Blaine</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Monaco Mai Tai 12oz can</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>4</v>
-      </c>
-      <c r="E91" t="n">
-        <v>99</v>
-      </c>
-      <c r="F91" t="n">
-        <v>4</v>
-      </c>
-      <c r="G91" t="n">
-        <v>8</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Monaco Purple Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>3</v>
-      </c>
-      <c r="E92" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F92" t="n">
-        <v>4</v>
-      </c>
-      <c r="G92" t="n">
-        <v>8</v>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
@@ -607,7 +607,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -617,44 +617,52 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>133</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="J4" t="n">
-        <v>8.119999999999999</v>
+        <v>17.02</v>
       </c>
       <c r="K4" t="n">
-        <v>49</v>
+        <v>1583</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>Sunny D Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,35 +672,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>10.33</v>
+        <v>15.46</v>
       </c>
       <c r="K5" t="n">
-        <v>124</v>
+        <v>325</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -701,7 +709,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -711,52 +719,44 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I6" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>17.04</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1534</v>
+        <v>244</v>
       </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Off buy-month - confirm timing</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -766,52 +766,44 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="H7" t="n">
-        <v>114</v>
-      </c>
       <c r="I7" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>17.07</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>1946</v>
+        <v>49</v>
       </c>
       <c r="L7" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Off buy-month - confirm timing</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -821,44 +813,52 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J8" t="n">
-        <v>8.119999999999999</v>
+        <v>17.05</v>
       </c>
       <c r="K8" t="n">
-        <v>195</v>
+        <v>1944</v>
       </c>
       <c r="L8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>Two Chicks Vodka Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -868,52 +868,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F9" t="n">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>8.65</v>
+        <v>13.55</v>
       </c>
       <c r="K9" t="n">
-        <v>1297</v>
+        <v>163</v>
       </c>
       <c r="L9" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Off buy-month - confirm timing</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -923,44 +915,52 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>13.59</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>163</v>
+        <v>1293</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sunny D Variety Pack 8pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -970,44 +970,52 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>15.47</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>325</v>
+        <v>207</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1017,48 +1025,44 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="F12" t="n">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>18.53</v>
+        <v>9.75</v>
       </c>
       <c r="K12" t="n">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1068,35 +1072,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>12.31</v>
+        <v>10.33</v>
       </c>
       <c r="K13" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="L13" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1119,10 +1123,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="F14" t="n">
         <v>16</v>
@@ -1137,13 +1141,13 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>7.84</v>
+        <v>7.86</v>
       </c>
       <c r="K14" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1152,7 +1156,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1166,31 +1170,31 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>46</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>54</v>
+      </c>
+      <c r="G15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>9.75</v>
+        <v>7.72</v>
       </c>
       <c r="K15" t="n">
-        <v>58</v>
+        <v>371</v>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1199,7 +1203,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1213,31 +1217,31 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
-        <v>54</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8</v>
-      </c>
       <c r="J16" t="n">
-        <v>7.72</v>
+        <v>12.26</v>
       </c>
       <c r="K16" t="n">
-        <v>371</v>
+        <v>110</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1246,7 +1250,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1256,44 +1260,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>9.75</v>
+        <v>18.53</v>
       </c>
       <c r="K17" t="n">
-        <v>292</v>
+        <v>222</v>
       </c>
       <c r="L17" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1307,31 +1315,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
+        <v>35</v>
+      </c>
+      <c r="G18" t="n">
         <v>6</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>7.17</v>
+        <v>9.75</v>
       </c>
       <c r="K18" t="n">
-        <v>43</v>
+        <v>292</v>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1340,7 +1348,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bacardi Mojito 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1354,10 +1362,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -1372,13 +1380,13 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>8.119999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L19" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1387,7 +1395,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1401,31 +1409,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>7.68</v>
+        <v>7.17</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="L20" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1434,7 +1442,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>Bacardi Mojito 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1448,31 +1456,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>9.720000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="L21" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1481,7 +1489,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1491,35 +1499,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>7.56</v>
+        <v>8.19</v>
       </c>
       <c r="K22" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="L22" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1528,7 +1536,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1542,31 +1550,31 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="H23" t="n">
-        <v>12</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
       <c r="J23" t="n">
-        <v>8.19</v>
+        <v>7.68</v>
       </c>
       <c r="K23" t="n">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1575,7 +1583,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1585,44 +1593,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E24" t="n">
         <v>4.3</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>7.15</v>
+        <v>18.33</v>
       </c>
       <c r="K24" t="n">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="L24" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1639,28 +1651,28 @@
         <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>7.17</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="L25" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1669,7 +1681,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1679,48 +1691,44 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F26" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>18.32</v>
+        <v>7.15</v>
       </c>
       <c r="K26" t="n">
-        <v>220</v>
+        <v>43</v>
       </c>
       <c r="L26" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1730,35 +1738,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
         <v>6</v>
       </c>
-      <c r="H27" t="n">
-        <v>12</v>
-      </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>5.27</v>
+        <v>7.17</v>
       </c>
       <c r="K27" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="L27" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1767,7 +1775,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1777,20 +1785,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
         <v>6</v>
@@ -1799,13 +1807,13 @@
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>8.039999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="K28" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L28" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1814,7 +1822,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1824,48 +1832,44 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="F29" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="G29" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>16.88</v>
+        <v>5.55</v>
       </c>
       <c r="K29" t="n">
-        <v>861</v>
+        <v>67</v>
       </c>
       <c r="L29" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1879,31 +1883,31 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9.02</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>6.44</v>
+        <v>12.88</v>
       </c>
       <c r="K30" t="n">
-        <v>39</v>
+        <v>193</v>
       </c>
       <c r="L30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1912,7 +1916,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1922,35 +1926,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>129</v>
       </c>
       <c r="E31" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="F31" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>4.5</v>
+        <v>1.92</v>
       </c>
       <c r="K31" t="n">
-        <v>162</v>
+        <v>23</v>
       </c>
       <c r="L31" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -1959,54 +1963,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="E32" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H32" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>1.92</v>
+        <v>16.88</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>861</v>
       </c>
       <c r="L32" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2016,17 +2024,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>9.02</v>
       </c>
       <c r="E33" t="n">
         <v>5.5</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2038,13 +2046,13 @@
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>7.79</v>
+        <v>6.44</v>
       </c>
       <c r="K33" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="L33" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2053,45 +2061,45 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="F34" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>8.6</v>
+        <v>7.79</v>
       </c>
       <c r="K34" t="n">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="L34" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2100,7 +2108,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2110,35 +2118,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
         <v>5.7</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>12.88</v>
+        <v>10.33</v>
       </c>
       <c r="K35" t="n">
-        <v>193</v>
+        <v>124</v>
       </c>
       <c r="L35" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -2147,45 +2155,45 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="G36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>5.41</v>
+        <v>4.5</v>
       </c>
       <c r="K36" t="n">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="L36" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2194,7 +2202,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2208,28 +2216,28 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
-        <v>7.57</v>
+        <v>7.58</v>
       </c>
       <c r="K37" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
         <v>39</v>
@@ -2241,7 +2249,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2255,31 +2263,31 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E38" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H38" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>6.94</v>
+        <v>5.33</v>
       </c>
       <c r="K38" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="L38" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -2288,45 +2296,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>7.58</v>
+        <v>8.6</v>
       </c>
       <c r="K39" t="n">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="L39" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2335,7 +2343,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2345,35 +2353,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E40" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="F40" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="K40" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="L40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -2382,7 +2390,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2392,35 +2400,35 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D41" t="n">
+        <v>29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>6</v>
       </c>
-      <c r="E41" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F41" t="n">
-        <v>12</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>12</v>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>10.33</v>
+        <v>7.58</v>
       </c>
       <c r="K41" t="n">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="L41" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -2429,45 +2437,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="F42" t="n">
+        <v>16</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>18</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="K42" t="n">
+        <v>125</v>
+      </c>
+      <c r="L42" t="n">
         <v>47</v>
-      </c>
-      <c r="G42" t="n">
-        <v>20</v>
-      </c>
-      <c r="H42" t="n">
-        <v>24</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>108</v>
-      </c>
-      <c r="L42" t="n">
-        <v>44</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -2476,45 +2484,45 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="E43" t="n">
-        <v>9.699999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>1.87</v>
+        <v>7.5</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="L43" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -2523,12 +2531,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2537,31 +2545,31 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="E44" t="n">
         <v>9.9</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>7.58</v>
+        <v>1.87</v>
       </c>
       <c r="K44" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -2570,45 +2578,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E45" t="n">
-        <v>16.8</v>
+        <v>10.7</v>
       </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>15.55</v>
+        <v>4.5</v>
       </c>
       <c r="K45" t="n">
-        <v>373</v>
+        <v>108</v>
       </c>
       <c r="L45" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -2631,10 +2639,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>19.8</v>
+        <v>14.1</v>
       </c>
       <c r="F46" t="n">
         <v>7</v>
@@ -2664,7 +2672,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Saint Spritz Sicily 4pk 355ml</t>
+          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2674,35 +2682,35 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>31.3</v>
+        <v>18.4</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>10.33</v>
+        <v>15.55</v>
       </c>
       <c r="K47" t="n">
-        <v>124</v>
+        <v>373</v>
       </c>
       <c r="L47" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -2711,7 +2719,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
+          <t>Saint Spritz Sicily 4pk 355ml</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2725,31 +2733,31 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E48" t="n">
-        <v>32.1</v>
+        <v>23.1</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>7.8</v>
+        <v>10.33</v>
       </c>
       <c r="K48" t="n">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="L48" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -2758,40 +2766,45 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Samichlaus Classic</t>
+          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E49" t="n">
         <v>32.1</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>15.38</v>
+        <v>7.8</v>
       </c>
       <c r="K49" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="L49" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
@@ -2800,45 +2813,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
+          <t>Samichlaus Classic</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>39.8</v>
+        <v>32.1</v>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>7.8</v>
+        <v>15.38</v>
       </c>
       <c r="K50" t="n">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -2847,7 +2855,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
+          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2857,35 +2865,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E51" t="n">
-        <v>42.2</v>
+        <v>39.8</v>
       </c>
       <c r="F51" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>8.130000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="K51" t="n">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="L51" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -2894,7 +2902,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2908,31 +2916,31 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="E52" t="n">
-        <v>58</v>
+        <v>42.2</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>24</v>
+      </c>
+      <c r="I52" t="n">
         <v>4</v>
       </c>
-      <c r="H52" t="n">
-        <v>6</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
       <c r="J52" t="n">
-        <v>9.779999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="L52" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
@@ -2941,37 +2949,45 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Estrella Daura IPA</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1</v>
+        <v>65</v>
+      </c>
+      <c r="E53" t="n">
+        <v>66.3</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>8.5</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="L53" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -2980,42 +2996,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Insight Control Alt Beer 4pk 16oz can</t>
+          <t>Estrella Daura IPA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Craft</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Insight Brewing Company (D)</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>11.53</v>
+        <v>8.5</v>
       </c>
       <c r="K54" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="L54" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -3024,41 +3035,85 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
+          <t>Insight Control Alt Beer 4pk 16oz can</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>Craft</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Insight Brewing Company (D)</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>2.3</v>
+        <v>11.53</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="L55" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Single Serve</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
+      <c r="L56" t="n">
+        <v>34</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3071,7 +3126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3228,28 +3283,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="n">
         <v>133</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H3" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3" t="n">
-        <v>17.04</v>
+        <v>17.02</v>
       </c>
       <c r="K3" t="n">
-        <v>1534</v>
+        <v>1583</v>
       </c>
       <c r="L3" t="n">
         <v>32</v>
@@ -3283,10 +3338,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F4" t="n">
         <v>120</v>
@@ -3301,10 +3356,10 @@
         <v>38</v>
       </c>
       <c r="J4" t="n">
-        <v>17.07</v>
+        <v>17.05</v>
       </c>
       <c r="K4" t="n">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="L4" t="n">
         <v>32</v>
@@ -3338,16 +3393,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F5" t="n">
         <v>156</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>150</v>
@@ -3356,10 +3411,10 @@
         <v>25</v>
       </c>
       <c r="J5" t="n">
-        <v>8.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="L5" t="n">
         <v>37</v>
@@ -3371,6 +3426,61 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>High Noon Lemon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>207</v>
+      </c>
+      <c r="L6" t="n">
+        <v>37</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -3609,10 +3719,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -3627,7 +3737,7 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
       <c r="K5" t="n">
         <v>164</v>
@@ -3699,10 +3809,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="F7" t="n">
         <v>19</v>
@@ -3744,10 +3854,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="F8" t="n">
         <v>14</v>
@@ -3783,7 +3893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3880,16 +3990,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="F2" t="n">
         <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
         <v>42</v>
@@ -3898,10 +4008,10 @@
         <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>8.59</v>
+        <v>8.56</v>
       </c>
       <c r="K2" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
         <v>38</v>
@@ -3930,28 +4040,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>8.460000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="K3" t="n">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="L3" t="n">
         <v>39</v>
@@ -3966,7 +4076,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3980,28 +4090,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>8.65</v>
+        <v>8.69</v>
       </c>
       <c r="K4" t="n">
-        <v>208</v>
+        <v>261</v>
       </c>
       <c r="L4" t="n">
         <v>37</v>
@@ -4016,7 +4126,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4030,31 +4140,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>8.720000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>107</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -4066,7 +4176,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4080,31 +4190,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>54</v>
+      </c>
+      <c r="I6" t="n">
         <v>9</v>
       </c>
-      <c r="H6" t="n">
-        <v>12</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
       <c r="J6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="K6" t="n">
-        <v>106</v>
+        <v>462</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -4116,7 +4226,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4130,31 +4240,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>93</v>
+        <v>399</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="H7" t="n">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="J7" t="n">
-        <v>8.56</v>
+        <v>21.92</v>
       </c>
       <c r="K7" t="n">
-        <v>462</v>
+        <v>1841</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
@@ -4166,7 +4276,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4180,84 +4290,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>34</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="F8" t="n">
-        <v>171</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>22.06</v>
+        <v>8.59</v>
       </c>
       <c r="K8" t="n">
-        <v>1235</v>
+        <v>155</v>
       </c>
       <c r="L8" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>36</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>31</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H9" t="n">
-        <v>18</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="K9" t="n">
-        <v>155</v>
-      </c>
-      <c r="L9" t="n">
-        <v>38</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -4344,7 +4404,7 @@
         <v>-5</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
@@ -4502,7 +4562,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Blaine (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -4609,7 +4669,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -4665,12 +4725,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -4683,11 +4743,11 @@
         <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -4702,19 +4762,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-192.9</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
@@ -4724,11 +4784,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4739,33 +4799,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9</v>
+        <v>-2.3</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Andover (6)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4776,29 +4836,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -4813,33 +4873,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-192.9</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -4970,10 +5030,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7</v>
+        <v>-3.3</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -5131,7 +5191,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -5192,20 +5252,20 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F25" t="n">
         <v>43</v>
       </c>
       <c r="G25" t="n">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Blaine (25), Minneapolis (18)</t>
+          <t>Blaine (18), Minneapolis (16), Bloomington (9)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -5220,7 +5280,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5229,24 +5289,24 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>290</v>
+        <v>221</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bloomington (8), St. Louis Park (5), Vadnais Heights (4)</t>
+          <t>St. Louis Park (13)</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -5266,10 +5326,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="F27" t="n">
         <v>10</v>
@@ -5294,29 +5354,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>St. Louis Park (10)</t>
+          <t>Rosemount (8)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -5343,7 +5403,7 @@
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>9</v>
@@ -5373,28 +5433,28 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Bloomington (8)</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -5405,29 +5465,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Andover (6)</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -5442,29 +5502,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -5479,29 +5539,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -5516,7 +5576,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5525,20 +5585,20 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F34" t="n">
         <v>8</v>
       </c>
-      <c r="E34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>7</v>
-      </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bloomington (7)</t>
+          <t>Bloomington (8)</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -5558,24 +5618,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -5590,33 +5650,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -5627,33 +5687,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
         <v>51</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Andover (6)</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -5664,7 +5724,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5673,24 +5733,24 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bloomington (5)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -5701,12 +5761,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -5719,7 +5779,7 @@
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -5727,7 +5787,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -5738,33 +5798,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Vadnais Heights (5)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5775,103 +5835,103 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="F42" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>375</v>
+        <v>42</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Rosemount (10), Bloomington (7)</t>
+          <t>Woodbury (5)</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Andover (15)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -5881,7 +5941,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5891,61 +5951,61 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="F44" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Osseo (8), Minnetonka (7)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>315</v>
+        <v>31</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Chanhassen (17)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -5960,29 +6020,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G46" t="n">
-        <v>220</v>
+        <v>315</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Chanhassen (17)</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -5997,33 +6057,33 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E47" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="F47" t="n">
         <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Stillwater (8), Minneapolis (4)</t>
+          <t>Andover (12)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -6034,29 +6094,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Rosemount (8)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -6071,29 +6131,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Minneapolis (8), Stillwater (4)</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -6113,24 +6173,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E50" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Rosemount (6)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -6145,33 +6205,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E51" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -6182,29 +6242,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Chanhassen (6)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -6219,7 +6279,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6228,24 +6288,24 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>99</v>
+        <v>2.2</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -6256,29 +6316,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F54" t="n">
         <v>6</v>
       </c>
-      <c r="E54" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>5</v>
-      </c>
       <c r="G54" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Chanhassen (6)</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -6293,33 +6353,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E55" t="n">
-        <v>6.3</v>
+        <v>99</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -6330,33 +6390,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="F56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Osseo (5), Vadnais Heights (4)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6367,29 +6427,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D57" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F57" t="n">
         <v>5</v>
       </c>
-      <c r="E57" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F57" t="n">
-        <v>4</v>
-      </c>
       <c r="G57" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -6404,33 +6464,33 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>99</v>
+        <v>2.2</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G58" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>St. Louis Park (9)</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -6441,33 +6501,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>51.7</v>
+        <v>3.3</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G59" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Osseo (5), Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -6478,29 +6538,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>99</v>
+        <v>3.8</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -6515,33 +6575,33 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>11.9</v>
+        <v>99</v>
       </c>
       <c r="F61" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (6)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -6552,33 +6612,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E62" t="n">
-        <v>2.1</v>
+        <v>51.7</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G62" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bloomington (4), Woodbury (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6589,29 +6649,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>2.2</v>
+        <v>99</v>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cottage Grove (7)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -6626,33 +6686,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E64" t="n">
-        <v>3.1</v>
+        <v>35.7</v>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G64" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Andover (6)</t>
+          <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -6663,29 +6723,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>99</v>
+        <v>2.2</v>
       </c>
       <c r="F65" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Vadnais Heights (27)</t>
+          <t>Cottage Grove (7)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -6700,29 +6760,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 4pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E66" t="n">
-        <v>11.7</v>
+        <v>99</v>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Cottage Grove (6)</t>
+          <t>Vadnais Heights (27)</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -6737,29 +6797,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
+        <v>8</v>
+      </c>
+      <c r="E67" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F67" t="n">
         <v>6</v>
       </c>
-      <c r="E67" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F67" t="n">
-        <v>5</v>
-      </c>
       <c r="G67" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Cottage Grove (6)</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -6774,19 +6834,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="F68" t="n">
         <v>5</v>
@@ -6796,11 +6856,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Woodbury (5)</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6811,33 +6871,33 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E69" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70">
@@ -6848,33 +6908,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6885,7 +6945,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6894,10 +6954,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="F71" t="n">
         <v>5</v>
@@ -6911,7 +6971,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -6922,29 +6982,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>6</v>
       </c>
       <c r="E72" t="n">
-        <v>3.5</v>
+        <v>99</v>
       </c>
       <c r="F72" t="n">
         <v>4</v>
       </c>
       <c r="G72" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>St. Louis Park (4)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -6959,19 +7019,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
         <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>99</v>
+        <v>3.9</v>
       </c>
       <c r="F73" t="n">
         <v>4</v>
@@ -6981,7 +7041,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -6996,33 +7056,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E74" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="F74" t="n">
         <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -7033,33 +7093,33 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F75" t="n">
         <v>6</v>
-      </c>
-      <c r="E75" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F75" t="n">
-        <v>4</v>
       </c>
       <c r="G75" t="n">
         <v>33</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -7070,33 +7130,33 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>14.3</v>
+        <v>4.9</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -7116,10 +7176,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="F77" t="n">
         <v>6</v>
@@ -7181,29 +7241,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E79" t="n">
-        <v>10.2</v>
+        <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G79" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Blaine (5)</t>
+          <t>Cottage Grove (11)</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -7218,33 +7278,33 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E80" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F80" t="n">
         <v>4</v>
-      </c>
-      <c r="F80" t="n">
-        <v>11</v>
       </c>
       <c r="G80" t="n">
         <v>21</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Cottage Grove (11)</t>
+          <t>Osseo (4)</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -7267,7 +7327,7 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="F81" t="n">
         <v>4</v>
@@ -7452,7 +7512,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="F86" t="n">
         <v>5</v>
@@ -7462,7 +7522,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -7536,7 +7596,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Minneapolis (4)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I88" t="n">

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P56"/>
+  <dimension ref="A1:P57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -621,28 +621,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F4" t="n">
         <v>133</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H4" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J4" t="n">
         <v>17.02</v>
       </c>
       <c r="K4" t="n">
-        <v>1583</v>
+        <v>1685</v>
       </c>
       <c r="L4" t="n">
         <v>32</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="F5" t="n">
         <v>21</v>
@@ -709,7 +709,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -719,39 +719,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
         <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="J6" t="n">
-        <v>8.119999999999999</v>
+        <v>17.04</v>
       </c>
       <c r="K6" t="n">
-        <v>244</v>
+        <v>1943</v>
       </c>
       <c r="L6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -803,7 +811,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -817,31 +825,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="J8" t="n">
-        <v>17.05</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1944</v>
+        <v>1345</v>
       </c>
       <c r="L8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
@@ -905,7 +913,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -919,28 +927,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F10" t="n">
-        <v>156</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
-        <v>150</v>
-      </c>
-      <c r="I10" t="n">
-        <v>25</v>
-      </c>
       <c r="J10" t="n">
-        <v>8.619999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1293</v>
+        <v>207</v>
       </c>
       <c r="L10" t="n">
         <v>37</v>
@@ -960,7 +968,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -974,31 +982,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>8.630000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>207</v>
+        <v>405</v>
       </c>
       <c r="L11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -1015,7 +1023,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>Two Chicks New Fashioned 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1029,31 +1037,31 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F12" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
       <c r="J12" t="n">
-        <v>9.75</v>
+        <v>7.88</v>
       </c>
       <c r="K12" t="n">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="L12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1062,7 +1070,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1072,35 +1080,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>12</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
       <c r="J13" t="n">
-        <v>10.33</v>
+        <v>9.75</v>
       </c>
       <c r="K13" t="n">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="L13" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1109,7 +1117,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Two Chicks New Fashioned 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1119,44 +1127,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>7.86</v>
+        <v>18.53</v>
       </c>
       <c r="K14" t="n">
-        <v>142</v>
+        <v>222</v>
       </c>
       <c r="L14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1170,31 +1182,31 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>7.72</v>
+        <v>12.2</v>
       </c>
       <c r="K15" t="n">
-        <v>371</v>
+        <v>110</v>
       </c>
       <c r="L15" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1203,7 +1215,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1220,28 +1232,28 @@
         <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>12.26</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1250,7 +1262,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1264,44 +1276,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>12</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>18.53</v>
+        <v>10.33</v>
       </c>
       <c r="K17" t="n">
-        <v>222</v>
+        <v>124</v>
       </c>
       <c r="L17" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1315,31 +1323,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>9.75</v>
+        <v>7.72</v>
       </c>
       <c r="K18" t="n">
-        <v>292</v>
+        <v>371</v>
       </c>
       <c r="L18" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1348,7 +1356,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1358,35 +1366,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>8.039999999999999</v>
+        <v>7.58</v>
       </c>
       <c r="K19" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="L19" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1395,7 +1403,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1409,31 +1417,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="F20" t="n">
+        <v>35</v>
+      </c>
+      <c r="G20" t="n">
         <v>6</v>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>7.17</v>
+        <v>9.75</v>
       </c>
       <c r="K20" t="n">
-        <v>43</v>
+        <v>292</v>
       </c>
       <c r="L20" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1442,7 +1450,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bacardi Mojito 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1456,31 +1464,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>8.119999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="K21" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="L21" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1489,7 +1497,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1499,20 +1507,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>12</v>
@@ -1521,13 +1529,13 @@
         <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>8.19</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1550,10 +1558,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="F23" t="n">
         <v>33</v>
@@ -1568,7 +1576,7 @@
         <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>7.68</v>
+        <v>7.67</v>
       </c>
       <c r="K23" t="n">
         <v>184</v>
@@ -1583,7 +1591,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1593,48 +1601,44 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="F24" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="K24" t="n">
         <v>48</v>
       </c>
-      <c r="H24" t="n">
-        <v>12</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="K24" t="n">
-        <v>220</v>
-      </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ole Smoky Blackberry Lemonade 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1644,44 +1648,48 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H25" t="n">
         <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>9.720000000000001</v>
+        <v>18.34</v>
       </c>
       <c r="K25" t="n">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="L25" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1691,35 +1699,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>19</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>16</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" t="n">
         <v>12</v>
       </c>
-      <c r="E26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F26" t="n">
-        <v>7</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>6</v>
-      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>7.15</v>
+        <v>8.19</v>
       </c>
       <c r="K26" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="L26" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1728,7 +1736,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1738,20 +1746,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
@@ -1766,7 +1774,7 @@
         <v>43</v>
       </c>
       <c r="L27" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1775,7 +1783,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Bacardi Mojito 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1785,20 +1793,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>6</v>
@@ -1807,13 +1815,13 @@
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>7.56</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L28" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -1822,7 +1830,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1832,35 +1840,35 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>6</v>
       </c>
-      <c r="H29" t="n">
-        <v>12</v>
-      </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>5.55</v>
+        <v>7.15</v>
       </c>
       <c r="K29" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="L29" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -1869,7 +1877,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1883,31 +1891,31 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>8.02</v>
       </c>
       <c r="E30" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>12.88</v>
+        <v>6.45</v>
       </c>
       <c r="K30" t="n">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -1916,45 +1924,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="E31" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="F31" t="n">
+        <v>11</v>
+      </c>
+      <c r="G31" t="n">
         <v>7</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.92</v>
+        <v>7.56</v>
       </c>
       <c r="K31" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="L31" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -1963,7 +1971,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1973,86 +1981,82 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="F32" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>16.88</v>
+        <v>12.88</v>
       </c>
       <c r="K32" t="n">
-        <v>861</v>
+        <v>193</v>
       </c>
       <c r="L32" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9.02</v>
+        <v>126</v>
       </c>
       <c r="E33" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>6.44</v>
+        <v>1.92</v>
       </c>
       <c r="K33" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="L33" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2061,7 +2065,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2071,35 +2075,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E34" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>7.79</v>
+        <v>5.55</v>
       </c>
       <c r="K34" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="L34" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2108,7 +2112,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2122,40 +2126,44 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="E35" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>10.33</v>
+        <v>16.88</v>
       </c>
       <c r="K35" t="n">
-        <v>124</v>
+        <v>962</v>
       </c>
       <c r="L35" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2165,35 +2173,35 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E36" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="K36" t="n">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c r="L36" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
@@ -2202,7 +2210,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2212,35 +2220,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E37" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>7.58</v>
+        <v>5.38</v>
       </c>
       <c r="K37" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="L37" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
@@ -2249,7 +2257,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2259,35 +2267,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>5.33</v>
+        <v>7.79</v>
       </c>
       <c r="K38" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="L38" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
@@ -2296,45 +2304,45 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="F39" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>12</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>8.6</v>
+        <v>10.33</v>
       </c>
       <c r="K39" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
@@ -2343,45 +2351,45 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
-        <v>7.57</v>
+        <v>4.5</v>
       </c>
       <c r="K40" t="n">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="L40" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
@@ -2404,10 +2412,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E41" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="F41" t="n">
         <v>7</v>
@@ -2422,13 +2430,13 @@
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>7.58</v>
+        <v>7.83</v>
       </c>
       <c r="K41" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L41" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -2437,7 +2445,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2447,35 +2455,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="E42" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>6.94</v>
+        <v>7.57</v>
       </c>
       <c r="K42" t="n">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="L42" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -2484,7 +2492,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2494,14 +2502,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E43" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="F43" t="n">
         <v>16</v>
@@ -2516,13 +2524,13 @@
         <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="K43" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="L43" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -2531,45 +2539,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="E44" t="n">
-        <v>9.9</v>
+        <v>7.7</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>1.87</v>
+        <v>7.5</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="L44" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -2578,7 +2586,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2588,35 +2596,35 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="E45" t="n">
-        <v>10.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="G45" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H45" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K45" t="n">
         <v>2</v>
       </c>
-      <c r="J45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K45" t="n">
-        <v>108</v>
-      </c>
       <c r="L45" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -2625,12 +2633,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2639,31 +2647,31 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E46" t="n">
-        <v>14.1</v>
+        <v>10.7</v>
       </c>
       <c r="F46" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="K46" t="n">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="L46" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -2686,28 +2694,28 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>18.4</v>
+        <v>12.2</v>
       </c>
       <c r="F47" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
         <v>15.55</v>
       </c>
       <c r="K47" t="n">
-        <v>373</v>
+        <v>327</v>
       </c>
       <c r="L47" t="n">
         <v>35</v>
@@ -2719,7 +2727,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Saint Spritz Sicily 4pk 355ml</t>
+          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2733,31 +2741,31 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E48" t="n">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>10.33</v>
+        <v>7.8</v>
       </c>
       <c r="K48" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="L48" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -2780,10 +2788,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>32.1</v>
+        <v>22.9</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
@@ -2813,40 +2821,45 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Samichlaus Classic</t>
+          <t>Saint Spritz Sicily 4pk 355ml</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E50" t="n">
-        <v>32.1</v>
+        <v>23.1</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>15.38</v>
+        <v>10.33</v>
       </c>
       <c r="K50" t="n">
+        <v>124</v>
+      </c>
+      <c r="L50" t="n">
         <v>31</v>
-      </c>
-      <c r="L50" t="n">
-        <v>27</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
@@ -2855,45 +2868,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
+          <t>Samichlaus Classic</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>39.8</v>
+        <v>32.1</v>
       </c>
       <c r="F51" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
         <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>7.8</v>
+        <v>15.38</v>
       </c>
       <c r="K51" t="n">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
@@ -2916,10 +2924,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E52" t="n">
-        <v>42.2</v>
+        <v>37.8</v>
       </c>
       <c r="F52" t="n">
         <v>26</v>
@@ -2949,7 +2957,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2959,35 +2967,35 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="E53" t="n">
-        <v>66.3</v>
+        <v>39.8</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>9.779999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="K53" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="L53" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
@@ -2996,37 +3004,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Estrella Daura IPA</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-1</v>
+        <v>65</v>
+      </c>
+      <c r="E54" t="n">
+        <v>77.40000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>8.5</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="L54" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
@@ -3035,42 +3051,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Insight Control Alt Beer 4pk 16oz can</t>
+          <t>Estrella Daura IPA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Craft</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Insight Brewing Company (D)</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>11.53</v>
+        <v>8.5</v>
       </c>
       <c r="K55" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="L55" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -3079,41 +3090,85 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
+          <t>Insight Control Alt Beer 4pk 16oz can</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>Craft</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Insight Brewing Company (D)</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>2.3</v>
+        <v>11.53</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="L56" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sierra Nevada Atomic Torpedo19.2oz can</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Single Serve</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="n">
+        <v>34</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3126,7 +3181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,28 +3338,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F3" t="n">
         <v>133</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J3" t="n">
         <v>17.02</v>
       </c>
       <c r="K3" t="n">
-        <v>1583</v>
+        <v>1685</v>
       </c>
       <c r="L3" t="n">
         <v>32</v>
@@ -3338,10 +3393,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="F4" t="n">
         <v>120</v>
@@ -3356,10 +3411,10 @@
         <v>38</v>
       </c>
       <c r="J4" t="n">
-        <v>17.05</v>
+        <v>17.04</v>
       </c>
       <c r="K4" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="L4" t="n">
         <v>32</v>
@@ -3393,28 +3448,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="n">
         <v>156</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1293</v>
+        <v>1345</v>
       </c>
       <c r="L5" t="n">
         <v>37</v>
@@ -3448,10 +3503,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
@@ -3481,6 +3536,61 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>55</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>405</v>
+      </c>
+      <c r="L7" t="n">
+        <v>39</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -3589,10 +3699,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>49.3</v>
+        <v>38.1</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -3607,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>8.56</v>
+        <v>8.57</v>
       </c>
       <c r="K2" t="n">
         <v>51</v>
@@ -3719,10 +3829,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -3764,10 +3874,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="F6" t="n">
         <v>11</v>
@@ -3809,28 +3919,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="F7" t="n">
         <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
       <c r="K7" t="n">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="L7" t="n">
         <v>49</v>
@@ -3893,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3990,10 +4100,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="F2" t="n">
         <v>63</v>
@@ -4011,7 +4121,7 @@
         <v>8.56</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L2" t="n">
         <v>38</v>
@@ -4026,7 +4136,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4040,31 +4150,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>8.44</v>
+        <v>8.68</v>
       </c>
       <c r="K3" t="n">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="L3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -4076,7 +4186,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4090,31 +4200,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>8.69</v>
+        <v>8.9</v>
       </c>
       <c r="K4" t="n">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
@@ -4126,7 +4236,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4140,31 +4250,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>54</v>
+      </c>
+      <c r="I5" t="n">
         <v>9</v>
       </c>
-      <c r="H5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
       <c r="J5" t="n">
-        <v>8.9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>107</v>
+        <v>462</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
@@ -4176,7 +4286,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4190,31 +4300,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>86</v>
+        <v>370</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>171</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="J6" t="n">
-        <v>8.56</v>
+        <v>21.83</v>
       </c>
       <c r="K6" t="n">
-        <v>462</v>
+        <v>2096</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
@@ -4226,7 +4336,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4240,84 +4350,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>399</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="F7" t="n">
-        <v>171</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="I7" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>21.92</v>
+        <v>8.58</v>
       </c>
       <c r="K7" t="n">
-        <v>1841</v>
+        <v>154</v>
       </c>
       <c r="L7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (May, Aug)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>34</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>31</v>
-      </c>
-      <c r="G8" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" t="n">
-        <v>18</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="K8" t="n">
-        <v>155</v>
-      </c>
-      <c r="L8" t="n">
-        <v>38</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -4334,7 +4394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4515,7 +4575,7 @@
         <v>-5</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -4558,7 +4618,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -4589,7 +4649,7 @@
         <v>-1</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
@@ -4688,29 +4748,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-20.3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -4725,29 +4785,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-20.3</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -4762,12 +4822,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4780,11 +4840,11 @@
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -4799,29 +4859,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -4836,12 +4896,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Traditional 6pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -4851,18 +4911,18 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4873,33 +4933,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E15" t="n">
-        <v>-192.9</v>
+        <v>-2.5</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5021,33 +5081,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3</v>
+        <v>-20.9</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Minneapolis (4)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -5058,29 +5118,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monaco Tropic Rush 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="E20" t="n">
-        <v>99</v>
+        <v>-3.7</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Minneapolis (15)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -5100,24 +5160,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Monaco Tropic Rush 12oz can</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E21" t="n">
         <v>99</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Minneapolis (11)</t>
+          <t>Minneapolis (15)</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -5132,7 +5192,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5141,20 +5201,20 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.6</v>
+        <v>99</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Minneapolis (11)</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -5169,19 +5229,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="E23" t="n">
-        <v>99</v>
+        <v>-6.6</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -5191,7 +5251,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -5211,24 +5271,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Tequila Lime Crush 12oz can</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5</v>
+        <v>99</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -5238,34 +5298,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>-2</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6</v>
+        <v>-2.5</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>942</v>
+        <v>8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Blaine (18), Minneapolis (16), Bloomington (9)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -5280,29 +5340,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
-        <v>221</v>
+        <v>939</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>St. Louis Park (13)</t>
+          <t>Minneapolis (14), Bloomington (13), Andover (12), Rosemount (4)</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -5317,29 +5377,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>183</v>
+        <v>315</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Plymouth (10)</t>
+          <t>Chanhassen (17)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -5354,29 +5414,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rosemount (8)</t>
+          <t>Bloomington (7), St. Louis Park (6)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -5391,7 +5451,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5403,17 +5463,17 @@
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Plymouth (9)</t>
+          <t>Plymouth (10)</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -5428,33 +5488,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bloomington (8)</t>
+          <t>Blaine (8)</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -5465,29 +5525,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Andover (6)</t>
+          <t>Plymouth (9)</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -5502,29 +5562,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Andover (6)</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -5539,29 +5599,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -5576,7 +5636,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5585,24 +5645,24 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>77</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Osseo (5), Vadnais Heights (4)</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>3</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F34" t="n">
-        <v>8</v>
-      </c>
-      <c r="G34" t="n">
-        <v>68</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bloomington (8)</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -5613,29 +5673,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Bloomington (8)</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -5650,19 +5710,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="F36" t="n">
         <v>4</v>
@@ -5672,11 +5732,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -5687,33 +5747,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>68</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (4)</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>6</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>6</v>
-      </c>
-      <c r="G37" t="n">
-        <v>51</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Andover (6)</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -5729,14 +5789,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F38" t="n">
         <v>6</v>
@@ -5746,7 +5806,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Andover (6)</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -5798,19 +5858,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
@@ -5820,7 +5880,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Vadnais Heights (5)</t>
+          <t>Woodbury (5)</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -5835,33 +5895,33 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="F41" t="n">
         <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Vadnais Heights (5)</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -5877,28 +5937,28 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Woodbury (5)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -5909,7 +5969,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5918,24 +5978,24 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -5955,10 +6015,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -5992,10 +6052,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -6020,33 +6080,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E46" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="F46" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>315</v>
+        <v>262</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Chanhassen (17)</t>
+          <t>Rosemount (8), Blaine (4)</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -6057,33 +6117,33 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="F47" t="n">
         <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Andover (12)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -6094,29 +6154,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="F48" t="n">
         <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Minneapolis (8), Stillwater (4)</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -6131,7 +6191,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6140,20 +6200,20 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Minneapolis (8), Stillwater (4)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -6168,29 +6228,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="F50" t="n">
         <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Rosemount (6)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -6205,33 +6265,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Chanhassen (6)</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -6242,33 +6302,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E52" t="n">
-        <v>3.7</v>
+        <v>99</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -6279,29 +6339,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D53" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F53" t="n">
         <v>5</v>
       </c>
-      <c r="E53" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F53" t="n">
-        <v>6</v>
-      </c>
       <c r="G53" t="n">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -6321,28 +6381,28 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
         <v>2.2</v>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G54" t="n">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Chanhassen (6)</t>
+          <t>St. Louis Park (9)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -6353,7 +6413,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6362,24 +6422,24 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>99</v>
+        <v>2.7</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6390,29 +6450,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>5.1</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -6427,29 +6487,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="E57" t="n">
-        <v>7.4</v>
+        <v>43.7</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -6469,28 +6529,28 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>2.2</v>
+        <v>99</v>
       </c>
       <c r="F58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>St. Louis Park (9)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -6501,33 +6561,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>3.3</v>
+        <v>35.7</v>
       </c>
       <c r="F59" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G59" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Osseo (5), Vadnais Heights (4)</t>
+          <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -6538,29 +6598,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G60" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Roseville (7)</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -6575,29 +6635,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E61" t="n">
         <v>99</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G61" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Vadnais Heights (27)</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -6612,29 +6672,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>51.7</v>
+        <v>11.7</v>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Cottage Grove (6)</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -6649,29 +6709,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>99</v>
+        <v>4.7</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -6686,33 +6746,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E64" t="n">
-        <v>35.7</v>
+        <v>3.5</v>
       </c>
       <c r="F64" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (6)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -6723,29 +6783,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>2.2</v>
+        <v>99</v>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Cottage Grove (7)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -6760,29 +6820,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>99</v>
+        <v>2.9</v>
       </c>
       <c r="F66" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Vadnais Heights (27)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -6797,33 +6857,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E67" t="n">
-        <v>11.7</v>
+        <v>7.1</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Cottage Grove (6)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
@@ -6834,29 +6894,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F68" t="n">
         <v>6</v>
       </c>
-      <c r="E68" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F68" t="n">
-        <v>5</v>
-      </c>
       <c r="G68" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Woodbury (5)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -6876,28 +6936,28 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -6908,33 +6968,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D70" t="n">
+        <v>11</v>
+      </c>
+      <c r="E70" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>6</v>
+      </c>
+      <c r="G70" t="n">
+        <v>32</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>St. Louis Park (6)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
         <v>3</v>
-      </c>
-      <c r="E70" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F70" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" t="n">
-        <v>39</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Minnetonka (4)</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6945,33 +7005,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E71" t="n">
-        <v>3.5</v>
+        <v>10.2</v>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -6982,29 +7042,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E72" t="n">
-        <v>99</v>
+        <v>4.1</v>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G72" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Cottage Grove (11)</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -7019,29 +7079,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="F73" t="n">
         <v>4</v>
       </c>
       <c r="G73" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -7056,33 +7116,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E74" t="n">
-        <v>7.1</v>
+        <v>99</v>
       </c>
       <c r="F74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7093,25 +7153,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>14.3</v>
+        <v>7.2</v>
       </c>
       <c r="F75" t="n">
         <v>6</v>
       </c>
       <c r="G75" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -7135,28 +7195,28 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>99</v>
+      </c>
+      <c r="F76" t="n">
         <v>6</v>
       </c>
-      <c r="E76" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F76" t="n">
-        <v>4</v>
-      </c>
       <c r="G76" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -7167,33 +7227,33 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>5.8</v>
+        <v>26.8</v>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>St. Louis Park (6)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -7204,29 +7264,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G78" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -7241,29 +7301,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Lemonade 12oz can</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F79" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Cottage Grove (11)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -7278,33 +7338,33 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>10.2</v>
+        <v>99</v>
       </c>
       <c r="F80" t="n">
         <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Osseo (4)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -7315,328 +7375,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>2.9</v>
+        <v>32.1</v>
       </c>
       <c r="F81" t="n">
         <v>4</v>
       </c>
       <c r="G81" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Osseo</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Monaco Mango Peach 12oz can</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10</v>
-      </c>
-      <c r="E82" t="n">
-        <v>99</v>
-      </c>
-      <c r="F82" t="n">
-        <v>6</v>
-      </c>
-      <c r="G82" t="n">
-        <v>11</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Minneapolis (6)</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Andover</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10</v>
-      </c>
-      <c r="E83" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F83" t="n">
-        <v>6</v>
-      </c>
-      <c r="G83" t="n">
-        <v>11</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (6)</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Blaine</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10</v>
-      </c>
-      <c r="E84" t="n">
-        <v>99</v>
-      </c>
-      <c r="F84" t="n">
-        <v>6</v>
-      </c>
-      <c r="G84" t="n">
-        <v>11</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (6)</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Monaco Citrus Rush 12oz can</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>5</v>
-      </c>
-      <c r="E85" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F85" t="n">
-        <v>5</v>
-      </c>
-      <c r="G85" t="n">
-        <v>10</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Cottage Grove (5)</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Monaco Mai Tai 12oz can</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F86" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" t="n">
-        <v>10</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Minneapolis (5)</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Osseo</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Monaco Lemonade 12oz can</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>13</v>
-      </c>
-      <c r="E87" t="n">
-        <v>99</v>
-      </c>
-      <c r="F87" t="n">
-        <v>5</v>
-      </c>
-      <c r="G87" t="n">
-        <v>9</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Minneapolis (5)</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Blaine</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Monaco Mai Tai 12oz can</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>4</v>
-      </c>
-      <c r="E88" t="n">
-        <v>99</v>
-      </c>
-      <c r="F88" t="n">
-        <v>4</v>
-      </c>
-      <c r="G88" t="n">
-        <v>8</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (4)</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Monaco Purple Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>3</v>
-      </c>
-      <c r="E89" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F89" t="n">
-        <v>4</v>
-      </c>
-      <c r="G89" t="n">
-        <v>8</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:Q57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,75 +428,80 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Chain OH (TOH)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>WOS</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -510,48 +515,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>085000432563</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>-5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>12</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>8.73</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>105</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>37</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -565,44 +574,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>089540535319</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.6</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>6.45</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>77</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>48</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,48 +623,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>085000031513</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>70</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1.1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>133</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>33</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>99</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>33</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>17.02</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>1685</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>32</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -667,44 +682,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>050200003486</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1.3</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>21</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>21</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>7</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>15.46</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>325</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>36</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -714,48 +731,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>085000032558</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>72</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>120</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>6</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>114</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>38</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>17.04</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>1943</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>32</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -769,44 +790,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>080480985448</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>8.119999999999999</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>49</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>41</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -816,48 +839,52 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>085000429266</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>85</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1.6</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>156</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>156</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>26</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1345</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>37</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -871,44 +898,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>850003574233</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>11</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1.7</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>11</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>12</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>13.55</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>163</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>41</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -918,48 +947,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>085000434260</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>14</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1.7</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>24</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>24</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>8.630000000000001</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>207</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>37</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -973,48 +1006,52 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>085000426272</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>55</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1.8</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>60</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>15</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>48</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>405</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>39</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -1028,44 +1065,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>850003574103</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>14</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>16</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>18</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>7.88</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>142</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>39</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1075,44 +1114,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>616003648011</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>2.1</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>7</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>6</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>9.75</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>58</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>35</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1122,48 +1163,51 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>43</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>2.3</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>74</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>62</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>12</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>18.53</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>222</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>38</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>In buy-month (Jun)</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1173,44 +1217,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>850003574172</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>13</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>2.3</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>8</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>12.2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>110</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>47</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1220,44 +1266,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>050200003295</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>14</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>2.3</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>29</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>24</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>8.119999999999999</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>195</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>29</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1267,44 +1315,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>197644216758</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>2.3</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>12</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>12</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>10.33</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>124</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>31</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1314,44 +1364,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>850003574066</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>45</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>2.7</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>54</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>48</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>8</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>7.72</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>371</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>41</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1361,44 +1413,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>891278002717</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>2.9</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>5</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>5</v>
       </c>
       <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
         <v>7.58</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>38</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>39</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1408,44 +1462,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>616003203135</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>18</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>3.1</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>35</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>6</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>30</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>9.75</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>292</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>35</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1455,44 +1511,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>089540535661</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>12</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>3.3</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>11</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>12</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>7.17</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>86</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>43</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1502,44 +1560,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>853915008728</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>13</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>3.4</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>11</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>12</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>117</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>35</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1549,44 +1609,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>850003574028</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>54</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>3.5</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>33</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>9</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>24</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>4</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>7.67</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>184</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>41</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1596,44 +1658,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>080432000779</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>3.9</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>4</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>6</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>48</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>46</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1643,48 +1707,51 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>085000037393</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>67</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>59</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>48</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>12</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>4</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>18.34</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>220</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>39</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>In buy-month (Jun)</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1694,44 +1761,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>850003574110</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>19</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>4.1</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>16</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>4</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>12</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>2</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>8.19</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>98</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>37</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1741,44 +1810,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>850003574288</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>15</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>4.1</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>6</v>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>6</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>7.17</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>43</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>45</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1788,44 +1859,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>080480986285</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>13</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>4.1</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>4</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>6</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>8.119999999999999</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>49</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>41</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1835,44 +1908,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>089540535685</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>12</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>4.3</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>7</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
       <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>6</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>7.15</v>
-      </c>
-      <c r="K29" t="n">
-        <v>43</v>
       </c>
       <c r="L29" t="n">
         <v>43</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1882,44 +1957,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>089540535289</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>8.02</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>4.4</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>6</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>6.45</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>39</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>48</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1929,44 +2006,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>891278002380</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>67</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>4.5</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>11</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>7</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>6</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>7.56</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>45</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>39</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1976,44 +2055,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>080432001257</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>10</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>4.7</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>16</v>
       </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>15</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>5</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>12.88</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>193</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>46</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2023,44 +2104,46 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>891278002458</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>Single Serve</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>126</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>4.8</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>7</v>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
         <v>12</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>1.92</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>23</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>45</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2070,44 +2153,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>850003574042</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>32</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>4.9</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>18</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>6</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>12</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>5.55</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>67</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>57</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2117,48 +2202,51 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>085000038963</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>96</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>5.1</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>84</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>28</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>57</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>19</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>16.88</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>962</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>32</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>In buy-month (Jun)</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2168,44 +2256,46 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>080686008064</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Single Serve</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>22</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>5.3</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>19</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>4</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>12</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>8.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>103</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>38</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2215,44 +2305,46 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>850003574202</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>42</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>5.6</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>25</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>10</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>12</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>2</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>5.38</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>65</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>59</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2262,44 +2354,46 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>082000799894</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>5.7</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>5</v>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
       <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>6</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>7.79</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>47</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>43</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2309,44 +2403,46 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>196852401789</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>5</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>5.7</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>12</v>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>12</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>2</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>10.33</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>124</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>31</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2356,44 +2452,46 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>085000034491</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Single Serve</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>10</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>5.8</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>40</v>
       </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>36</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>3</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>4.5</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>162</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>44</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2403,44 +2501,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>850003574264</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>28</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>6.9</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>7</v>
       </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>6</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>7.83</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>47</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>40</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2450,44 +2550,46 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>891278002311</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>67</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>7</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>8</v>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>6</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>7.57</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>45</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>39</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2497,44 +2599,46 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>850003574196</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>35</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>7.2</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>16</v>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>18</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>3</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>6.9</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>124</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>47</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2544,44 +2648,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>860007263392</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>31</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>7.7</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>16</v>
       </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>18</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>3</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>7.5</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>135</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>40</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2591,44 +2697,46 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>891278002335</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>Single Serve</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>66</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>7</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>6</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
         <v>1.87</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>2</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>46</v>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2638,44 +2746,46 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>085000034484</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Single Serve</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>33</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>10.7</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>47</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>20</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>24</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>2</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>4.5</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>108</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>44</v>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2685,44 +2795,46 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>050200006050</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>4</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>12.2</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>22</v>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
         <v>21</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>7</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>15.55</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>327</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>35</v>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2732,44 +2844,46 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>082000799931</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>12</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>15.4</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>6</v>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>6</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>7.8</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>47</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>43</v>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2779,44 +2893,46 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>082000799955</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>16</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>22.9</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>5</v>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
       <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>6</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>7.8</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>47</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>43</v>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2826,44 +2942,46 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>197644897254</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>18</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>23.1</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>12</v>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
       <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>12</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>2</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>10.33</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>124</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>31</v>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2873,39 +2991,41 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>9009100000669</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>1</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>32.1</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>2</v>
       </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>2</v>
       </c>
       <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="n">
         <v>15.38</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>31</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>27</v>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2915,44 +3035,46 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>050200003578</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>20</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>37.8</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>26</v>
       </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>24</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>4</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>195</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>35</v>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2962,44 +3084,46 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>082000799917</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>13</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>39.8</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>10</v>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
       <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>12</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>2</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>7.8</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>94</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>43</v>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3009,44 +3133,46 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>850019260588</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>65</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>8</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>4</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>6</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>9.779999999999999</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>59</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>48</v>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3056,36 +3182,38 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>050648491609</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>-1</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>1</v>
       </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
       </c>
       <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
         <v>8.5</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>8</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>29</v>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3095,41 +3223,43 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>850033550160</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>Craft</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Insight Brewing Company (D)</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>-5</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>6</v>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
       <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
         <v>6</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>1</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>11.53</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>69</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>32</v>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3139,36 +3269,38 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>083783381085</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>Single Serve</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>-4</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>1</v>
       </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
       </c>
       <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
         <v>2.3</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>2</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>34</v>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3181,7 +3313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3192,75 +3324,80 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Chain OH (TOH)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>WOS</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -3274,48 +3411,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>085000432563</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>-5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>12</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>8.73</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>105</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>37</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -3329,48 +3470,52 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>085000031513</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>70</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1.1</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>133</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>33</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>99</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>33</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>17.02</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1685</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>32</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -3384,48 +3529,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>085000032558</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>72</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>120</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>114</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>38</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>17.04</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>1943</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>32</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -3439,48 +3588,52 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>085000429266</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>85</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1.6</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>156</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>156</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>26</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>8.619999999999999</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1345</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>37</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -3494,48 +3647,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>085000434260</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>14</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1.7</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>24</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>24</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>4</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>8.630000000000001</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>207</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>37</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -3549,48 +3706,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>085000426272</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>55</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1.8</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>60</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>15</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>48</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>405</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>39</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -3607,7 +3768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3618,65 +3779,70 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Chain OH (TOH)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>WOS</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
@@ -3690,42 +3856,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>082184006870</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>38.1</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>8.57</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>51</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>39</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3735,42 +3905,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>082184006887</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>18.4</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>9</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>7.82</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>94</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>44</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3780,37 +3954,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>088076185074</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>128.6</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
       </c>
       <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>7.22</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>36</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>52</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3820,42 +3998,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>860272001484</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>14</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>16</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>10.22</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>164</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>49</v>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3865,42 +4047,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>860272001477</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1.4</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>11</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>12</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>10.52</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>126</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>56</v>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3910,42 +4096,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>860272001446</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>24</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2.1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>19</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>20</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>10.22</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>204</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>49</v>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3955,42 +4145,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>860272001439</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>25</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>5.1</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>14</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>10.26</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>82</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>49</v>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4003,7 +4197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4014,70 +4208,75 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Chain OH (TOH)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>WOS</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
@@ -4091,43 +4290,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>085000429273</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>78</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>3.3</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>63</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>23</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>42</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>7</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>8.56</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>360</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>38</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -4141,43 +4344,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>085000430958</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>73</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>3.7</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>70</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>42</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>30</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>8.68</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>260</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>37</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -4191,43 +4398,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>085000432327</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>2.2</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>22</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>9</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>8.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>107</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>35</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -4241,43 +4452,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>085000431375</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>80</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2.9</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>72</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>16</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>54</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>9</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>462</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>38</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -4291,43 +4506,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>085000029862</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>370</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>171</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>74</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>96</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>48</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>21.83</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2096</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>34</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -4341,43 +4560,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>085000429259</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>RTD</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>33</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>3.6</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>31</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>18</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>8.58</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>154</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>38</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
         </is>
@@ -4394,7 +4617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4415,30 +4638,35 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Product Code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>To OH</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>To WOS</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Transfer In</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Value $</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Then Buy</t>
         </is>
@@ -4460,24 +4688,29 @@
           <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>085000031513</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>-5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-4</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>204</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Bloomington (12)</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4497,24 +4730,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>-4</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>8</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>148</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Chanhassen (8)</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4534,24 +4772,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>-43</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>99</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>130</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Blaine (7)</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4571,24 +4814,29 @@
           <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>085000430958</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>-5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-2</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>14</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>122</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>St. Louis Park (14)</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4608,24 +4856,29 @@
           <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>085000029862</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>-3</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>109</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Minneapolis (5)</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4645,24 +4898,29 @@
           <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>085000032558</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>-1</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>6</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>102</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Bloomington (6)</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4682,24 +4940,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>-2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>-21.4</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>93</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Chanhassen (5)</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4719,24 +4982,29 @@
           <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>085000426272</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>-8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>10</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>84</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Bloomington (10)</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4756,24 +5024,29 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>085000037393</t>
+        </is>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>73</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Plymouth (4)</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4793,24 +5066,29 @@
           <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>085000031513</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>-12</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-20.3</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>68</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Bloomington (4)</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4830,24 +5108,29 @@
           <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>616003203135</t>
+        </is>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>6</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>58</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Plymouth (6)</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4867,24 +5150,29 @@
           <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>085000430958</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>6</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>52</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Bloomington (6)</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4904,24 +5192,29 @@
           <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>085000431375</t>
+        </is>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>6</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>51</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Bloomington (6)</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4941,24 +5234,29 @@
           <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>085000432327</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>-4</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>44</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>St. Louis Park (5)</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4978,24 +5276,29 @@
           <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>085000429259</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>-7</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>4</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>34</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Cottage Grove (4)</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5015,24 +5318,29 @@
           <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>085000429259</t>
+        </is>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>4</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>34</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Rosemount (4)</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5052,24 +5360,29 @@
           <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>080686008064</t>
+        </is>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>99</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>4</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>34</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Minnetonka (4)</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5089,24 +5402,29 @@
           <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>050200003295</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>-13</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>-20.9</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>32</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Bloomington (4)</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5126,24 +5444,29 @@
           <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>850003574066</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>-4</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>-3.7</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>4</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>31</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Minneapolis (4)</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5163,24 +5486,29 @@
           <t>Monaco Tropic Rush 12oz can</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>891278002762</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>-1</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>99</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>15</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>29</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Minneapolis (15)</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5200,24 +5528,29 @@
           <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>891278003219</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>-3</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>99</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>11</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>21</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Minneapolis (11)</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5237,24 +5570,29 @@
           <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>891278003219</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
         <v>-11</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>-6.6</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>5</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>9</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Minneapolis (5)</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5274,24 +5612,29 @@
           <t>Monaco Tequila Lime Crush 12oz can</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>891278002373</t>
+        </is>
       </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>99</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>5</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>9</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>St. Louis Park (5)</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5311,24 +5654,29 @@
           <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>891278002298</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
         <v>-2</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>4</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>8</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Cottage Grove (4)</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5348,24 +5696,29 @@
           <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>085000029862</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>36</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>1.2</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>43</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>939</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Minneapolis (14), Bloomington (13), Andover (12), Rosemount (4)</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5385,24 +5738,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
         <v>9</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>1.7</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>17</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>315</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Chanhassen (17)</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5422,24 +5780,29 @@
           <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>085000031513</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>0.1</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>13</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>221</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Bloomington (7), St. Louis Park (6)</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5459,24 +5822,29 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>085000037393</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
         <v>5</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0.9</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>10</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>183</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Plymouth (10)</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5496,24 +5864,29 @@
           <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>085000029862</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
         <v>12</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>1.6</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>175</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Blaine (8)</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5533,24 +5906,29 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>085000037393</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
         <v>4</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>0.8</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>9</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>165</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Plymouth (9)</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5570,24 +5948,29 @@
           <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>085000029862</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>0.1</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>6</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>131</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Andover (6)</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5607,24 +5990,29 @@
           <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>085000038963</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>3</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>1.8</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>5</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>84</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Stillwater (5)</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5644,24 +6032,29 @@
           <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>085000429273</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
         <v>7</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>2</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>9</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>77</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Osseo (5), Vadnais Heights (4)</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5681,24 +6074,29 @@
           <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>085000429273</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
         <v>3</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>0.6</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>8</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>69</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Bloomington (8)</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5718,24 +6116,29 @@
           <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>085000038963</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.5</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>68</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Stillwater (4)</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5755,24 +6158,29 @@
           <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>085000031513</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>4</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>0.5</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>4</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>68</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Vadnais Heights (4)</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5792,24 +6200,29 @@
           <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>085000429273</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>4</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>0.7</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>6</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>51</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Andover (6)</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5829,24 +6242,29 @@
           <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>860272001439</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>0.4</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>5</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>51</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Minnetonka (5)</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5866,24 +6284,29 @@
           <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>085000430958</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
         <v>4</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>1.4</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>5</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>43</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Woodbury (5)</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5903,24 +6326,29 @@
           <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>085000431375</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
         <v>4</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>1.5</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>5</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>43</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Vadnais Heights (5)</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5940,24 +6368,29 @@
           <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>085000431375</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
         <v>10</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>1.6</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>5</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>43</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Minnetonka (5)</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5977,24 +6410,29 @@
           <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>085000426272</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>0.5</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>5</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>42</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Minnetonka (5)</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6014,24 +6452,29 @@
           <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>085000429259</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
         <v>4</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>1.4</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>4</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>34</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Stillwater (4)</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6051,24 +6494,29 @@
           <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>850003574028</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
         <v>2</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>0.4</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>4</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>31</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Bloomington (4)</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6088,24 +6536,29 @@
           <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>085000029862</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
         <v>23</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>2.7</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>12</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>262</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Rosemount (8), Blaine (4)</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6125,24 +6578,29 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>085000037393</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
         <v>4</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>3.7</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>12</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>220</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Plymouth (12)</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6162,24 +6620,29 @@
           <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>085000038963</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
         <v>11</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>5.2</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>12</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>203</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Minneapolis (8), Stillwater (4)</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6199,24 +6662,29 @@
           <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>085000038963</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
         <v>8</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>4</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>7</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>118</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Stillwater (7)</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6236,24 +6704,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
         <v>5</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>2.3</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>6</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>111</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Blaine (6)</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6273,24 +6746,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
         <v>5</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>2.3</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>6</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>111</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Chanhassen (6)</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6310,24 +6788,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
         <v>42</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>99</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>5</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>93</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Roseville (5)</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6347,24 +6830,29 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>085000037393</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
         <v>6</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>5.1</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>5</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>92</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Plymouth (5)</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6384,24 +6872,29 @@
           <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>085000430958</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
         <v>8</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>2.2</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>9</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>78</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>St. Louis Park (9)</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6421,24 +6914,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
         <v>4</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>2.7</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>4</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>74</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Blaine (4)</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6458,24 +6956,29 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>085000036099</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
         <v>5</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>99</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>4</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>74</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Chanhassen (4)</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6495,24 +6998,29 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>085000037393</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
         <v>68</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>43.7</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>4</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>73</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Andover (4)</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6532,24 +7040,29 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>085000037393</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
         <v>4</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>99</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>4</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>73</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Plymouth (4)</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6569,24 +7082,29 @@
           <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>085000034484</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
         <v>10</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>35.7</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>16</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>72</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6606,24 +7124,29 @@
           <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>891278002380</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
         <v>5</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>2.2</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>7</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>53</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>Roseville (7)</t>
         </is>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6643,24 +7166,29 @@
           <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>891278003530</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
         <v>16</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>99</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>27</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>51</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Vadnais Heights (27)</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6680,24 +7208,29 @@
           <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>891278002465</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
         <v>8</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>11.7</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>6</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>45</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>Cottage Grove (6)</t>
         </is>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6717,24 +7250,29 @@
           <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>850019260588</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
         <v>3</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>4.7</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>4</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>39</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>Minnetonka (4)</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6754,24 +7292,29 @@
           <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>850003574028</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
         <v>8</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>3.5</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>5</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>38</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>Minnetonka (5)</t>
         </is>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6791,24 +7334,29 @@
           <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>085000432327</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>6</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>99</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>4</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>36</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Woodbury (4)</t>
         </is>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6828,24 +7376,29 @@
           <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>085000430958</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
         <v>5</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>2.9</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>4</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>35</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>Woodbury (4)</t>
         </is>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6865,24 +7418,29 @@
           <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>085000430958</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
         <v>23</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>7.1</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>4</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>35</v>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Bloomington (4)</t>
         </is>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6902,24 +7460,29 @@
           <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>850003574042</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
         <v>10</v>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>14.3</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>6</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>33</v>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>Vadnais Heights (6)</t>
         </is>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6939,24 +7502,29 @@
           <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>850003574110</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
         <v>6</v>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>5.5</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>4</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>33</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Andover (4)</t>
         </is>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6976,24 +7544,29 @@
           <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>850003574202</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
         <v>11</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>6.3</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>6</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>32</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>St. Louis Park (6)</t>
         </is>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7013,24 +7586,29 @@
           <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>850003574202</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
         <v>10</v>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>10.2</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>4</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>22</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Blaine (4)</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7050,24 +7628,29 @@
           <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>891278003271</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
         <v>17</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>4.1</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>11</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>21</v>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Cottage Grove (11)</t>
         </is>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7087,24 +7670,29 @@
           <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>085000034484</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
         <v>1</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>2.9</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>4</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>18</v>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Blaine (4)</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7124,24 +7712,29 @@
           <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>891278002335</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
         <v>10</v>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>99</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>6</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>11</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Minneapolis (6)</t>
         </is>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7161,24 +7754,29 @@
           <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>891278003530</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
         <v>10</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>7.2</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>6</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>11</v>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Vadnais Heights (6)</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7198,24 +7796,29 @@
           <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>891278003530</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
         <v>10</v>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>99</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>6</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>11</v>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Vadnais Heights (6)</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7235,24 +7838,29 @@
           <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>891278002298</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
         <v>5</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>26.8</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>5</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>10</v>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Cottage Grove (5)</t>
         </is>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7272,24 +7880,29 @@
           <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>891278003271</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
         <v>1</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>6.4</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>5</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>10</v>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>Minneapolis (5)</t>
         </is>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7309,24 +7922,29 @@
           <t>Monaco Lemonade 12oz can</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>891278003332</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
         <v>13</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>99</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>5</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>9</v>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Minneapolis (5)</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7346,24 +7964,29 @@
           <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>891278003271</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
         <v>4</v>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>99</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>4</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>8</v>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>Vadnais Heights (4)</t>
         </is>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7383,24 +8006,29 @@
           <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>891278002519</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
         <v>3</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>32.1</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>4</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>8</v>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Minneapolis (4)</t>
         </is>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,7 +532,7 @@
         <v>-5</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="G2" t="n">
         <v>12</v>
@@ -555,6 +555,7 @@
       <c r="M2" t="n">
         <v>37</v>
       </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -588,10 +589,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
@@ -614,6 +615,9 @@
       <c r="M3" t="n">
         <v>48</v>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -637,32 +641,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>133</v>
       </c>
       <c r="H4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I4" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>17.02</v>
+        <v>16.98</v>
       </c>
       <c r="L4" t="n">
-        <v>1685</v>
+        <v>1834</v>
       </c>
       <c r="M4" t="n">
         <v>32</v>
       </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -722,6 +727,9 @@
       <c r="M5" t="n">
         <v>36</v>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -745,10 +753,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
         <v>120</v>
@@ -763,14 +771,15 @@
         <v>38</v>
       </c>
       <c r="K6" t="n">
-        <v>17.04</v>
+        <v>17.07</v>
       </c>
       <c r="L6" t="n">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="M6" t="n">
         <v>32</v>
       </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -785,12 +794,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>080480985448</t>
+          <t>082000799894</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -800,14 +809,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
@@ -822,14 +831,17 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>8.119999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M7" t="n">
-        <v>41</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -853,10 +865,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
         <v>156</v>
@@ -871,14 +883,15 @@
         <v>26</v>
       </c>
       <c r="K8" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="M8" t="n">
-        <v>37</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -893,12 +906,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka Variety Pack 8pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>850003574233</t>
+          <t>080480985448</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -908,46 +921,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>13.55</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="M9" t="n">
         <v>41</v>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>085000434260</t>
+          <t>085000426272</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -961,32 +977,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>8.630000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>207</v>
+        <v>355</v>
       </c>
       <c r="M10" t="n">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -1001,12 +1018,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>Two Chicks Vodka Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>085000426272</t>
+          <t>850003574233</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1016,56 +1033,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="F11" t="n">
         <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>8.449999999999999</v>
+        <v>13.55</v>
       </c>
       <c r="L11" t="n">
-        <v>405</v>
+        <v>163</v>
       </c>
       <c r="M11" t="n">
-        <v>39</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Off buy-month - confirm timing</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Two Chicks New Fashioned 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>850003574103</t>
+          <t>085000434260</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1075,46 +1085,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>7.88</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>142</v>
+        <v>207</v>
       </c>
       <c r="M12" t="n">
-        <v>39</v>
+        <v>37</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
+          <t>Two Chicks New Fashioned 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>616003648011</t>
+          <t>850003574103</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1128,42 +1149,45 @@
         </is>
       </c>
       <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
       <c r="K13" t="n">
-        <v>9.75</v>
+        <v>7.89</v>
       </c>
       <c r="L13" t="n">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="M13" t="n">
-        <v>35</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Zing Zang RTD Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>085000036099</t>
+          <t>616003648011</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1173,51 +1197,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>18.53</v>
+        <v>9.75</v>
       </c>
       <c r="L14" t="n">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="M14" t="n">
-        <v>38</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
+          <t>Bacardi Mojito 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>850003574172</t>
+          <t>080480986285</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1227,46 +1249,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
         <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>12.2</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>47</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>050200003295</t>
+          <t>197644216758</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1276,46 +1301,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>8.119999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="L16" t="n">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="M16" t="n">
-        <v>29</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>197644216758</t>
+          <t>085000036099</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1329,42 +1357,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I17" t="n">
         <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>10.33</v>
+        <v>18.53</v>
       </c>
       <c r="L17" t="n">
-        <v>124</v>
+        <v>222</v>
       </c>
       <c r="M17" t="n">
-        <v>31</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>850003574066</t>
+          <t>050200003295</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1378,42 +1413,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>7.72</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>371</v>
+        <v>195</v>
       </c>
       <c r="M18" t="n">
-        <v>41</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Two Chicks Craft Cocktail Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>891278002717</t>
+          <t>850003574172</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1423,46 +1461,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>7.58</v>
+        <v>12.2</v>
       </c>
       <c r="L19" t="n">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="M19" t="n">
-        <v>39</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>616003203135</t>
+          <t>850003574066</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1476,42 +1517,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>9.75</v>
+        <v>7.72</v>
       </c>
       <c r="L20" t="n">
-        <v>292</v>
+        <v>371</v>
       </c>
       <c r="M20" t="n">
-        <v>35</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>089540535661</t>
+          <t>891278002717</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1521,36 +1565,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>7.17</v>
+        <v>7.58</v>
       </c>
       <c r="L21" t="n">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="M21" t="n">
-        <v>43</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1574,10 +1621,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>11</v>
@@ -1600,16 +1647,19 @@
       <c r="M22" t="n">
         <v>35</v>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>850003574028</t>
+          <t>616003203135</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1623,42 +1673,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>7.67</v>
+        <v>9.75</v>
       </c>
       <c r="L23" t="n">
-        <v>184</v>
+        <v>292</v>
       </c>
       <c r="M23" t="n">
-        <v>41</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>080432000779</t>
+          <t>089540535661</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1672,42 +1725,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>8.039999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="L24" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="M24" t="n">
-        <v>46</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>085000037393</t>
+          <t>850003574028</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1717,51 +1773,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="G25" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="H25" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>18.34</v>
+        <v>7.67</v>
       </c>
       <c r="L25" t="n">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="M25" t="n">
-        <v>39</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>850003574110</t>
+          <t>089540535685</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1771,46 +1825,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>8.19</v>
+        <v>7.15</v>
       </c>
       <c r="L26" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="M26" t="n">
-        <v>37</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>850003574288</t>
+          <t>085000037393</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1820,46 +1877,53 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="F27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>7.17</v>
+        <v>18.34</v>
       </c>
       <c r="L27" t="n">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="M27" t="n">
-        <v>45</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bacardi Mojito 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>080480986285</t>
+          <t>850003574288</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1869,17 +1933,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1891,24 +1955,27 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>8.119999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="L28" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>41</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>089540535685</t>
+          <t>850003574110</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1918,46 +1985,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E29" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" t="n">
         <v>12</v>
       </c>
-      <c r="F29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G29" t="n">
-        <v>7</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>6</v>
-      </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>7.15</v>
+        <v>8.19</v>
       </c>
       <c r="L29" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="M29" t="n">
-        <v>43</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>089540535289</t>
+          <t>891278002380</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1967,20 +2037,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8.02</v>
+        <v>67</v>
       </c>
       <c r="F30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
         <v>6</v>
@@ -1989,24 +2059,27 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>6.45</v>
+        <v>7.56</v>
       </c>
       <c r="L30" t="n">
+        <v>45</v>
+      </c>
+      <c r="M30" t="n">
         <v>39</v>
       </c>
-      <c r="M30" t="n">
-        <v>48</v>
-      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>891278002380</t>
+          <t>080432000779</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2016,20 +2089,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
         <v>4.5</v>
       </c>
       <c r="G31" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>6</v>
@@ -2038,24 +2111,27 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>7.56</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M31" t="n">
-        <v>39</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>080432001257</t>
+          <t>850003574042</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2065,144 +2141,153 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F32" t="n">
         <v>4.7</v>
       </c>
       <c r="G32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>12.88</v>
+        <v>5.86</v>
       </c>
       <c r="L32" t="n">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="M32" t="n">
-        <v>46</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>891278002458</t>
+          <t>089540535289</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>126</v>
+        <v>8.02</v>
       </c>
       <c r="F33" t="n">
         <v>4.8</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1.92</v>
+        <v>6.45</v>
       </c>
       <c r="L33" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="M33" t="n">
-        <v>45</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>850003574042</t>
+          <t>891278002458</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="F34" t="n">
         <v>4.9</v>
       </c>
       <c r="G34" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>12</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>5.55</v>
+        <v>1.92</v>
       </c>
       <c r="L34" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="M34" t="n">
-        <v>57</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>085000038963</t>
+          <t>080432001257</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2212,149 +2297,157 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="F35" t="n">
         <v>5.1</v>
       </c>
       <c r="G35" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="H35" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="J35" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>16.88</v>
+        <v>12.88</v>
       </c>
       <c r="L35" t="n">
-        <v>962</v>
+        <v>193</v>
       </c>
       <c r="M35" t="n">
-        <v>32</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>080686008064</t>
+          <t>085000038963</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="F36" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G36" t="n">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="I36" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K36" t="n">
-        <v>8.6</v>
+        <v>16.88</v>
       </c>
       <c r="L36" t="n">
-        <v>103</v>
+        <v>861</v>
       </c>
       <c r="M36" t="n">
-        <v>38</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>850003574202</t>
+          <t>080686008064</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="F37" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="G37" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
         <v>12</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>5.38</v>
+        <v>8.6</v>
       </c>
       <c r="L37" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="M37" t="n">
-        <v>59</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>082000799894</t>
+          <t>850003574202</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2364,36 +2457,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>7.79</v>
+        <v>5.3</v>
       </c>
       <c r="L38" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="M38" t="n">
-        <v>43</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2443,114 +2539,123 @@
       <c r="M39" t="n">
         <v>31</v>
       </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>085000034491</t>
+          <t>891278002311</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F40" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>4.5</v>
+        <v>7.58</v>
       </c>
       <c r="L40" t="n">
-        <v>162</v>
+        <v>45</v>
       </c>
       <c r="M40" t="n">
-        <v>44</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>850003574264</t>
+          <t>085000034491</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>7.83</v>
+        <v>4.5</v>
       </c>
       <c r="L41" t="n">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="M41" t="n">
-        <v>40</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>891278002311</t>
+          <t>850003574196</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2560,46 +2665,49 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="G42" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>7.57</v>
+        <v>6.88</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="M42" t="n">
-        <v>39</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>850003574196</t>
+          <t>850003574264</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2613,32 +2721,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F43" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G43" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>6.9</v>
+        <v>7.83</v>
       </c>
       <c r="L43" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="M43" t="n">
-        <v>47</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2665,7 +2776,7 @@
         <v>31</v>
       </c>
       <c r="F44" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="G44" t="n">
         <v>16</v>
@@ -2688,6 +2799,9 @@
       <c r="M44" t="n">
         <v>40</v>
       </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2737,6 +2851,9 @@
       <c r="M45" t="n">
         <v>46</v>
       </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2786,6 +2903,9 @@
       <c r="M46" t="n">
         <v>44</v>
       </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2835,6 +2955,9 @@
       <c r="M47" t="n">
         <v>35</v>
       </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2884,16 +3007,19 @@
       <c r="M48" t="n">
         <v>43</v>
       </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
+          <t>Saint Spritz Sicily 4pk 355ml</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>082000799955</t>
+          <t>197644897254</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2907,42 +3033,45 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F49" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="G49" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>7.8</v>
+        <v>10.33</v>
       </c>
       <c r="L49" t="n">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="M49" t="n">
-        <v>43</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Saint Spritz Sicily 4pk 355ml</t>
+          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>197644897254</t>
+          <t>082000799955</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2956,32 +3085,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F50" t="n">
-        <v>23.1</v>
+        <v>28.6</v>
       </c>
       <c r="G50" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>10.33</v>
+        <v>7.8</v>
       </c>
       <c r="L50" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="M50" t="n">
-        <v>31</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3026,16 +3158,19 @@
       <c r="M51" t="n">
         <v>27</v>
       </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
+          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>050200003578</t>
+          <t>082000799917</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3045,46 +3180,49 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F52" t="n">
-        <v>37.8</v>
+        <v>39.8</v>
       </c>
       <c r="G52" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>8.130000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="L52" t="n">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="M52" t="n">
-        <v>35</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer Orange Pineapple</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>082000799917</t>
+          <t>050200003578</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3094,36 +3232,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F53" t="n">
-        <v>39.8</v>
+        <v>51.4</v>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>7.8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>94</v>
+        <v>195</v>
       </c>
       <c r="M53" t="n">
-        <v>43</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3173,6 +3314,9 @@
       <c r="M54" t="n">
         <v>48</v>
       </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3214,6 +3358,9 @@
       <c r="M55" t="n">
         <v>29</v>
       </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3260,6 +3407,9 @@
       <c r="M56" t="n">
         <v>32</v>
       </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3301,6 +3451,9 @@
       <c r="M57" t="n">
         <v>34</v>
       </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3428,7 +3581,7 @@
         <v>-5</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="G2" t="n">
         <v>12</v>
@@ -3451,6 +3604,7 @@
       <c r="M2" t="n">
         <v>37</v>
       </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -3484,32 +3638,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>133</v>
       </c>
       <c r="H3" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I3" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="J3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>17.02</v>
+        <v>16.98</v>
       </c>
       <c r="L3" t="n">
-        <v>1685</v>
+        <v>1834</v>
       </c>
       <c r="M3" t="n">
         <v>32</v>
       </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -3543,10 +3698,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
         <v>120</v>
@@ -3561,14 +3716,15 @@
         <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>17.04</v>
+        <v>17.07</v>
       </c>
       <c r="L4" t="n">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="M4" t="n">
         <v>32</v>
       </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -3602,10 +3758,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
         <v>156</v>
@@ -3620,14 +3776,15 @@
         <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="M5" t="n">
-        <v>37</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -3642,12 +3799,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>085000434260</t>
+          <t>085000426272</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3661,32 +3818,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>8.630000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>207</v>
+        <v>355</v>
       </c>
       <c r="M6" t="n">
-        <v>37</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -3701,12 +3859,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>085000426272</t>
+          <t>085000434260</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3720,32 +3878,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
         <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>8.449999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>405</v>
+        <v>207</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
@@ -3896,6 +4055,7 @@
       <c r="M2" t="n">
         <v>39</v>
       </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3945,6 +4105,7 @@
       <c r="M3" t="n">
         <v>44</v>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3989,6 +4150,7 @@
       <c r="M4" t="n">
         <v>52</v>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4012,10 +4174,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
         <v>14</v>
@@ -4038,6 +4200,7 @@
       <c r="M5" t="n">
         <v>49</v>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4064,7 +4227,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
         <v>11</v>
@@ -4087,6 +4250,7 @@
       <c r="M6" t="n">
         <v>56</v>
       </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4110,10 +4274,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="n">
         <v>19</v>
@@ -4136,6 +4300,7 @@
       <c r="M7" t="n">
         <v>49</v>
       </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4159,10 +4324,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="G8" t="n">
         <v>14</v>
@@ -4185,6 +4350,7 @@
       <c r="M8" t="n">
         <v>49</v>
       </c>
+      <c r="O8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4304,7 +4470,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
         <v>3.3</v>
@@ -4313,7 +4479,7 @@
         <v>63</v>
       </c>
       <c r="H2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
         <v>42</v>
@@ -4325,11 +4491,12 @@
         <v>8.56</v>
       </c>
       <c r="L2" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M2" t="n">
         <v>38</v>
       </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
@@ -4358,10 +4525,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
         <v>70</v>
@@ -4384,6 +4551,7 @@
       <c r="M3" t="n">
         <v>37</v>
       </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
@@ -4415,7 +4583,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
         <v>22</v>
@@ -4438,6 +4606,7 @@
       <c r="M4" t="n">
         <v>35</v>
       </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
@@ -4466,16 +4635,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
         <v>72</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
         <v>54</v>
@@ -4484,14 +4653,15 @@
         <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>8.550000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M5" t="n">
         <v>38</v>
       </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
@@ -4520,7 +4690,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -4538,14 +4708,15 @@
         <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>21.83</v>
+        <v>21.77</v>
       </c>
       <c r="L6" t="n">
-        <v>2096</v>
+        <v>2090</v>
       </c>
       <c r="M6" t="n">
         <v>34</v>
       </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
@@ -4577,29 +4748,30 @@
         <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="G7" t="n">
         <v>31</v>
       </c>
       <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="n">
         <v>12</v>
       </c>
-      <c r="I7" t="n">
-        <v>18</v>
-      </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>8.58</v>
       </c>
       <c r="L7" t="n">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="M7" t="n">
         <v>38</v>
       </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Wait for buy-month (May, Aug)</t>
@@ -4617,7 +4789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4638,35 +4810,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Product Code</t>
+          <t>To OH</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>To OH</t>
+          <t>To WOS</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>To WOS</t>
+          <t>Transfer In</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Transfer In</t>
+          <t>Value $</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Value $</t>
+          <t>From</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Then Buy</t>
         </is>
@@ -4688,29 +4855,24 @@
           <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>085000031513</t>
-        </is>
+      <c r="D2" t="n">
+        <v>-5</v>
       </c>
       <c r="E2" t="n">
-        <v>-5</v>
+        <v>-4.1</v>
       </c>
       <c r="F2" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" t="n">
         <v>204</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Bloomington (12)</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="I2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4730,29 +4892,24 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+      <c r="D3" t="n">
+        <v>-4</v>
       </c>
       <c r="E3" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="n">
         <v>148</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Chanhassen (8)</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="I3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4772,29 +4929,24 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+      <c r="D4" t="n">
+        <v>-43</v>
       </c>
       <c r="E4" t="n">
-        <v>-43</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" t="n">
         <v>130</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Blaine (7)</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Chanhassen (7)</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4814,29 +4966,24 @@
           <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>085000430958</t>
-        </is>
+      <c r="D5" t="n">
+        <v>-5</v>
       </c>
       <c r="E5" t="n">
-        <v>-5</v>
+        <v>-2.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
-      </c>
-      <c r="H5" t="n">
         <v>122</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>St. Louis Park (14)</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="I5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4856,29 +5003,24 @@
           <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>085000029862</t>
-        </is>
+      <c r="D6" t="n">
+        <v>-3</v>
       </c>
       <c r="E6" t="n">
-        <v>-3</v>
+        <v>-1.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="n">
         <v>109</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Minneapolis (5)</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Andover (5)</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4898,29 +5040,24 @@
           <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>085000032558</t>
-        </is>
+      <c r="D7" t="n">
+        <v>-1</v>
       </c>
       <c r="E7" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" t="n">
         <v>102</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Bloomington (6)</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="I7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4932,37 +5069,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-21.4</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>93</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Chanhassen (5)</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+        <v>102</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bloomington (6)</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4974,38 +5106,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>085000426272</t>
-        </is>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2</v>
       </c>
       <c r="E9" t="n">
-        <v>-8</v>
+        <v>-21.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" t="n">
-        <v>84</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Bloomington (10)</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
+        <v>93</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Chanhassen (5)</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5016,38 +5143,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>085000037393</t>
-        </is>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-8</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>73</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Plymouth (4)</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
+        <v>85</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bloomington (10)</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5058,37 +5180,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>085000031513</t>
-        </is>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-20.3</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>68</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Bloomington (4)</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+        <v>73</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Plymouth (4)</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5100,37 +5217,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>616003203135</t>
-        </is>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-12</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-20.3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>58</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Plymouth (6)</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bloomington (4)</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5142,37 +5254,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>085000430958</t>
-        </is>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>52</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Bloomington (6)</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+        <v>58</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Plymouth (6)</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5189,33 +5296,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>085000431375</t>
-        </is>
+          <t>High Noon Lime 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>51</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Bloomington (6)</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Woodbury (6)</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5226,38 +5328,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>085000432327</t>
-        </is>
+          <t>High Noon Peach 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>44</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>St. Louis Park (5)</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (6)</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5268,38 +5365,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>085000429259</t>
-        </is>
+          <t>High Noon Mango 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-4</v>
       </c>
       <c r="E16" t="n">
-        <v>-7</v>
+        <v>-2.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.5</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>34</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Cottage Grove (4)</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>St. Louis Park (5)</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5315,32 +5407,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>085000429259</t>
-        </is>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" t="n">
         <v>34</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Rosemount (4)</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Minnetonka (4)</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5352,38 +5439,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>080686008064</t>
-        </is>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" t="n">
         <v>34</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Minnetonka (4)</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Chanhassen (4)</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -5394,38 +5476,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>050200003295</t>
-        </is>
+          <t>High Noon Watermelon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-7</v>
       </c>
       <c r="E19" t="n">
-        <v>-13</v>
+        <v>-6.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.9</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>32</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Bloomington (4)</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>6</v>
+        <v>34</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Cottage Grove (4)</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -5436,37 +5513,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>850003574066</t>
-        </is>
+          <t>High Noon Watermelon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>31</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
+        <v>34</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Rosemount (4)</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5478,37 +5550,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monaco Tropic Rush 12oz can</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>891278002762</t>
-        </is>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-1</v>
+        <v>99</v>
       </c>
       <c r="F21" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>15</v>
-      </c>
-      <c r="H21" t="n">
-        <v>29</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Minneapolis (15)</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
+        <v>34</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Minnetonka (4)</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5520,38 +5587,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>891278003219</t>
-        </is>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-13</v>
       </c>
       <c r="E22" t="n">
-        <v>-3</v>
+        <v>-22</v>
       </c>
       <c r="F22" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>11</v>
-      </c>
-      <c r="H22" t="n">
-        <v>21</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Minneapolis (11)</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bloomington (4)</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -5562,37 +5624,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>891278003219</t>
-        </is>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-4</v>
       </c>
       <c r="E23" t="n">
-        <v>-11</v>
+        <v>-3.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.6</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>9</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Minneapolis (5)</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
+        <v>31</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Minneapolis (4)</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5604,37 +5661,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>891278002373</t>
-        </is>
+          <t>Monaco Tropic Rush 12oz can</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F24" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>9</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>St. Louis Park (5)</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
+        <v>28</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Minneapolis (15)</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5646,163 +5698,143 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>891278002298</t>
-        </is>
+          <t>Monaco Sun Crush 12oz can</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-3</v>
       </c>
       <c r="E25" t="n">
-        <v>-2</v>
+        <v>99</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Cottage Grove (4)</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Minneapolis (11)</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>085000029862</t>
-        </is>
+          <t>Monaco Sun Crush 12oz can</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-11</v>
       </c>
       <c r="E26" t="n">
-        <v>36</v>
+        <v>-6.6</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>43</v>
-      </c>
-      <c r="H26" t="n">
-        <v>939</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Minneapolis (14), Bloomington (13), Andover (12), Rosemount (4)</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
+        <v>9</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Minneapolis (5)</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+          <t>Monaco Tequila Lime Crush 12oz can</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
       <c r="E27" t="n">
+        <v>99</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
         <v>9</v>
       </c>
-      <c r="F27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G27" t="n">
-        <v>17</v>
-      </c>
-      <c r="H27" t="n">
-        <v>315</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Chanhassen (17)</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>St. Louis Park (5)</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>085000031513</t>
-        </is>
+          <t>Monaco Citrus Rush 12oz can</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-2</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>-2.5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>13</v>
-      </c>
-      <c r="H28" t="n">
-        <v>221</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Bloomington (7), St. Louis Park (6)</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Cottage Grove (4)</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5814,37 +5846,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>085000037393</t>
-        </is>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" t="n">
-        <v>183</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Plymouth (10)</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
+        <v>936</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Andover (14), Bloomington (13), Rosemount (12), Minneapolis (4)</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5856,37 +5883,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>085000029862</t>
-        </is>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>1.7</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>175</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Blaine (8)</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
+        <v>315</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Chanhassen (17)</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5898,7 +5920,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5906,29 +5928,24 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>085000037393</t>
-        </is>
+      <c r="D31" t="n">
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
-      </c>
-      <c r="H31" t="n">
-        <v>165</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Plymouth (9)</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
+        <v>183</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Plymouth (10)</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5940,7 +5957,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5948,29 +5965,24 @@
           <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>085000029862</t>
-        </is>
+      <c r="D32" t="n">
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
-      </c>
-      <c r="H32" t="n">
-        <v>131</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Andover (6)</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
+        <v>174</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Blaine (8)</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5982,37 +5994,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>085000038963</t>
-        </is>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="F33" t="n">
-        <v>1.8</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" t="n">
-        <v>84</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Stillwater (5)</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
+        <v>165</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Plymouth (9)</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6024,38 +6031,33 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>085000429273</t>
-        </is>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>0.1</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
-      </c>
-      <c r="H34" t="n">
-        <v>77</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Osseo (5), Vadnais Heights (4)</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>3</v>
+        <v>131</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Minneapolis (6)</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -6066,38 +6068,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>085000429273</t>
-        </is>
+          <t>High Noon Peach 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="G35" t="n">
-        <v>8</v>
-      </c>
-      <c r="H35" t="n">
-        <v>69</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Bloomington (8)</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Minnetonka (5), Bloomington (5), St. Louis Park (4)</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -6108,7 +6105,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6116,29 +6113,24 @@
           <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>085000038963</t>
-        </is>
+      <c r="D36" t="n">
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
-      </c>
-      <c r="H36" t="n">
-        <v>68</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Stillwater (4)</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
+        <v>84</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Stillwater (5)</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,38 +6142,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>085000031513</t>
-        </is>
+          <t>High Noon Lime 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" t="n">
-        <v>68</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (4)</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>6</v>
+        <v>78</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>St. Louis Park (9)</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -6192,7 +6179,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6200,30 +6187,25 @@
           <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>085000429273</t>
-        </is>
+      <c r="D38" t="n">
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="G38" t="n">
-        <v>6</v>
-      </c>
-      <c r="H38" t="n">
-        <v>51</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Andover (6)</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bloomington (8)</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -6239,32 +6221,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>860272001439</t>
-        </is>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>51</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Minnetonka (5)</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
+        <v>68</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Stillwater (4)</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6276,38 +6253,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>085000430958</t>
-        </is>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
       </c>
       <c r="E40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F40" t="n">
         <v>4</v>
       </c>
-      <c r="F40" t="n">
-        <v>1.4</v>
-      </c>
       <c r="G40" t="n">
-        <v>5</v>
-      </c>
-      <c r="H40" t="n">
-        <v>43</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Woodbury (5)</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (4)</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -6318,38 +6290,33 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>085000431375</t>
-        </is>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="F41" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>43</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (5)</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Andover (6)</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -6365,33 +6332,28 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>085000431375</t>
-        </is>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>0.4</v>
       </c>
       <c r="F42" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>43</v>
-      </c>
-      <c r="I42" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>Minnetonka (5)</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>11</v>
+      <c r="I42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6402,38 +6364,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>085000426272</t>
-        </is>
+          <t>High Noon Lime 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>42</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Minnetonka (5)</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bloomington (5)</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -6452,29 +6409,24 @@
           <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>085000429259</t>
-        </is>
+      <c r="D44" t="n">
+        <v>4</v>
       </c>
       <c r="E44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F44" t="n">
         <v>4</v>
       </c>
-      <c r="F44" t="n">
-        <v>1.4</v>
-      </c>
       <c r="G44" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" t="n">
         <v>34</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Stillwater (4)</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Chanhassen (4)</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6494,29 +6446,24 @@
           <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>850003574028</t>
-        </is>
+      <c r="D45" t="n">
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
-      </c>
-      <c r="H45" t="n">
         <v>31</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Bloomington (4)</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="I45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6536,29 +6483,24 @@
           <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>085000029862</t>
-        </is>
+      <c r="D46" t="n">
+        <v>21</v>
       </c>
       <c r="E46" t="n">
-        <v>23</v>
+        <v>2.4</v>
       </c>
       <c r="F46" t="n">
-        <v>2.7</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
-        <v>12</v>
-      </c>
-      <c r="H46" t="n">
-        <v>262</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Rosemount (8), Blaine (4)</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
+        <v>261</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Minneapolis (8), Blaine (4)</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6578,29 +6520,24 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>085000037393</t>
-        </is>
+      <c r="D47" t="n">
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="F47" t="n">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
-      </c>
-      <c r="H47" t="n">
         <v>220</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Plymouth (12)</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="I47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6620,30 +6557,25 @@
           <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>085000038963</t>
-        </is>
+      <c r="D48" t="n">
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="F48" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>12</v>
-      </c>
-      <c r="H48" t="n">
-        <v>203</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Minneapolis (8), Stillwater (4)</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Minneapolis (9)</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -6662,29 +6594,24 @@
           <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>085000038963</t>
-        </is>
+      <c r="D49" t="n">
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
-        <v>7</v>
-      </c>
-      <c r="H49" t="n">
         <v>118</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Stillwater (7)</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="I49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6696,38 +6623,33 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="F50" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
-      </c>
-      <c r="H50" t="n">
-        <v>111</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Blaine (6)</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Stillwater (7)</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -6746,29 +6668,24 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+      <c r="D51" t="n">
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="F51" t="n">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
-      </c>
-      <c r="H51" t="n">
         <v>111</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Chanhassen (6)</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Blaine (6)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6780,7 +6697,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6788,30 +6705,25 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+      <c r="D52" t="n">
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>2.5</v>
       </c>
       <c r="F52" t="n">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>93</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Roseville (5)</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>3</v>
+        <v>111</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Blaine (6)</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -6822,38 +6734,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>085000037393</t>
-        </is>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>42</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="F53" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>5</v>
-      </c>
-      <c r="H53" t="n">
-        <v>92</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Plymouth (5)</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
+        <v>93</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Roseville (5)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -6864,38 +6771,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>085000430958</t>
-        </is>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="F54" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>9</v>
-      </c>
-      <c r="H54" t="n">
-        <v>78</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>St. Louis Park (9)</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
+        <v>92</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Plymouth (5)</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -6914,29 +6816,24 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+      <c r="D55" t="n">
+        <v>4</v>
       </c>
       <c r="E55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F55" t="n">
         <v>4</v>
       </c>
-      <c r="F55" t="n">
-        <v>2.7</v>
-      </c>
       <c r="G55" t="n">
-        <v>4</v>
-      </c>
-      <c r="H55" t="n">
         <v>74</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Blaine (4)</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Chanhassen (4)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6956,29 +6853,24 @@
           <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>085000036099</t>
-        </is>
+      <c r="D56" t="n">
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="F56" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>4</v>
-      </c>
-      <c r="H56" t="n">
         <v>74</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Chanhassen (4)</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Blaine (4)</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6998,29 +6890,24 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>085000037393</t>
-        </is>
+      <c r="D57" t="n">
+        <v>68</v>
       </c>
       <c r="E57" t="n">
-        <v>68</v>
+        <v>43.7</v>
       </c>
       <c r="F57" t="n">
-        <v>43.7</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>4</v>
-      </c>
-      <c r="H57" t="n">
         <v>73</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Andover (4)</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="I57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7040,29 +6927,24 @@
           <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>085000037393</t>
-        </is>
+      <c r="D58" t="n">
+        <v>4</v>
       </c>
       <c r="E58" t="n">
+        <v>99</v>
+      </c>
+      <c r="F58" t="n">
         <v>4</v>
       </c>
-      <c r="F58" t="n">
-        <v>99</v>
-      </c>
       <c r="G58" t="n">
-        <v>4</v>
-      </c>
-      <c r="H58" t="n">
         <v>73</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Plymouth (4)</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="I58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7082,29 +6964,24 @@
           <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>085000034484</t>
-        </is>
+      <c r="D59" t="n">
+        <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>10</v>
+        <v>35.7</v>
       </c>
       <c r="F59" t="n">
-        <v>35.7</v>
+        <v>16</v>
       </c>
       <c r="G59" t="n">
-        <v>16</v>
-      </c>
-      <c r="H59" t="n">
         <v>72</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="I59" t="n">
         <v>15</v>
       </c>
     </row>
@@ -7124,29 +7001,24 @@
           <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>891278002380</t>
-        </is>
+      <c r="D60" t="n">
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="F60" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="G60" t="n">
-        <v>7</v>
-      </c>
-      <c r="H60" t="n">
         <v>53</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Roseville (7)</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="I60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7166,30 +7038,25 @@
           <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>891278003530</t>
-        </is>
+      <c r="D61" t="n">
+        <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="F61" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G61" t="n">
-        <v>27</v>
-      </c>
-      <c r="H61" t="n">
-        <v>51</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (27)</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (25)</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -7208,29 +7075,24 @@
           <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>891278002465</t>
-        </is>
+      <c r="D62" t="n">
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>8</v>
+        <v>11.7</v>
       </c>
       <c r="F62" t="n">
-        <v>11.7</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>6</v>
-      </c>
-      <c r="H62" t="n">
         <v>45</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Cottage Grove (6)</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="I62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7242,38 +7104,33 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>850019260588</t>
-        </is>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="F63" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G63" t="n">
-        <v>4</v>
-      </c>
-      <c r="H63" t="n">
-        <v>39</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Minnetonka (4)</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Osseo (5)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -7284,38 +7141,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>850003574028</t>
-        </is>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="F64" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" t="n">
-        <v>38</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Minnetonka (5)</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>2</v>
+        <v>41</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Stillwater (5)</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -7326,37 +7178,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>085000432327</t>
-        </is>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="F65" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>4</v>
-      </c>
-      <c r="H65" t="n">
-        <v>36</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Woodbury (4)</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
+        <v>39</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Minnetonka (4)</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7368,38 +7215,33 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>085000430958</t>
-        </is>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7</v>
       </c>
       <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="n">
         <v>5</v>
       </c>
-      <c r="F66" t="n">
-        <v>2.9</v>
-      </c>
       <c r="G66" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" t="n">
-        <v>35</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Woodbury (4)</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Minnetonka (5)</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -7410,38 +7252,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>085000430958</t>
-        </is>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
       </c>
       <c r="E67" t="n">
-        <v>23</v>
+        <v>6.1</v>
       </c>
       <c r="F67" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="G67" t="n">
-        <v>4</v>
-      </c>
-      <c r="H67" t="n">
-        <v>35</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Bloomington (4)</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>14</v>
+        <v>37</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Andover (7)</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -7457,32 +7294,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>850003574042</t>
-        </is>
+          <t>High Noon Mango 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F68" t="n">
-        <v>14.3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
-      </c>
-      <c r="H68" t="n">
-        <v>33</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (6)</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
+        <v>36</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Woodbury (4)</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7499,33 +7331,28 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>850003574110</t>
-        </is>
+          <t>High Noon Lime 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="F69" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
-      </c>
-      <c r="H69" t="n">
-        <v>33</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Andover (4)</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Bloomington (4)</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -7536,38 +7363,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>850003574202</t>
-        </is>
+          <t>High Noon Lime 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>23</v>
       </c>
       <c r="E70" t="n">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="F70" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
-      </c>
-      <c r="H70" t="n">
-        <v>32</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>St. Louis Park (6)</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Woodbury (4)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -7578,38 +7400,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>850003574202</t>
-        </is>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="F71" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="G71" t="n">
-        <v>4</v>
-      </c>
-      <c r="H71" t="n">
-        <v>22</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Blaine (4)</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (6)</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -7620,38 +7437,33 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>891278003271</t>
-        </is>
+          <t>High Noon Watermelon 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="F72" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G72" t="n">
-        <v>11</v>
-      </c>
-      <c r="H72" t="n">
-        <v>21</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Cottage Grove (11)</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Stillwater (4)</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -7662,37 +7474,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>085000034484</t>
-        </is>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>11.9</v>
       </c>
       <c r="F73" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
-        <v>4</v>
-      </c>
-      <c r="H73" t="n">
-        <v>18</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Blaine (4)</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
+        <v>26</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>St. Louis Park (5)</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7704,37 +7511,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>891278002335</t>
-        </is>
+          <t>Monaco Mai Tai 12oz can</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>17</v>
       </c>
       <c r="E74" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="F74" t="n">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="G74" t="n">
-        <v>6</v>
-      </c>
-      <c r="H74" t="n">
-        <v>11</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Minneapolis (6)</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
+        <v>21</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Cottage Grove (11)</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7746,37 +7548,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>891278003530</t>
-        </is>
+          <t>High Noon Pineapple 24oz can</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>10</v>
+        <v>2.9</v>
       </c>
       <c r="F75" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
-      </c>
-      <c r="H75" t="n">
-        <v>11</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (6)</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
+        <v>18</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Blaine (4)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7788,37 +7585,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>891278003530</t>
-        </is>
+          <t>Monaco Mango Peach 12oz can</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F76" t="n">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>6</v>
-      </c>
-      <c r="H76" t="n">
         <v>11</v>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (6)</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Minneapolis (6)</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7830,37 +7622,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>891278002298</t>
-        </is>
+          <t>Monaco Watermelon Crush 12oz can</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
       </c>
       <c r="E77" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="F77" t="n">
-        <v>26.8</v>
+        <v>6</v>
       </c>
       <c r="G77" t="n">
-        <v>5</v>
-      </c>
-      <c r="H77" t="n">
-        <v>10</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Cottage Grove (5)</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
+        <v>11</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (6)</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7872,37 +7659,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>891278003271</t>
-        </is>
+          <t>Monaco Watermelon Crush 12oz can</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F78" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="G78" t="n">
-        <v>5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>10</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Minneapolis (5)</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
+        <v>11</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (6)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7914,37 +7696,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Monaco Lemonade 12oz can</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>891278003332</t>
-        </is>
+          <t>Monaco Citrus Rush 12oz can</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>13</v>
+        <v>26.8</v>
       </c>
       <c r="F79" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>5</v>
-      </c>
-      <c r="H79" t="n">
-        <v>9</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Minneapolis (5)</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Cottage Grove (5)</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7956,7 +7733,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7964,29 +7741,24 @@
           <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>891278003271</t>
-        </is>
+      <c r="D80" t="n">
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="F80" t="n">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="G80" t="n">
-        <v>4</v>
-      </c>
-      <c r="H80" t="n">
-        <v>8</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Vadnais Heights (4)</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
+        <v>10</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Minneapolis (5)</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7998,37 +7770,106 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>Osseo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Monaco Lemonade 12oz can</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>13</v>
+      </c>
+      <c r="E81" t="n">
+        <v>99</v>
+      </c>
+      <c r="F81" t="n">
+        <v>5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>9</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Minneapolis (5)</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Blaine</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Monaco Mai Tai 12oz can</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>99</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Vadnais Heights (4)</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>Ramsey</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>891278002519</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
+      <c r="D83" t="n">
         <v>3</v>
       </c>
-      <c r="F81" t="n">
+      <c r="E83" t="n">
         <v>32.1</v>
       </c>
-      <c r="G81" t="n">
+      <c r="F83" t="n">
         <v>4</v>
       </c>
-      <c r="H81" t="n">
+      <c r="G83" t="n">
         <v>8</v>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Minneapolis (4)</t>
         </is>
       </c>
-      <c r="J81" t="n">
+      <c r="I83" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="n">
         <v>133</v>
@@ -659,10 +659,10 @@
         <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>16.98</v>
+        <v>16.97</v>
       </c>
       <c r="L4" t="n">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="M4" t="n">
         <v>32</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
         <v>1.4</v>
@@ -771,10 +771,10 @@
         <v>38</v>
       </c>
       <c r="K6" t="n">
-        <v>17.07</v>
+        <v>17.06</v>
       </c>
       <c r="L6" t="n">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="M6" t="n">
         <v>32</v>
@@ -794,12 +794,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>082000799894</t>
+          <t>085000429266</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -813,45 +813,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="F7" t="n">
         <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>156</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="K7" t="n">
-        <v>7.79</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>47</v>
+        <v>1344</v>
       </c>
       <c r="M7" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>Bacardi Rum Punch 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>085000429266</t>
+          <t>080480985448</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -861,57 +869,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>156</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>156</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>8.609999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1344</v>
+        <v>49</v>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Off buy-month - confirm timing</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bacardi Rum Punch 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>080480985448</t>
+          <t>085000426272</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -921,49 +921,57 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I9" t="n">
+        <v>36</v>
+      </c>
+      <c r="J9" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" t="n">
-        <v>8.119999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>304</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Lemon 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>085000426272</t>
+          <t>085000434260</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -977,31 +985,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
         <v>1.8</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="H10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>8.460000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>355</v>
+        <v>207</v>
       </c>
       <c r="M10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1018,12 +1026,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks New Fashioned 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>850003574233</t>
+          <t>850003574103</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1037,31 +1045,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
         <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>13.55</v>
+        <v>7.89</v>
       </c>
       <c r="L11" t="n">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1070,12 +1078,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Noon Lemon 4pk 12oz can</t>
+          <t>Two Chicks Vodka Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>085000434260</t>
+          <t>850003574233</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1085,57 +1093,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>8.630000000000001</v>
+        <v>13.55</v>
       </c>
       <c r="L12" t="n">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="M12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Off buy-month - confirm timing</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Two Chicks New Fashioned 4pk 12oz can</t>
+          <t>Bacardi Mojito 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>850003574103</t>
+          <t>080480986285</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1145,35 +1145,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>7.89</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1234,12 +1234,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bacardi Mojito 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>080480986285</t>
+          <t>085000036099</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1249,49 +1249,53 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
+        <v>74</v>
+      </c>
+      <c r="H15" t="n">
+        <v>62</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
       <c r="K15" t="n">
-        <v>8.119999999999999</v>
+        <v>18.54</v>
       </c>
       <c r="L15" t="n">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="M15" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saint Spritz Hugo 4pk 355ml</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>197644216758</t>
+          <t>082000799894</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1308,28 +1312,28 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>10.33</v>
+        <v>7.79</v>
       </c>
       <c r="L16" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1338,12 +1342,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>085000036099</t>
+          <t>050200003295</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1353,53 +1357,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="H17" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
         <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>18.53</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="M17" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>050200003295</t>
+          <t>850003574066</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1413,31 +1413,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>8.119999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="L18" t="n">
-        <v>195</v>
+        <v>371</v>
       </c>
       <c r="M18" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -1468,7 +1468,7 @@
         <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
         <v>8</v>
@@ -1498,12 +1498,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>850003574066</t>
+          <t>089540535661</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1513,35 +1513,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>7.72</v>
+        <v>7.17</v>
       </c>
       <c r="L20" t="n">
-        <v>371</v>
+        <v>86</v>
       </c>
       <c r="M20" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -1624,7 +1624,7 @@
         <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
         <v>11</v>
@@ -1654,12 +1654,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>616003203135</t>
+          <t>089540535685</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1669,35 +1669,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>6</v>
       </c>
-      <c r="I23" t="n">
-        <v>30</v>
-      </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>9.75</v>
+        <v>7.15</v>
       </c>
       <c r="L23" t="n">
-        <v>292</v>
+        <v>43</v>
       </c>
       <c r="M23" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -1706,12 +1706,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Saint Spritz Hugo 4pk 355ml</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>089540535661</t>
+          <t>197644216758</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G24" t="n">
         <v>12</v>
-      </c>
-      <c r="F24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>11</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1743,13 +1743,13 @@
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>7.17</v>
+        <v>10.33</v>
       </c>
       <c r="L24" t="n">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="M24" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -1810,12 +1810,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Two Chicks Melon Drop 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>089540535685</t>
+          <t>850003574288</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1825,17 +1825,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1853,7 +1853,7 @@
         <v>43</v>
       </c>
       <c r="M26" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -1862,12 +1862,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>085000037393</t>
+          <t>616003203135</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1877,53 +1877,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="H27" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>18.34</v>
+        <v>9.75</v>
       </c>
       <c r="L27" t="n">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="M27" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Two Chicks Melon Drop 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>850003574288</t>
+          <t>085000037393</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1933,38 +1929,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="F28" t="n">
         <v>4.2</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>7.17</v>
+        <v>18.34</v>
       </c>
       <c r="L28" t="n">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="M28" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2022,12 +2022,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>891278002380</t>
+          <t>080432000779</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2037,20 +2037,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
         <v>4.5</v>
       </c>
       <c r="G30" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>6</v>
@@ -2059,13 +2059,13 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>7.56</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M30" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -2074,12 +2074,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>080432000779</t>
+          <t>850003574042</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2089,35 +2089,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>8.039999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="L31" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="M31" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -2126,50 +2126,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>Monaco Blue Crush 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>850003574042</t>
+          <t>891278002458</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="F32" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G32" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>12</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>5.86</v>
+        <v>1.92</v>
       </c>
       <c r="L32" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="M32" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
@@ -2178,12 +2178,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>089540535289</t>
+          <t>891278002380</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2193,20 +2193,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8.02</v>
+        <v>67</v>
       </c>
       <c r="F33" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
         <v>6</v>
@@ -2215,13 +2215,13 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>6.45</v>
+        <v>7.56</v>
       </c>
       <c r="L33" t="n">
+        <v>45</v>
+      </c>
+      <c r="M33" t="n">
         <v>39</v>
-      </c>
-      <c r="M33" t="n">
-        <v>48</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
@@ -2230,64 +2230,68 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>891278002458</t>
+          <t>085000038963</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F34" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I34" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>1.92</v>
+        <v>16.88</v>
       </c>
       <c r="L34" t="n">
-        <v>23</v>
+        <v>861</v>
       </c>
       <c r="M34" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>080432001257</t>
+          <t>089540535289</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2301,31 +2305,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>8.02</v>
       </c>
       <c r="F35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G35" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>12.88</v>
+        <v>6.45</v>
       </c>
       <c r="L35" t="n">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="M35" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -2334,12 +2338,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>085000038963</t>
+          <t>080432001257</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2349,42 +2353,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="G36" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="H36" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="J36" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>16.88</v>
+        <v>12.88</v>
       </c>
       <c r="L36" t="n">
-        <v>861</v>
+        <v>193</v>
       </c>
       <c r="M36" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2412,7 +2412,7 @@
         <v>22</v>
       </c>
       <c r="F37" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="G37" t="n">
         <v>19</v>
@@ -2442,12 +2442,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Saint Spritz Amalfi 4pk 355ml</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>850003574202</t>
+          <t>196852401789</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2457,20 +2457,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G38" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H38" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>12</v>
@@ -2479,13 +2479,13 @@
         <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>5.3</v>
+        <v>10.33</v>
       </c>
       <c r="L38" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="M38" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Saint Spritz Amalfi 4pk 355ml</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>196852401789</t>
+          <t>850003574202</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2509,20 +2509,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F39" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G39" t="n">
+        <v>25</v>
+      </c>
+      <c r="H39" t="n">
         <v>12</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>12</v>
@@ -2531,13 +2531,13 @@
         <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>10.33</v>
+        <v>5.3</v>
       </c>
       <c r="L39" t="n">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="M39" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -2546,50 +2546,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 4pk 12oz can</t>
+          <t>High Noon Peach 24oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>891278002311</t>
+          <t>085000034491</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="G40" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>7.58</v>
+        <v>4.5</v>
       </c>
       <c r="L40" t="n">
-        <v>45</v>
+        <v>162</v>
       </c>
       <c r="M40" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -2598,50 +2598,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Noon Peach 24oz can</t>
+          <t>Monaco Citrus Rush 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>085000034491</t>
+          <t>891278002311</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="G41" t="n">
+        <v>8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="L41" t="n">
+        <v>45</v>
+      </c>
+      <c r="M41" t="n">
         <v>39</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>36</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L41" t="n">
-        <v>162</v>
-      </c>
-      <c r="M41" t="n">
-        <v>44</v>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
@@ -2650,12 +2650,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
+          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>850003574196</t>
+          <t>850003574264</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2669,31 +2669,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F42" t="n">
         <v>7.1</v>
       </c>
       <c r="G42" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>6.88</v>
+        <v>7.83</v>
       </c>
       <c r="L42" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="M42" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
@@ -2702,12 +2702,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Two Chicks Watermelon Breeze 4pk 12oz can</t>
+          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>850003574264</t>
+          <t>860007263392</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2717,32 +2717,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F43" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="G43" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>7.83</v>
+        <v>7.5</v>
       </c>
       <c r="L43" t="n">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="M43" t="n">
         <v>40</v>
@@ -2754,12 +2754,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dirty Shirley Cherry Vanilla 4pk 12oz can</t>
+          <t>Two Chicks Lemon Strawberry Kiss 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>860007263392</t>
+          <t>850003574196</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F44" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="G44" t="n">
         <v>16</v>
@@ -2791,13 +2791,13 @@
         <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>7.5</v>
+        <v>6.88</v>
       </c>
       <c r="L44" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="M44" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F45" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G45" t="n">
         <v>7</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="n">
         <v>133</v>
@@ -3656,10 +3656,10 @@
         <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>16.98</v>
+        <v>16.97</v>
       </c>
       <c r="L3" t="n">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="M3" t="n">
         <v>32</v>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
         <v>1.4</v>
@@ -3716,10 +3716,10 @@
         <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>17.07</v>
+        <v>17.06</v>
       </c>
       <c r="L4" t="n">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="M4" t="n">
         <v>32</v>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
         <v>156</v>
@@ -3776,7 +3776,7 @@
         <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>8.609999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>1344</v>
@@ -3818,28 +3818,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>8.460000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="M6" t="n">
         <v>39</v>
@@ -4032,7 +4032,7 @@
         <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>38.1</v>
+        <v>39.6</v>
       </c>
       <c r="G2" t="n">
         <v>7</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
         <v>14</v>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
         <v>3.3</v>
@@ -4488,7 +4488,7 @@
         <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>8.56</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>359</v>
@@ -4528,7 +4528,7 @@
         <v>72</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="G3" t="n">
         <v>70</v>
@@ -4583,7 +4583,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>22</v>
@@ -4638,25 +4638,25 @@
         <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="n">
         <v>72</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>461</v>
+        <v>410</v>
       </c>
       <c r="M5" t="n">
         <v>38</v>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -4699,7 +4699,7 @@
         <v>171</v>
       </c>
       <c r="H6" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6" t="n">
         <v>96</v>
@@ -4708,10 +4708,10 @@
         <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>21.77</v>
+        <v>21.74</v>
       </c>
       <c r="L6" t="n">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="M6" t="n">
         <v>34</v>
@@ -4748,7 +4748,7 @@
         <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
         <v>31</v>
@@ -4789,7 +4789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Chanhassen (7)</t>
+          <t>Blaine (7)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -4970,7 +4970,7 @@
         <v>-5</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3</v>
+        <v>-3.4</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -5044,7 +5044,7 @@
         <v>-1</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="F7" t="n">
         <v>6</v>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -5269,14 +5269,14 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Vadnais Heights (7)</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -5309,11 +5309,11 @@
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Woodbury (6)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -5346,15 +5346,15 @@
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Woodbury (6)</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5488,7 +5488,7 @@
         <v>-7</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.2</v>
+        <v>-7</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Minneapolis (11)</t>
+          <t>Chanhassen (11)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -5855,24 +5855,24 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F29" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G29" t="n">
-        <v>936</v>
+        <v>891</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Andover (14), Bloomington (13), Rosemount (12), Minneapolis (4)</t>
+          <t>Andover (14), Blaine (14), Bloomington (13)</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Blaine (8)</t>
+          <t>Rosemount (8)</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -6049,7 +6049,7 @@
         <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -6105,29 +6105,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Chanhassen (6)</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -6142,33 +6142,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>St. Louis Park (9)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -6188,10 +6188,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
@@ -6406,14 +6406,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
@@ -6423,11 +6423,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -6443,65 +6443,65 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>261</v>
+        <v>31</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Minneapolis (8), Blaine (4)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -6512,29 +6512,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E47" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G47" t="n">
-        <v>220</v>
+        <v>326</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Minneapolis (11), Rosemount (4)</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -6549,33 +6549,33 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Minneapolis (9)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6595,24 +6595,24 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G49" t="n">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Minneapolis (9)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="F50" t="n">
         <v>7</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6672,7 +6672,7 @@
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6706,24 +6706,24 @@
         </is>
       </c>
       <c r="D52" t="n">
+        <v>42</v>
+      </c>
+      <c r="E52" t="n">
+        <v>99</v>
+      </c>
+      <c r="F52" t="n">
         <v>5</v>
       </c>
-      <c r="E52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F52" t="n">
-        <v>6</v>
-      </c>
       <c r="G52" t="n">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -6734,33 +6734,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>99</v>
+        <v>5.8</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -6771,33 +6771,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -6808,33 +6808,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G55" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>St. Louis Park (9)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6854,10 +6854,10 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>4</v>
@@ -6882,29 +6882,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>43.7</v>
+        <v>99</v>
       </c>
       <c r="F57" t="n">
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="E58" t="n">
-        <v>99</v>
+        <v>43.7</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Andover (4)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -6956,33 +6956,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>35.7</v>
+        <v>99</v>
       </c>
       <c r="F59" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (6)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6993,33 +6993,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>2.2</v>
+        <v>35.7</v>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G60" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Roseville (7)</t>
+          <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -7030,33 +7030,33 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>99</v>
+        <v>7.4</v>
       </c>
       <c r="F61" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Vadnais Heights (25)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -7072,24 +7072,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Monaco Blue Crush 4pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>11.7</v>
+        <v>2.5</v>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G62" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Cottage Grove (6)</t>
+          <t>Roseville (7)</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -7104,33 +7104,33 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E63" t="n">
-        <v>2.1</v>
+        <v>99</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G63" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Osseo (5)</t>
+          <t>Vadnais Heights (26)</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -7146,24 +7146,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Monaco Blue Crush 4pk 12oz can</t>
         </is>
       </c>
       <c r="D64" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F64" t="n">
         <v>6</v>
       </c>
-      <c r="E64" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F64" t="n">
-        <v>5</v>
-      </c>
       <c r="G64" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Cottage Grove (6)</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -7178,33 +7178,33 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G65" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Osseo (5)</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -7215,33 +7215,33 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="F66" t="n">
         <v>5</v>
       </c>
       <c r="G66" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -7252,33 +7252,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="F67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Andover (7)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -7289,33 +7289,33 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G68" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -7331,28 +7331,28 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G69" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Andover (7)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
         <v>99</v>
@@ -7381,7 +7381,7 @@
         <v>4</v>
       </c>
       <c r="G70" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -7400,29 +7400,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>8.9</v>
+        <v>3.2</v>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
         <v>35</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -7437,33 +7437,33 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E72" t="n">
-        <v>5.2</v>
+        <v>99</v>
       </c>
       <c r="F72" t="n">
         <v>4</v>
       </c>
       <c r="G72" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -7474,29 +7474,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>11.9</v>
+        <v>8.9</v>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G73" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -7511,33 +7511,33 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="F74" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cottage Grove (11)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -7548,29 +7548,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>2.9</v>
+        <v>14.3</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -7585,29 +7585,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E76" t="n">
-        <v>99</v>
+        <v>7.8</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G76" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Minneapolis (11)</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -7622,29 +7622,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G77" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -7696,29 +7696,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
-        <v>26.8</v>
+        <v>24.7</v>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -7733,29 +7733,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E80" t="n">
-        <v>6.4</v>
+        <v>99</v>
       </c>
       <c r="F80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -7770,29 +7770,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monaco Lemonade 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>99</v>
+        <v>26.8</v>
       </c>
       <c r="F81" t="n">
         <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7816,20 +7816,20 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>99</v>
+        <v>6.4</v>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -7844,32 +7844,106 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>Osseo</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Monaco Lemonade 12oz can</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>13</v>
+      </c>
+      <c r="E83" t="n">
+        <v>99</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>9</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Minneapolis (5)</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Blaine</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Monaco Mai Tai 12oz can</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" t="n">
+        <v>99</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>8</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Cottage Grove (4)</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Top-up</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>Ramsey</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D85" t="n">
         <v>3</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E85" t="n">
         <v>32.1</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F85" t="n">
         <v>4</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G85" t="n">
         <v>8</v>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Minneapolis (4)</t>
         </is>
       </c>
-      <c r="I83" t="n">
+      <c r="I85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
@@ -622,12 +622,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>085000031513</t>
+          <t>050200003486</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -637,57 +637,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="L4" t="n">
+        <v>324</v>
+      </c>
+      <c r="M4" t="n">
         <v>36</v>
       </c>
-      <c r="K4" t="n">
-        <v>16.97</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1833</v>
-      </c>
-      <c r="M4" t="n">
-        <v>32</v>
-      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Off buy-month - confirm timing</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sunny D Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>050200003486</t>
+          <t>085000031513</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -697,49 +689,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>15.46</v>
+        <v>16.97</v>
       </c>
       <c r="L5" t="n">
-        <v>325</v>
+        <v>1832</v>
       </c>
       <c r="M5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Off-month, buy anyway - urgent (deal: May, Aug)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Off buy-month - confirm timing</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>085000032558</t>
+          <t>085000429266</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,31 +753,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="J6" t="n">
+        <v>26</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1341</v>
+      </c>
+      <c r="M6" t="n">
         <v>38</v>
-      </c>
-      <c r="K6" t="n">
-        <v>17.06</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1945</v>
-      </c>
-      <c r="M6" t="n">
-        <v>32</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -794,12 +794,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>085000429266</t>
+          <t>085000032558</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="J7" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K7" t="n">
-        <v>8.619999999999999</v>
+        <v>17.06</v>
       </c>
       <c r="L7" t="n">
-        <v>1344</v>
+        <v>1945</v>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -943,7 +943,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>8.449999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="L9" t="n">
         <v>304</v>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
         <v>24</v>
@@ -1003,13 +1003,13 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>8.630000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
         <v>16</v>
@@ -1063,7 +1063,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="L11" t="n">
         <v>142</v>
@@ -1234,12 +1234,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>085000036099</t>
+          <t>050200003295</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1249,53 +1249,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>18.54</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="M15" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Loyal 9 Lemonade 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>082000799894</t>
+          <t>085000036099</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1309,45 +1305,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
         <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>7.79</v>
+        <v>18.54</v>
       </c>
       <c r="L16" t="n">
-        <v>47</v>
+        <v>223</v>
       </c>
       <c r="M16" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>Loyal 9 Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>050200003295</t>
+          <t>082000799894</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>8.119999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="L17" t="n">
-        <v>195</v>
+        <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
         <v>54</v>
@@ -1468,7 +1468,7 @@
         <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
         <v>8</v>
@@ -1498,12 +1498,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Malibu Pina Colada 4pk 12oz can</t>
+          <t>Monaco Moscow Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>089540535661</t>
+          <t>891278002717</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1513,35 +1513,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>7.17</v>
+        <v>7.58</v>
       </c>
       <c r="L20" t="n">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="M20" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -1550,12 +1550,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Monaco Moscow Mule 4pk 12oz can</t>
+          <t>Malibu Pina Colada 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>891278002717</t>
+          <t>089540535661</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1565,35 +1565,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="F21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>5</v>
-      </c>
       <c r="K21" t="n">
-        <v>7.58</v>
+        <v>7.17</v>
       </c>
       <c r="L21" t="n">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="M21" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -1654,12 +1654,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>089540535685</t>
+          <t>850003574028</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1669,35 +1669,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>7.15</v>
+        <v>7.67</v>
       </c>
       <c r="L23" t="n">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="M23" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -1758,12 +1758,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Malibu Strawberry Daiquiri 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>850003574028</t>
+          <t>089540535685</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1773,35 +1773,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
         <v>3.5</v>
       </c>
       <c r="G25" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>7.67</v>
+        <v>7.15</v>
       </c>
       <c r="L25" t="n">
-        <v>184</v>
+        <v>43</v>
       </c>
       <c r="M25" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
         <v>6</v>
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>7.15</v>
+        <v>7.12</v>
       </c>
       <c r="L26" t="n">
         <v>43</v>
@@ -1862,12 +1862,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>Jameson Orange Spritz 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>616003203135</t>
+          <t>080432000779</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1877,35 +1877,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
         <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>6</v>
       </c>
-      <c r="I27" t="n">
-        <v>30</v>
-      </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>9.75</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>292</v>
+        <v>48</v>
       </c>
       <c r="M27" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -1914,12 +1914,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>085000037393</t>
+          <t>616003203135</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1929,42 +1929,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="H28" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>18.34</v>
+        <v>9.75</v>
       </c>
       <c r="L28" t="n">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="M28" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1992,7 +1988,7 @@
         <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G29" t="n">
         <v>16</v>
@@ -2022,12 +2018,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jameson Orange Spritz 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>080432000779</t>
+          <t>085000037393</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2037,49 +2033,53 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="F30" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G30" t="n">
+        <v>59</v>
+      </c>
+      <c r="H30" t="n">
+        <v>48</v>
+      </c>
+      <c r="I30" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" t="n">
         <v>4</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
       <c r="K30" t="n">
-        <v>8.039999999999999</v>
+        <v>18.34</v>
       </c>
       <c r="L30" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="M30" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>850003574042</t>
+          <t>085000038963</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2089,38 +2089,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="F31" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>5.86</v>
+        <v>16.88</v>
       </c>
       <c r="L31" t="n">
-        <v>70</v>
+        <v>861</v>
       </c>
       <c r="M31" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>In buy-month (Jun)</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2148,7 +2152,7 @@
         <v>124</v>
       </c>
       <c r="F32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
         <v>7</v>
@@ -2200,7 +2204,7 @@
         <v>67</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G33" t="n">
         <v>11</v>
@@ -2230,12 +2234,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>085000038963</t>
+          <t>850003574042</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2245,53 +2249,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="F34" t="n">
         <v>5.1</v>
       </c>
       <c r="G34" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="H34" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="J34" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>16.88</v>
+        <v>5.86</v>
       </c>
       <c r="L34" t="n">
-        <v>861</v>
+        <v>70</v>
       </c>
       <c r="M34" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>In buy-month (Jun)</t>
-        </is>
-      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Absolut Mango Mule 4pk 12oz can</t>
+          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>089540535289</t>
+          <t>080432001257</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2305,31 +2305,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8.02</v>
+        <v>10</v>
       </c>
       <c r="F35" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="G35" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>6.45</v>
+        <v>12.88</v>
       </c>
       <c r="L35" t="n">
-        <v>39</v>
+        <v>193</v>
       </c>
       <c r="M35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -2338,17 +2338,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Absolut Ocean Spray Variety Pack 8pk 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>080432001257</t>
+          <t>080686008064</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2357,31 +2357,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F36" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="G36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>12.88</v>
+        <v>8.6</v>
       </c>
       <c r="L36" t="n">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="M36" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -2390,17 +2390,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>Absolut Mango Mule 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>080686008064</t>
+          <t>089540535289</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2409,31 +2409,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>22</v>
+        <v>8.02</v>
       </c>
       <c r="F37" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G37" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>8.6</v>
+        <v>6.45</v>
       </c>
       <c r="L37" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -2516,13 +2516,13 @@
         <v>40</v>
       </c>
       <c r="F39" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G39" t="n">
         <v>25</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I39" t="n">
         <v>12</v>
@@ -2568,7 +2568,7 @@
         <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G40" t="n">
         <v>39</v>
@@ -2672,7 +2672,7 @@
         <v>27</v>
       </c>
       <c r="F42" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="G42" t="n">
         <v>7</v>
@@ -2724,7 +2724,7 @@
         <v>30</v>
       </c>
       <c r="F43" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G43" t="n">
         <v>16</v>
@@ -2776,7 +2776,7 @@
         <v>34</v>
       </c>
       <c r="F44" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="G44" t="n">
         <v>16</v>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F45" t="n">
         <v>9.199999999999999</v>
@@ -2880,7 +2880,7 @@
         <v>33</v>
       </c>
       <c r="F46" t="n">
-        <v>10.7</v>
+        <v>11.3</v>
       </c>
       <c r="G46" t="n">
         <v>47</v>
@@ -2910,12 +2910,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
+          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>050200006050</t>
+          <t>082000799931</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2925,35 +2925,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F47" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="G47" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>15.55</v>
+        <v>7.8</v>
       </c>
       <c r="L47" t="n">
-        <v>327</v>
+        <v>47</v>
       </c>
       <c r="M47" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
@@ -2962,12 +2962,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Loyal 9 Ice Tea Lemonade 4pk 12oz can</t>
+          <t>Sunny D Vodka Seltzer Summer Variety Pack</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>082000799931</t>
+          <t>050200006050</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>15.4</v>
+        <v>12.2</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>7.8</v>
+        <v>15.55</v>
       </c>
       <c r="L48" t="n">
-        <v>47</v>
+        <v>327</v>
       </c>
       <c r="M48" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
@@ -3014,12 +3014,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Saint Spritz Sicily 4pk 355ml</t>
+          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>197644897254</t>
+          <t>082000799917</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3033,13 +3033,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
-        <v>23.1</v>
+        <v>20.8</v>
       </c>
       <c r="G49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -3051,13 +3051,13 @@
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>10.33</v>
+        <v>7.8</v>
       </c>
       <c r="L49" t="n">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="M49" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
@@ -3066,12 +3066,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
+          <t>Saint Spritz Sicily 4pk 355ml</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>082000799955</t>
+          <t>197644897254</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3085,31 +3085,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F50" t="n">
-        <v>28.6</v>
+        <v>28.2</v>
       </c>
       <c r="G50" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>7.8</v>
+        <v>10.33</v>
       </c>
       <c r="L50" t="n">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="M50" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
@@ -3118,45 +3118,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Samichlaus Classic</t>
+          <t>Loyal 9 Watermelon Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9009100000669</t>
+          <t>082000799955</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Import</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E51" t="n">
+        <v>16</v>
+      </c>
+      <c r="F51" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>6</v>
+      </c>
+      <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="F51" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2</v>
-      </c>
       <c r="K51" t="n">
-        <v>15.38</v>
+        <v>7.8</v>
       </c>
       <c r="L51" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="M51" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
@@ -3165,50 +3170,45 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Loyal 9 Mixed Berry Lemonade 4pk 12oz can</t>
+          <t>Samichlaus Classic</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>082000799917</t>
+          <t>9009100000669</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Import</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>39.8</v>
+        <v>32.1</v>
       </c>
       <c r="G52" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>7.8</v>
+        <v>15.38</v>
       </c>
       <c r="L52" t="n">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="M52" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
         <v>133</v>
@@ -3659,7 +3659,7 @@
         <v>16.97</v>
       </c>
       <c r="L3" t="n">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="M3" t="n">
         <v>32</v>
@@ -3679,12 +3679,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 4pk 12oz can</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>085000032558</t>
+          <t>085000429266</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3698,31 +3698,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="J4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1341</v>
+      </c>
+      <c r="M4" t="n">
         <v>38</v>
-      </c>
-      <c r="K4" t="n">
-        <v>17.06</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1945</v>
-      </c>
-      <c r="M4" t="n">
-        <v>32</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -3739,12 +3739,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 4pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>085000429266</t>
+          <t>085000032558</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3758,31 +3758,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>156</v>
+        <v>120</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="J5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K5" t="n">
-        <v>8.619999999999999</v>
+        <v>17.06</v>
       </c>
       <c r="L5" t="n">
-        <v>1344</v>
+        <v>1945</v>
       </c>
       <c r="M5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -3836,7 +3836,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="L6" t="n">
         <v>304</v>
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
         <v>24</v>
@@ -3896,13 +3896,13 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>8.630000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -4227,7 +4227,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
         <v>11</v>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
         <v>1.9</v>
@@ -4473,7 +4473,7 @@
         <v>76</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
         <v>63</v>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
         <v>70</v>
@@ -4583,7 +4583,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
         <v>22</v>
@@ -4635,28 +4635,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
         <v>72</v>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>8.539999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>410</v>
+        <v>462</v>
       </c>
       <c r="M5" t="n">
         <v>38</v>
@@ -4690,28 +4690,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
         <v>171</v>
       </c>
       <c r="H6" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I6" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K6" t="n">
-        <v>21.74</v>
+        <v>21.7</v>
       </c>
       <c r="L6" t="n">
-        <v>2087</v>
+        <v>2344</v>
       </c>
       <c r="M6" t="n">
         <v>34</v>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n">
         <v>4.3</v>
@@ -4754,7 +4754,7 @@
         <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
         <v>12</v>
@@ -4789,7 +4789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4859,7 +4859,7 @@
         <v>-5</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
@@ -4896,7 +4896,7 @@
         <v>-4</v>
       </c>
       <c r="E3" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
@@ -4958,29 +4958,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.4</v>
+        <v>-0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>St. Louis Park (14)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -4995,29 +4995,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4</v>
+        <v>-3.4</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Andover (5)</t>
+          <t>St. Louis Park (14)</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -5032,29 +5032,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E7" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bloomington (6)</t>
+          <t>Andover (5)</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -5069,19 +5069,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tropical Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
@@ -5106,29 +5106,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-21.4</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Chanhassen (5)</t>
+          <t>Bloomington (6)</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -5143,33 +5143,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4</v>
+        <v>-21.4</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bloomington (10)</t>
+          <t>Chanhassen (5)</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5180,33 +5180,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Bloomington (10)</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5217,29 +5217,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.3</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -5269,14 +5269,14 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Vadnais Heights (7)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -5291,29 +5291,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-20.3</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Plymouth (6)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Zing Zang RTD Bloody Mary 4pk 12oz can</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -5346,11 +5346,11 @@
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Woodbury (6)</t>
+          <t>Plymouth (6)</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -5365,29 +5365,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>High Noon Mango 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Woodbury (6)</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -5402,29 +5402,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Mango 4pk 12oz can</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -5454,14 +5454,14 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -5488,21 +5488,21 @@
         <v>-7</v>
       </c>
       <c r="E19" t="n">
-        <v>-7</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Chanhassen (5)</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Rosemount (4)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -5550,19 +5550,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
@@ -5572,11 +5572,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -5587,33 +5587,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
+          <t>High Noon Grapefruit 4pk 12oz can</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -5624,29 +5624,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Minneapolis (4)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -5661,29 +5661,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monaco Tropic Rush 12oz can</t>
+          <t>On The Rocks Blue Hawaiian LTO 375ml</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>99</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Minneapolis (15)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -5698,33 +5698,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Sunny D Vodka Seltzer 4pk 12oz can</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="E25" t="n">
-        <v>99</v>
+        <v>-22</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Chanhassen (11)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -5735,29 +5735,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monaco Sun Crush 12oz can</t>
+          <t>Two Chicks Pear &amp; Elderflower 4pk 12oz can</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.6</v>
+        <v>-3.7</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -5772,29 +5772,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monaco Tequila Lime Crush 12oz can</t>
+          <t>Monaco Tropic Rush 12oz can</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E27" t="n">
         <v>99</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Minneapolis (15)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -5809,29 +5809,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.5</v>
+        <v>99</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Chanhassen (11)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -5841,71 +5841,71 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>Monaco Sun Crush 12oz can</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>-11</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1</v>
+        <v>-6.6</v>
       </c>
       <c r="F29" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>891</v>
+        <v>9</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Andover (14), Blaine (14), Bloomington (13)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>Monaco Tequila Lime Crush 12oz can</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>99</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
         <v>9</v>
       </c>
-      <c r="E30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F30" t="n">
-        <v>17</v>
-      </c>
-      <c r="G30" t="n">
-        <v>315</v>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Chanhassen (17)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -5915,34 +5915,34 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Low &lt;2wk</t>
+          <t>STOCKOUT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9</v>
+        <v>-2.5</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Plymouth (10)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5966,24 +5966,24 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G32" t="n">
-        <v>174</v>
+        <v>868</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Rosemount (8)</t>
+          <t>Bloomington (14), Andover (14), Rosemount (12)</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G33" t="n">
-        <v>165</v>
+        <v>315</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Plymouth (9)</t>
+          <t>Chanhassen (17)</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -6031,29 +6031,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" t="n">
-        <v>0.1</v>
-      </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Plymouth (10)</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -6068,33 +6068,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High Noon Peach 4pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
         <v>1.5</v>
       </c>
       <c r="F35" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Minnetonka (5), Bloomington (5), St. Louis Park (4)</t>
+          <t>Minneapolis (8)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -6105,29 +6105,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Chanhassen (6)</t>
+          <t>Plymouth (9)</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -6142,33 +6142,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="D37" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14</v>
+      </c>
+      <c r="G37" t="n">
+        <v>120</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bloomington (5), Vadnais Heights (5), St. Louis Park (4)</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>5</v>
-      </c>
-      <c r="G37" t="n">
-        <v>84</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Stillwater (5)</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -6179,29 +6179,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bloomington (8)</t>
+          <t>Chanhassen (6)</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -6216,29 +6216,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>Blaine (6)</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -6253,33 +6253,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -6290,29 +6290,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>High Noon Black Cherry 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Andover (6)</t>
+          <t>St. Louis Park (9)</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -6327,29 +6327,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>0.4</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G42" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Bloomington (8)</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -6364,33 +6364,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F43" t="n">
         <v>4</v>
       </c>
-      <c r="E43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F43" t="n">
-        <v>5</v>
-      </c>
       <c r="G43" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bloomington (5)</t>
+          <t>Vadnais Heights (4)</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
@@ -6401,33 +6401,33 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High Noon Grapefruit 4pk 12oz can</t>
+          <t>High Noon Black Cherry 4pk 12oz can</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Vadnais Heights (4)</t>
+          <t>Andover (6)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -6443,28 +6443,28 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>The Finnish Long Drink Zero 6pk 12oz can</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -6475,29 +6475,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Bloomington (5)</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -6507,34 +6507,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>High Noon Variety Pack 12pk 12oz can</t>
+          <t>High Noon Lime 4pk 12oz can</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>326</v>
+        <v>35</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Minneapolis (11), Rosemount (4)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -6544,75 +6544,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F48" t="n">
         <v>4</v>
       </c>
-      <c r="E48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F48" t="n">
-        <v>12</v>
-      </c>
       <c r="G48" t="n">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Plymouth (12)</t>
+          <t>Rosemount (4)</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Top-up</t>
+          <t>Low &lt;2wk</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cottage Grove</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>0.3</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Minneapolis (9)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -6623,29 +6623,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vadnais Heights</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>118</v>
+        <v>220</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Stillwater (7)</t>
+          <t>Plymouth (12)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -6660,33 +6660,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Cottage Grove</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G51" t="n">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Blaine (6)</t>
+          <t>Minneapolis (9)</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -6697,33 +6697,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chanhassen</t>
+          <t>Vadnais Heights</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>99</v>
+        <v>4.7</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Roseville (5)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -6734,33 +6734,33 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Plymouth (5)</t>
+          <t>Stillwater (7)</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -6771,29 +6771,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Chanhassen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E54" t="n">
-        <v>6.4</v>
+        <v>99</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Roseville (5)</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -6808,33 +6808,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>2.1</v>
+        <v>6.7</v>
       </c>
       <c r="F55" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>St. Louis Park (9)</t>
+          <t>Plymouth (5)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6845,33 +6845,33 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rosemount</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
+          <t>High Noon Variety Pack 12pk 12oz can</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="F56" t="n">
         <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Rosemount</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>4</v>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Chanhassen (4)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -6919,29 +6919,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
+          <t>High Noon Tequila Variety Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>43.7</v>
+        <v>99</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Andover (4)</t>
+          <t>Chanhassen (4)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="E59" t="n">
-        <v>99</v>
+        <v>43.7</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Plymouth (4)</t>
+          <t>Bloomington (4)</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -6993,33 +6993,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Minneapolis</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>High Noon Tequila Fiesta Pack 8pk 12oz can</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>35.7</v>
+        <v>99</v>
       </c>
       <c r="F60" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Blaine (10), Minnetonka (6)</t>
+          <t>Plymouth (4)</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -7030,33 +7030,33 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Minneapolis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High Noon Iced Tea Variety Pack 8pk 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>7.4</v>
+        <v>40.2</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G61" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Blaine (10), Minnetonka (6)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -7079,7 +7079,7 @@
         <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F62" t="n">
         <v>7</v>
@@ -7190,7 +7190,7 @@
         <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F65" t="n">
         <v>5</v>
@@ -7220,28 +7220,28 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Stillwater (5)</t>
+          <t>Andover (8)</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -7252,29 +7252,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
+          <t>Two Chicks Vodka CuTea 4pk 12oz can</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G67" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Minnetonka (4)</t>
+          <t>Stillwater (5)</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -7289,33 +7289,33 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Two Chicks Paloma 4pk 12oz can</t>
+          <t>Tattersall Blueberry Collins 4pk 12oz can</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Minnetonka (5)</t>
+          <t>Minnetonka (4)</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -7326,33 +7326,33 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Two Chicks Paloma 4pk 12oz can</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Andover (7)</t>
+          <t>Minnetonka (5)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>St. Louis Park</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E71" t="n">
-        <v>3.2</v>
+        <v>99</v>
       </c>
       <c r="F71" t="n">
         <v>4</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bloomington (4)</t>
+          <t>Woodbury (4)</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -7442,24 +7442,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>High Noon Lime 4pk 12oz can</t>
+          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E72" t="n">
-        <v>99</v>
+        <v>8.9</v>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G72" t="n">
         <v>35</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Woodbury (4)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -7474,33 +7474,33 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>St. Louis Park</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Two Chicks Citrus Margarita 4pk 12oz can</t>
+          <t>High Noon Watermelon 4pk 12oz can</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>8.9</v>
+        <v>6.1</v>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G73" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Stillwater (4)</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -7516,28 +7516,28 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High Noon Watermelon 4pk 12oz can</t>
+          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
         </is>
       </c>
       <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F74" t="n">
         <v>5</v>
       </c>
-      <c r="E74" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F74" t="n">
-        <v>4</v>
-      </c>
       <c r="G74" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Stillwater (4)</t>
+          <t>St. Louis Park (5)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7548,29 +7548,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Roseville</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Two Chicks Cranberry Tartini 4pk 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E75" t="n">
-        <v>14.3</v>
+        <v>7.8</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G75" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>St. Louis Park (5)</t>
+          <t>Minneapolis (11)</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -7585,29 +7585,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Roseville</t>
+          <t>Woodbury</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>High Noon Pineapple 24oz can</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="F76" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Minneapolis (11)</t>
+          <t>Blaine (4)</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -7622,29 +7622,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Woodbury</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>High Noon Pineapple 24oz can</t>
+          <t>Monaco Mango Peach 12oz can</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E77" t="n">
-        <v>2.9</v>
+        <v>99</v>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G77" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Blaine (4)</t>
+          <t>Minneapolis (6)</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -7659,19 +7659,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Andover</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Monaco Mango Peach 12oz can</t>
+          <t>Monaco Watermelon Crush 12oz can</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>10</v>
       </c>
       <c r="E78" t="n">
-        <v>99</v>
+        <v>24.7</v>
       </c>
       <c r="F78" t="n">
         <v>6</v>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Minneapolis (6)</t>
+          <t>Vadnais Heights (6)</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Andover</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7708,7 +7708,7 @@
         <v>10</v>
       </c>
       <c r="E79" t="n">
-        <v>24.7</v>
+        <v>99</v>
       </c>
       <c r="F79" t="n">
         <v>6</v>
@@ -7733,29 +7733,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Monaco Watermelon Crush 12oz can</t>
+          <t>Monaco Citrus Rush 12oz can</t>
         </is>
       </c>
       <c r="D80" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" t="n">
         <v>10</v>
       </c>
-      <c r="E80" t="n">
-        <v>99</v>
-      </c>
-      <c r="F80" t="n">
-        <v>6</v>
-      </c>
-      <c r="G80" t="n">
-        <v>11</v>
-      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Vadnais Heights (6)</t>
+          <t>Cottage Grove (5)</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -7775,14 +7775,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monaco Citrus Rush 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>26.8</v>
+        <v>6.4</v>
       </c>
       <c r="F81" t="n">
         <v>5</v>
@@ -7807,29 +7807,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ramsey</t>
+          <t>Osseo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Lemonade 12oz can</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E82" t="n">
-        <v>6.4</v>
+        <v>99</v>
       </c>
       <c r="F82" t="n">
         <v>5</v>
       </c>
       <c r="G82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Cottage Grove (5)</t>
+          <t>Minneapolis (5)</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -7844,29 +7844,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Osseo</t>
+          <t>Blaine</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monaco Lemonade 12oz can</t>
+          <t>Monaco Mai Tai 12oz can</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
         <v>99</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Minneapolis (5)</t>
+          <t>Cottage Grove (4)</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -7881,19 +7881,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blaine</t>
+          <t>Ramsey</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monaco Mai Tai 12oz can</t>
+          <t>Monaco Purple Crush 12oz can</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>99</v>
+        <v>32.1</v>
       </c>
       <c r="F84" t="n">
         <v>4</v>
@@ -7903,47 +7903,10 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Cottage Grove (4)</t>
+          <t>Minneapolis (4)</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Top-up</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Ramsey</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Monaco Purple Crush 12oz can</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>3</v>
-      </c>
-      <c r="E85" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F85" t="n">
-        <v>4</v>
-      </c>
-      <c r="G85" t="n">
-        <v>8</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Minneapolis (4)</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S474"/>
+  <dimension ref="A1:S473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27051,55 +27051,60 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Michelob Golden Light 6pk 16oz can</t>
+          <t>Sun Cruiser Pink Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>01844328</t>
+          <t>087692024286</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>330</v>
+        <v>95</v>
       </c>
       <c r="F465" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G465" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
       <c r="H465" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I465" t="n">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="J465" t="n">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="K465" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="L465" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="M465" t="n">
-        <v>5.49</v>
+        <v>7.1</v>
       </c>
       <c r="N465" t="n">
-        <v>231</v>
+        <v>43</v>
       </c>
       <c r="O465" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q465" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R465" t="inlineStr"/>
@@ -27108,12 +27113,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Sun Cruiser Pink Lemonade 4pk 12oz can</t>
+          <t>Sun Cruiser Vodka Variety 8pk 12oz can</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>087692024286</t>
+          <t>087692020301</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -27127,37 +27132,37 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>95</v>
+        <v>552</v>
       </c>
       <c r="F466" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G466" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H466" t="n">
-        <v>0</v>
+        <v>54.8</v>
       </c>
       <c r="I466" t="n">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="J466" t="n">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="K466" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L466" t="n">
         <v>1</v>
       </c>
       <c r="M466" t="n">
-        <v>7.1</v>
+        <v>14.75</v>
       </c>
       <c r="N466" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O466" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="Q466" t="inlineStr">
         <is>
@@ -27170,12 +27175,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Sun Cruiser Vodka Variety 8pk 12oz can</t>
+          <t>Carbliss Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>087692020301</t>
+          <t>86000981953</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -27185,41 +27190,41 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>College City Beverage, Inc.</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>552</v>
+        <v>148</v>
       </c>
       <c r="F467" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G467" t="n">
-        <v>-4</v>
+        <v>-17</v>
       </c>
       <c r="H467" t="n">
-        <v>54.8</v>
+        <v>41.2</v>
       </c>
       <c r="I467" t="n">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="J467" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="K467" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L467" t="n">
         <v>1</v>
       </c>
       <c r="M467" t="n">
-        <v>14.75</v>
+        <v>8.81</v>
       </c>
       <c r="N467" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="O467" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q467" t="inlineStr">
         <is>
@@ -27232,12 +27237,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Carbliss Peach 4pk 12oz can</t>
+          <t>Sun Cruiser Lemonade Iced Tea 8pk 12oz can</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>86000981953</t>
+          <t>087692021421</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -27245,43 +27250,38 @@
           <t>RTD</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>College City Beverage, Inc.</t>
-        </is>
-      </c>
       <c r="E468" t="n">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="F468" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="G468" t="n">
-        <v>-17</v>
+        <v>1</v>
       </c>
       <c r="H468" t="n">
-        <v>41.2</v>
+        <v>5.8</v>
       </c>
       <c r="I468" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="J468" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K468" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L468" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M468" t="n">
-        <v>8.81</v>
+        <v>14.64</v>
       </c>
       <c r="N468" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="O468" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="Q468" t="inlineStr">
         <is>
@@ -27294,12 +27294,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Sun Cruiser Lemonade Iced Tea 8pk 12oz can</t>
+          <t>Sun Cruiser Classic Iced Tea  8pk 12oz can</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>087692021421</t>
+          <t>087692021414</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -27308,34 +27308,34 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="F469" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="G469" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H469" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="I469" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="J469" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K469" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L469" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M469" t="n">
-        <v>14.64</v>
+        <v>14.8</v>
       </c>
       <c r="N469" t="n">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="O469" t="n">
         <v>33</v>
@@ -27351,51 +27351,51 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Sun Cruiser Classic Iced Tea  8pk 12oz can</t>
+          <t>Sun Cruiser Lemonade Iced Tea 700ml can</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>087692021414</t>
+          <t>087692021933</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>264</v>
+        <v>2</v>
       </c>
       <c r="F470" t="n">
-        <v>6.7</v>
+        <v>8.6</v>
       </c>
       <c r="G470" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H470" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I470" t="n">
+        <v>1</v>
+      </c>
+      <c r="J470" t="n">
+        <v>0</v>
+      </c>
+      <c r="K470" t="n">
+        <v>1</v>
+      </c>
+      <c r="L470" t="n">
+        <v>1</v>
+      </c>
+      <c r="M470" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N470" t="n">
         <v>4</v>
       </c>
-      <c r="H470" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I470" t="n">
-        <v>51</v>
-      </c>
-      <c r="J470" t="n">
-        <v>48</v>
-      </c>
-      <c r="K470" t="n">
-        <v>3</v>
-      </c>
-      <c r="L470" t="n">
-        <v>3</v>
-      </c>
-      <c r="M470" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N470" t="n">
-        <v>44</v>
-      </c>
       <c r="O470" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
@@ -27403,56 +27403,65 @@
         </is>
       </c>
       <c r="R470" t="inlineStr"/>
-      <c r="S470" t="inlineStr"/>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>Overstocked (9 wks on hand) - confirm before buying more; Seasonal - last year ~10/wk vs 0 now, buy ahead?</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Sun Cruiser Lemonade Iced Tea 700ml can</t>
+          <t>Sun Cruiser Vodka Iced Tea Classic 4pk 12oz can</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>087692021933</t>
+          <t>087692020288</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="F471" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G471" t="n">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="H471" t="n">
-        <v>10.2</v>
+        <v>2.2</v>
       </c>
       <c r="I471" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J471" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K471" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L471" t="n">
         <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>3.74</v>
+        <v>7.15</v>
       </c>
       <c r="N471" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="O471" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
@@ -27462,19 +27471,19 @@
       <c r="R471" t="inlineStr"/>
       <c r="S471" t="inlineStr">
         <is>
-          <t>Overstocked (9 wks on hand) - confirm before buying more; Seasonal - last year ~10/wk vs 0 now, buy ahead?</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Sun Cruiser Vodka Iced Tea Classic 4pk 12oz can</t>
+          <t>Sun Cruiser Vodka Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>087692020288</t>
+          <t>087692024293</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -27488,22 +27497,22 @@
         </is>
       </c>
       <c r="E472" t="n">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="F472" t="n">
-        <v>9.800000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="G472" t="n">
-        <v>-10</v>
+        <v>-41</v>
       </c>
       <c r="H472" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I472" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J472" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K472" t="n">
         <v>6</v>
@@ -27512,13 +27521,13 @@
         <v>1</v>
       </c>
       <c r="M472" t="n">
-        <v>7.15</v>
+        <v>7.28</v>
       </c>
       <c r="N472" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O472" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
@@ -27528,63 +27537,58 @@
       <c r="R472" t="inlineStr"/>
       <c r="S472" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Sun Cruiser Vodka Lemonade 4pk 12oz can</t>
+          <t>Sun Cruiser Classic Iced Tea 700ml can</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>087692024293</t>
+          <t>087692021926</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F473" t="n">
-        <v>11.4</v>
+        <v>15</v>
       </c>
       <c r="G473" t="n">
-        <v>-41</v>
+        <v>26</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
       </c>
       <c r="I473" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J473" t="n">
         <v>0</v>
       </c>
       <c r="K473" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L473" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M473" t="n">
-        <v>7.28</v>
+        <v>3.88</v>
       </c>
       <c r="N473" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="O473" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
@@ -27593,67 +27597,6 @@
       </c>
       <c r="R473" t="inlineStr"/>
       <c r="S473" t="inlineStr">
-        <is>
-          <t>Overstocked (11 wks on hand) - confirm before buying more</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>Sun Cruiser Classic Iced Tea 700ml can</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>087692021926</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>Single Serve</t>
-        </is>
-      </c>
-      <c r="E474" t="n">
-        <v>28</v>
-      </c>
-      <c r="F474" t="n">
-        <v>15</v>
-      </c>
-      <c r="G474" t="n">
-        <v>26</v>
-      </c>
-      <c r="H474" t="n">
-        <v>0</v>
-      </c>
-      <c r="I474" t="n">
-        <v>3</v>
-      </c>
-      <c r="J474" t="n">
-        <v>0</v>
-      </c>
-      <c r="K474" t="n">
-        <v>3</v>
-      </c>
-      <c r="L474" t="n">
-        <v>3</v>
-      </c>
-      <c r="M474" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N474" t="n">
-        <v>12</v>
-      </c>
-      <c r="O474" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q474" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R474" t="inlineStr"/>
-      <c r="S474" t="inlineStr">
         <is>
           <t>Overstocked (15 wks on hand) - confirm before buying more</t>
         </is>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27171,21 +27171,25 @@
         <v>136</v>
       </c>
       <c r="K466" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="L466" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="M466" t="n">
         <v>5.49</v>
       </c>
       <c r="N466" t="n">
-        <v>11</v>
+        <v>330</v>
       </c>
       <c r="O466" t="n">
         <v>39</v>
       </c>
-      <c r="Q466" t="inlineStr"/>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R466" t="inlineStr"/>
       <c r="S466" t="inlineStr"/>
     </row>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S502"/>
+  <dimension ref="A1:S501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28682,55 +28682,60 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Michelob Golden Light 6pk 16oz can</t>
+          <t>Sun Cruiser Pink Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>01844328</t>
+          <t>087692024286</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>340</v>
+        <v>86</v>
       </c>
       <c r="F493" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G493" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="H493" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I493" t="n">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="J493" t="n">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="K493" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="L493" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="M493" t="n">
-        <v>5.5</v>
+        <v>7.09</v>
       </c>
       <c r="N493" t="n">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="O493" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q493" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
       <c r="R493" t="inlineStr"/>
@@ -28739,12 +28744,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Sun Cruiser Pink Lemonade 4pk 12oz can</t>
+          <t>Sun Cruiser Lemonade Iced Tea 8pk 12oz can</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>087692024286</t>
+          <t>087692021421</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -28752,43 +28757,38 @@
           <t>RTD</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
-        </is>
-      </c>
       <c r="E494" t="n">
-        <v>86</v>
+        <v>261</v>
       </c>
       <c r="F494" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="G494" t="n">
-        <v>-12</v>
+        <v>11</v>
       </c>
       <c r="H494" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="I494" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="J494" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K494" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L494" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M494" t="n">
-        <v>7.09</v>
+        <v>14.51</v>
       </c>
       <c r="N494" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O494" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q494" t="inlineStr">
         <is>
@@ -28801,51 +28801,51 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Sun Cruiser Lemonade Iced Tea 8pk 12oz can</t>
+          <t>Lagunitas Uncensored Punch 19.2oz can</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>087692021421</t>
+          <t>723830200180</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>261</v>
+        <v>23</v>
       </c>
       <c r="F495" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="G495" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H495" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I495" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="J495" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K495" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L495" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M495" t="n">
-        <v>14.51</v>
+        <v>1.81</v>
       </c>
       <c r="N495" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="O495" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="Q495" t="inlineStr">
         <is>
@@ -28858,51 +28858,51 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Lagunitas Uncensored Punch 19.2oz can</t>
+          <t>Sun Cruiser Classic Iced Tea  8pk 12oz can</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>723830200180</t>
+          <t>087692021414</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>23</v>
+        <v>285</v>
       </c>
       <c r="F496" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
       <c r="G496" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H496" t="n">
+        <v>6</v>
+      </c>
+      <c r="I496" t="n">
+        <v>62</v>
+      </c>
+      <c r="J496" t="n">
+        <v>57</v>
+      </c>
+      <c r="K496" t="n">
         <v>5</v>
       </c>
-      <c r="I496" t="n">
-        <v>1</v>
-      </c>
-      <c r="J496" t="n">
-        <v>0</v>
-      </c>
-      <c r="K496" t="n">
-        <v>1</v>
-      </c>
       <c r="L496" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M496" t="n">
-        <v>1.81</v>
+        <v>14.74</v>
       </c>
       <c r="N496" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="O496" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="Q496" t="inlineStr">
         <is>
@@ -28915,12 +28915,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Sun Cruiser Classic Iced Tea  8pk 12oz can</t>
+          <t>Carbliss Peach 4pk 12oz can</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>087692021414</t>
+          <t>86000981953</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -28928,38 +28928,43 @@
           <t>RTD</t>
         </is>
       </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>College City Beverage, Inc.</t>
+        </is>
+      </c>
       <c r="E497" t="n">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="F497" t="n">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G497" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H497" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="I497" t="n">
         <v>9</v>
       </c>
-      <c r="H497" t="n">
+      <c r="J497" t="n">
+        <v>7</v>
+      </c>
+      <c r="K497" t="n">
         <v>6</v>
       </c>
-      <c r="I497" t="n">
-        <v>62</v>
-      </c>
-      <c r="J497" t="n">
-        <v>57</v>
-      </c>
-      <c r="K497" t="n">
-        <v>5</v>
-      </c>
       <c r="L497" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M497" t="n">
-        <v>14.74</v>
+        <v>8.84</v>
       </c>
       <c r="N497" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="O497" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q497" t="inlineStr">
         <is>
@@ -28967,61 +28972,60 @@
         </is>
       </c>
       <c r="R497" t="inlineStr"/>
-      <c r="S497" t="inlineStr"/>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>Overstocked (8 wks on hand) - confirm before buying more; Seasonal - last year ~47/wk vs 29 now, buy ahead?</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Carbliss Peach 4pk 12oz can</t>
+          <t>Sun Cruiser Lemonade Iced Tea 700ml can</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>86000981953</t>
+          <t>087692021933</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>College City Beverage, Inc.</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="F498" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G498" t="n">
-        <v>-15</v>
+        <v>50</v>
       </c>
       <c r="H498" t="n">
-        <v>47.2</v>
+        <v>10.8</v>
       </c>
       <c r="I498" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J498" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K498" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L498" t="n">
         <v>1</v>
       </c>
       <c r="M498" t="n">
-        <v>8.84</v>
+        <v>3.74</v>
       </c>
       <c r="N498" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="O498" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="Q498" t="inlineStr">
         <is>
@@ -29031,58 +29035,63 @@
       <c r="R498" t="inlineStr"/>
       <c r="S498" t="inlineStr">
         <is>
-          <t>Overstocked (8 wks on hand) - confirm before buying more; Seasonal - last year ~47/wk vs 29 now, buy ahead?</t>
+          <t>Overstocked (9 wks on hand) - confirm before buying more; Seasonal - last year ~11/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Sun Cruiser Lemonade Iced Tea 700ml can</t>
+          <t>Sun Cruiser Vodka Lemonade 4pk 12oz can</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>087692021933</t>
+          <t>087692024293</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Single Serve</t>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Beer, LLC</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="F499" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="G499" t="n">
-        <v>50</v>
+        <v>-32</v>
       </c>
       <c r="H499" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="I499" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J499" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K499" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L499" t="n">
         <v>1</v>
       </c>
       <c r="M499" t="n">
-        <v>3.74</v>
+        <v>7.26</v>
       </c>
       <c r="N499" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="O499" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="Q499" t="inlineStr">
         <is>
@@ -29092,19 +29101,19 @@
       <c r="R499" t="inlineStr"/>
       <c r="S499" t="inlineStr">
         <is>
-          <t>Overstocked (9 wks on hand) - confirm before buying more; Seasonal - last year ~11/wk vs 0 now, buy ahead?</t>
+          <t>Overstocked (9 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Sun Cruiser Vodka Lemonade 4pk 12oz can</t>
+          <t>Sun Cruiser Vodka Iced Tea Classic 4pk 12oz can</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>087692024293</t>
+          <t>087692020288</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -29118,22 +29127,22 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="F500" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G500" t="n">
-        <v>-32</v>
+        <v>-17</v>
       </c>
       <c r="H500" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I500" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J500" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K500" t="n">
         <v>6</v>
@@ -29142,13 +29151,13 @@
         <v>1</v>
       </c>
       <c r="M500" t="n">
-        <v>7.26</v>
+        <v>7.15</v>
       </c>
       <c r="N500" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O500" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q500" t="inlineStr">
         <is>
@@ -29158,63 +29167,58 @@
       <c r="R500" t="inlineStr"/>
       <c r="S500" t="inlineStr">
         <is>
-          <t>Overstocked (9 wks on hand) - confirm before buying more</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Sun Cruiser Vodka Iced Tea Classic 4pk 12oz can</t>
+          <t>Sun Cruiser Classic Iced Tea 700ml can</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>087692020288</t>
+          <t>087692021926</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Beer, LLC</t>
+          <t>Single Serve</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="F501" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="G501" t="n">
-        <v>-17</v>
+        <v>20</v>
       </c>
       <c r="H501" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I501" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J501" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K501" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L501" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M501" t="n">
-        <v>7.15</v>
+        <v>3.88</v>
       </c>
       <c r="N501" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="O501" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Q501" t="inlineStr">
         <is>
@@ -29223,67 +29227,6 @@
       </c>
       <c r="R501" t="inlineStr"/>
       <c r="S501" t="inlineStr">
-        <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>Sun Cruiser Classic Iced Tea 700ml can</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>087692021926</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>Single Serve</t>
-        </is>
-      </c>
-      <c r="E502" t="n">
-        <v>27</v>
-      </c>
-      <c r="F502" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G502" t="n">
-        <v>20</v>
-      </c>
-      <c r="H502" t="n">
-        <v>0</v>
-      </c>
-      <c r="I502" t="n">
-        <v>3</v>
-      </c>
-      <c r="J502" t="n">
-        <v>0</v>
-      </c>
-      <c r="K502" t="n">
-        <v>3</v>
-      </c>
-      <c r="L502" t="n">
-        <v>3</v>
-      </c>
-      <c r="M502" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N502" t="n">
-        <v>12</v>
-      </c>
-      <c r="O502" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q502" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R502" t="inlineStr"/>
-      <c r="S502" t="inlineStr">
         <is>
           <t>Overstocked (14 wks on hand) - confirm before buying more</t>
         </is>

--- a/data/Beer Recommended Order.xlsx
+++ b/data/Beer Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
